--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,36 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7ECDEA-BF12-45FE-BEB2-36534ED29CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45483B66-ECBF-4CCA-900B-63503DB0C757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
     <sheet name="LEEME" sheetId="1" r:id="rId2"/>
-    <sheet name="Sebastián Muratore" sheetId="2" r:id="rId3"/>
-    <sheet name="Ezequiel Fasciolo" sheetId="3" r:id="rId4"/>
-    <sheet name="Barbara Lauriente" sheetId="4" r:id="rId5"/>
-    <sheet name="Germán Muratore" sheetId="5" r:id="rId6"/>
-    <sheet name="Romano Copello" sheetId="6" r:id="rId7"/>
-    <sheet name="Juan Lauriente" sheetId="7" r:id="rId8"/>
-    <sheet name="Josefina Pellejero" sheetId="8" r:id="rId9"/>
-    <sheet name="Valeria Blois" sheetId="12" r:id="rId10"/>
-    <sheet name="Natalia Sanchez" sheetId="13" r:id="rId11"/>
-    <sheet name="Rocio Duchi" sheetId="14" r:id="rId12"/>
-    <sheet name="Candela Stamadianos" sheetId="15" r:id="rId13"/>
-    <sheet name="Mario Flores" sheetId="16" r:id="rId14"/>
-    <sheet name="Elio Acevedo" sheetId="11" r:id="rId15"/>
-    <sheet name="Johana Araujo" sheetId="10" r:id="rId16"/>
-    <sheet name="Juan Ignacio Giancarli" sheetId="9" r:id="rId17"/>
-    <sheet name="Nancy Noguera" sheetId="17" r:id="rId18"/>
+    <sheet name="Eric Tomanovich" sheetId="19" r:id="rId3"/>
+    <sheet name="Sebastián Muratore" sheetId="2" r:id="rId4"/>
+    <sheet name="Ezequiel Fasciolo" sheetId="3" r:id="rId5"/>
+    <sheet name="Barbara Lauriente" sheetId="4" r:id="rId6"/>
+    <sheet name="Germán Muratore" sheetId="5" r:id="rId7"/>
+    <sheet name="Romano Copello" sheetId="6" r:id="rId8"/>
+    <sheet name="Juan Lauriente" sheetId="7" r:id="rId9"/>
+    <sheet name="Josefina Pellejero" sheetId="8" r:id="rId10"/>
+    <sheet name="Valeria Blois" sheetId="12" r:id="rId11"/>
+    <sheet name="Natalia Sanchez" sheetId="13" r:id="rId12"/>
+    <sheet name="Rocio Duchi" sheetId="14" r:id="rId13"/>
+    <sheet name="Candela Stamadianos" sheetId="15" r:id="rId14"/>
+    <sheet name="Mario Flores" sheetId="16" r:id="rId15"/>
+    <sheet name="Elio Acevedo" sheetId="11" r:id="rId16"/>
+    <sheet name="Johana Araujo" sheetId="10" r:id="rId17"/>
+    <sheet name="Juan Ignacio Giancarli" sheetId="9" r:id="rId18"/>
+    <sheet name="Nancy Noguera" sheetId="17" r:id="rId19"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="247">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -387,9 +388,6 @@
     <t>Aperturas en banco plano</t>
   </si>
   <si>
-    <t>1x7 (60% RM) 4x5 (70%)</t>
-  </si>
-  <si>
     <t>3x6 cada pierna</t>
   </si>
   <si>
@@ -432,9 +430,6 @@
     <t>Skater squats</t>
   </si>
   <si>
-    <t>1x7 (60% RM) 3x5 (70%)</t>
-  </si>
-  <si>
     <t>1x7 3x5 (Aumentando la carga)</t>
   </si>
   <si>
@@ -670,6 +665,120 @@
   </si>
   <si>
     <t>Pull over en polea</t>
+  </si>
+  <si>
+    <t>5x7 (60% RM)</t>
+  </si>
+  <si>
+    <t>Curl de isquios en maquina unilat</t>
+  </si>
+  <si>
+    <t>Goblet Lunges</t>
+  </si>
+  <si>
+    <t>Vuelos poteriores en maquina</t>
+  </si>
+  <si>
+    <t>Elevación de Gemelos en Prensa</t>
+  </si>
+  <si>
+    <t>4x8 cada pierna</t>
+  </si>
+  <si>
+    <t>Bulgarian split Squats</t>
+  </si>
+  <si>
+    <t>Plank inverted</t>
+  </si>
+  <si>
+    <t>Toco talones</t>
+  </si>
+  <si>
+    <t>15''</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunges </t>
+  </si>
+  <si>
+    <t>Athletic Burpees</t>
+  </si>
+  <si>
+    <t>Squat jump</t>
+  </si>
+  <si>
+    <t>Sumo Squats</t>
+  </si>
+  <si>
+    <t>Mountain climbers</t>
+  </si>
+  <si>
+    <t>Box pistols</t>
+  </si>
+  <si>
+    <t>Espinales</t>
+  </si>
+  <si>
+    <t>V ups alternados</t>
+  </si>
+  <si>
+    <t>Lunges Jump</t>
+  </si>
+  <si>
+    <t>Burpees</t>
+  </si>
+  <si>
+    <t>Skipping</t>
+  </si>
+  <si>
+    <t>Tuck up</t>
+  </si>
+  <si>
+    <t>Push ups inclinado</t>
+  </si>
+  <si>
+    <t>Jumping jacks</t>
+  </si>
+  <si>
+    <t>Grasshoppers</t>
+  </si>
+  <si>
+    <t>6 cada pe</t>
+  </si>
+  <si>
+    <t>30''</t>
+  </si>
+  <si>
+    <t>1x8 3x6 (Aumentando la carga)</t>
+  </si>
+  <si>
+    <t>Curl biceps en polea</t>
+  </si>
+  <si>
+    <t>Curl de biceps con mancuernas</t>
+  </si>
+  <si>
+    <t>Row 45°</t>
+  </si>
+  <si>
+    <t>Patada de gluteos con tobillera</t>
+  </si>
+  <si>
+    <t>Goblet lateral lunges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Press arnold   </t>
+  </si>
+  <si>
+    <t>Row Serruchio</t>
+  </si>
+  <si>
+    <t>8 cada brazo</t>
+  </si>
+  <si>
+    <t>Back Sumo Squats</t>
+  </si>
+  <si>
+    <t>Abductores con tobilleras</t>
   </si>
 </sst>
 </file>
@@ -714,7 +823,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -745,6 +854,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -758,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -771,6 +904,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1075,85 +1212,88 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFA7DCE8-210C-4BFD-AA45-1F97287776CF}">
   <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -1162,6 +1302,505 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C300" xr:uid="{00000000-0002-0000-0700-000000000000}">
+      <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1672,9 +2311,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1782,7 +2421,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>51</v>
@@ -1834,344 +2473,1208 @@
         <v>2</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="7">
-        <v>8</v>
+        <v>54</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="4">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="7">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" s="7">
+        <v>1</v>
+      </c>
+      <c r="B14" s="7">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="7">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="7">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" s="7">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="7">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+      <c r="A20" s="7">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="F21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="A22" s="7">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="F22" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>3</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4">
+        <v>3</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="4">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4">
+        <v>3</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4">
+        <v>3</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4">
+        <v>3</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4">
+        <v>3</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4">
+        <v>3</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="7">
+        <v>1</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="4">
+        <v>3</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H30" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="A31" s="7">
+        <v>1</v>
+      </c>
+      <c r="B31" s="4">
+        <v>3</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4">
+        <v>3</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="F32" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
+      <c r="A33" s="7">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4">
+        <v>3</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="F33" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4">
+        <v>3</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="F34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="7">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4">
+        <v>3</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="4">
+        <v>2</v>
+      </c>
+      <c r="E35" s="4">
+        <v>3</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="A36" s="7">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4">
+        <v>3</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="4">
+        <v>2</v>
+      </c>
+      <c r="E36" s="4">
+        <v>3</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" s="4">
+        <v>12</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="A37" s="7">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4">
+        <v>3</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="4">
+        <v>2</v>
+      </c>
+      <c r="E37" s="4">
+        <v>3</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="A38" s="7">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4">
+        <v>3</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="4">
+        <v>3</v>
+      </c>
+      <c r="E38" s="4">
+        <v>3</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="A39" s="7">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="4">
+        <v>3</v>
+      </c>
+      <c r="E39" s="4">
+        <v>3</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H39" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4">
+        <v>3</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="4">
+        <v>3</v>
+      </c>
+      <c r="E40" s="4">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4">
+        <v>4</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="7">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H41" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4">
+        <v>4</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1</v>
+      </c>
+      <c r="E42" s="7">
+        <v>2</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4">
+        <v>4</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H43" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4">
+        <v>4</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H44" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4">
+        <v>4</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1</v>
+      </c>
+      <c r="E45" s="7">
+        <v>2</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>1</v>
+      </c>
+      <c r="B46" s="4">
+        <v>4</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>1</v>
+      </c>
+      <c r="B47" s="4">
+        <v>4</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>1</v>
+      </c>
+      <c r="B48" s="4">
+        <v>4</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H48" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>1</v>
+      </c>
+      <c r="B49" s="4">
+        <v>4</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4">
+        <v>4</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4">
+        <v>4</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4">
+        <v>4</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>3</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4">
+        <v>4</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4">
+        <v>4</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H54" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2183,9 +3686,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2228,25 +3731,25 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <v>2</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2254,25 +3757,25 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2280,25 +3783,25 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="8">
         <v>10</v>
       </c>
     </row>
@@ -2306,25 +3809,25 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>2</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="8">
         <v>8</v>
       </c>
     </row>
@@ -2332,357 +3835,1145 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>4</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" s="7">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="7">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4">
+        <v>4</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="7">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4">
+        <v>4</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10">
+        <v>2</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" s="7">
+        <v>1</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11">
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="7">
+        <v>1</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="A20" s="7">
+        <v>1</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11">
+        <v>2</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="A22" s="7">
+        <v>1</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11">
+        <v>2</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="10">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>4</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="4">
+        <v>2</v>
+      </c>
+      <c r="E24" s="4">
+        <v>4</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2</v>
+      </c>
+      <c r="E25" s="4">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="10">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="4">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4">
+        <v>4</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" s="4">
+        <v>12</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="4">
+        <v>3</v>
+      </c>
+      <c r="E27" s="4">
+        <v>4</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="4">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4">
+        <v>4</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="4">
+        <v>4</v>
+      </c>
+      <c r="E29" s="4">
+        <v>4</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="10">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="4">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="A31" s="7">
+        <v>1</v>
+      </c>
+      <c r="B31" s="10">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="4">
+        <v>4</v>
+      </c>
+      <c r="E31" s="4">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="10">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="4">
+        <v>4</v>
+      </c>
+      <c r="E32" s="4">
+        <v>4</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="A33" s="7">
+        <v>1</v>
+      </c>
+      <c r="B33" s="10">
+        <v>2</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="4">
+        <v>4</v>
+      </c>
+      <c r="E33" s="4">
+        <v>4</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H33" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="10">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="4">
+        <v>4</v>
+      </c>
+      <c r="E34" s="4">
+        <v>4</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H34" s="4">
+        <v>12</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="7">
+        <v>1</v>
+      </c>
+      <c r="B35" s="12">
+        <v>3</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="13">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13">
+        <v>2</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="A36" s="7">
+        <v>1</v>
+      </c>
+      <c r="B36" s="12">
+        <v>3</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13">
+        <v>2</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="A37" s="7">
+        <v>1</v>
+      </c>
+      <c r="B37" s="12">
+        <v>3</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="13">
+        <v>2</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="12">
+        <v>7</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="A38" s="7">
+        <v>1</v>
+      </c>
+      <c r="B38" s="12">
+        <v>3</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="13">
+        <v>1</v>
+      </c>
+      <c r="E38" s="13">
+        <v>2</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" s="12">
+        <v>8</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="A39" s="7">
+        <v>1</v>
+      </c>
+      <c r="B39" s="12">
+        <v>3</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="13">
+        <v>1</v>
+      </c>
+      <c r="E39" s="13">
+        <v>2</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>1</v>
+      </c>
+      <c r="B40" s="12">
+        <v>3</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="13">
+        <v>1</v>
+      </c>
+      <c r="E40" s="13">
+        <v>2</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>1</v>
+      </c>
+      <c r="B41" s="12">
+        <v>3</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2</v>
+      </c>
+      <c r="E41" s="13">
+        <v>4</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>1</v>
+      </c>
+      <c r="B42" s="12">
+        <v>3</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2</v>
+      </c>
+      <c r="E42" s="13">
+        <v>4</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="12">
+        <v>3</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2</v>
+      </c>
+      <c r="E43" s="13">
+        <v>4</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>1</v>
+      </c>
+      <c r="B44" s="12">
+        <v>3</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="13">
+        <v>3</v>
+      </c>
+      <c r="E44" s="13">
+        <v>4</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>1</v>
+      </c>
+      <c r="B45" s="12">
+        <v>3</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="13">
+        <v>3</v>
+      </c>
+      <c r="E45" s="13">
+        <v>4</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H45" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>1</v>
+      </c>
+      <c r="B46" s="12">
+        <v>3</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="13">
+        <v>3</v>
+      </c>
+      <c r="E46" s="13">
+        <v>4</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H46" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>1</v>
+      </c>
+      <c r="B47" s="12">
+        <v>3</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="13">
+        <v>4</v>
+      </c>
+      <c r="E47" s="13">
+        <v>4</v>
+      </c>
+      <c r="F47" t="s">
+        <v>246</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>1</v>
+      </c>
+      <c r="B48" s="12">
+        <v>3</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="13">
+        <v>4</v>
+      </c>
+      <c r="E48" s="13">
+        <v>4</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" s="13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>1</v>
+      </c>
+      <c r="B49" s="12">
+        <v>3</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="13">
+        <v>4</v>
+      </c>
+      <c r="E49" s="13">
+        <v>4</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H49" s="13">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2694,9 +4985,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2739,25 +5030,25 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <v>2</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2765,25 +5056,25 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2791,25 +5082,25 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="8">
         <v>10</v>
       </c>
     </row>
@@ -2817,25 +5108,25 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>2</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="8">
         <v>8</v>
       </c>
     </row>
@@ -2843,357 +5134,1197 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="4">
+        <v>30</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" s="7">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
+        <v>4</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="7">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="4">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4">
+        <v>4</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="7">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
+        <v>4</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="B17" s="8">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="4">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4">
+        <v>4</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H17" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" s="7">
+        <v>1</v>
+      </c>
+      <c r="B18" s="8">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="4">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="4">
+        <v>12</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="7">
+        <v>1</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="A20" s="7">
+        <v>1</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11">
+        <v>2</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="A22" s="7">
+        <v>1</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11">
+        <v>2</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="10">
+        <v>2</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="11">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11">
+        <v>2</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="11">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11">
+        <v>2</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="4">
+        <v>2</v>
+      </c>
+      <c r="E25" s="4">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="10">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2</v>
+      </c>
+      <c r="E26" s="4">
+        <v>4</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4">
+        <v>4</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="4">
+        <v>30</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4">
+        <v>4</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="4">
+        <v>3</v>
+      </c>
+      <c r="E29" s="4">
+        <v>4</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="10">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="4">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="4">
+        <v>8</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="A31" s="7">
+        <v>1</v>
+      </c>
+      <c r="B31" s="10">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="4">
+        <v>3</v>
+      </c>
+      <c r="E31" s="4">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="4">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="10">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="4">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4">
+        <v>4</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H32" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="A33" s="7">
+        <v>1</v>
+      </c>
+      <c r="B33" s="10">
+        <v>2</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="4">
+        <v>4</v>
+      </c>
+      <c r="E33" s="4">
+        <v>4</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="10">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="4">
+        <v>4</v>
+      </c>
+      <c r="E34" s="4">
+        <v>4</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="7">
+        <v>1</v>
+      </c>
+      <c r="B35" s="10">
+        <v>2</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="4">
+        <v>4</v>
+      </c>
+      <c r="E35" s="4">
+        <v>4</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H35" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="A36" s="7">
+        <v>1</v>
+      </c>
+      <c r="B36" s="10">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="4">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4">
+        <v>4</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="A37" s="7">
+        <v>1</v>
+      </c>
+      <c r="B37" s="12">
+        <v>3</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="13">
+        <v>2</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="A38" s="7">
+        <v>1</v>
+      </c>
+      <c r="B38" s="12">
+        <v>3</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="13">
+        <v>1</v>
+      </c>
+      <c r="E38" s="13">
+        <v>2</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="A39" s="7">
+        <v>1</v>
+      </c>
+      <c r="B39" s="12">
+        <v>3</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="13">
+        <v>1</v>
+      </c>
+      <c r="E39" s="13">
+        <v>2</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>1</v>
+      </c>
+      <c r="B40" s="12">
+        <v>3</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="13">
+        <v>1</v>
+      </c>
+      <c r="E40" s="13">
+        <v>2</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>1</v>
+      </c>
+      <c r="B41" s="12">
+        <v>3</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="13">
+        <v>1</v>
+      </c>
+      <c r="E41" s="13">
+        <v>2</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H41" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>1</v>
+      </c>
+      <c r="B42" s="12">
+        <v>3</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="13">
+        <v>1</v>
+      </c>
+      <c r="E42" s="13">
+        <v>2</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="12">
+        <v>3</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="13">
+        <v>2</v>
+      </c>
+      <c r="E43" s="13">
+        <v>6</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H43" s="12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>1</v>
+      </c>
+      <c r="B44" s="12">
+        <v>3</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="13">
+        <v>2</v>
+      </c>
+      <c r="E44" s="13">
+        <v>6</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>1</v>
+      </c>
+      <c r="B45" s="12">
+        <v>3</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="13">
+        <v>2</v>
+      </c>
+      <c r="E45" s="13">
+        <v>6</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>1</v>
+      </c>
+      <c r="B46" s="12">
+        <v>3</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="13">
+        <v>2</v>
+      </c>
+      <c r="E46" s="13">
+        <v>6</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>1</v>
+      </c>
+      <c r="B47" s="12">
+        <v>3</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="13">
+        <v>2</v>
+      </c>
+      <c r="E47" s="13">
+        <v>6</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>1</v>
+      </c>
+      <c r="B48" s="12">
+        <v>3</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" s="13">
+        <v>2</v>
+      </c>
+      <c r="E48" s="13">
+        <v>6</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>1</v>
+      </c>
+      <c r="B49" s="12">
+        <v>3</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" s="13">
+        <v>2</v>
+      </c>
+      <c r="E49" s="13">
+        <v>6</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H49">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>1</v>
+      </c>
+      <c r="B50" s="12">
+        <v>3</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="13">
+        <v>2</v>
+      </c>
+      <c r="E50" s="13">
+        <v>6</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>1</v>
+      </c>
+      <c r="B51" s="12">
+        <v>3</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" s="13">
+        <v>2</v>
+      </c>
+      <c r="E51" s="13">
+        <v>6</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3205,7 +6336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3716,7 +6847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4215,7 +7346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4714,7 +7845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5213,7 +8344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5836,6 +8967,1139 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F357C59-977B-4591-AD82-2B7621F6CA1A}">
+  <dimension ref="A1:H45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
+        <v>2</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
+        <v>2</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="7">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="7">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="7">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="7">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>1</v>
+      </c>
+      <c r="B14" s="7">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>1</v>
+      </c>
+      <c r="B16" s="7">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4">
+        <v>4</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
+        <v>4</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="4">
+        <v>3</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>1</v>
+      </c>
+      <c r="B31" s="4">
+        <v>3</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4">
+        <v>3</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4">
+        <v>3</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="7">
+        <v>1</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H33" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4">
+        <v>3</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="7">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4">
+        <v>3</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="7">
+        <v>1</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H35" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4">
+        <v>3</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4">
+        <v>3</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4">
+        <v>3</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4">
+        <v>4</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H38" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4">
+        <v>4</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4">
+        <v>3</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4">
+        <v>4</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4">
+        <v>3</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="4">
+        <v>3</v>
+      </c>
+      <c r="E41" s="4">
+        <v>4</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4">
+        <v>3</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="4">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4">
+        <v>4</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4">
+        <v>3</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="4">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4">
+        <v>4</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4">
+        <v>3</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="4">
+        <v>4</v>
+      </c>
+      <c r="E44" s="4">
+        <v>4</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4">
+        <v>3</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="4">
+        <v>4</v>
+      </c>
+      <c r="E45" s="4">
+        <v>4</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="4">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C45" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
+      <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6978,7 +11242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7168,7 +11432,7 @@
         <v>52</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -7190,7 +11454,7 @@
         <v>52</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -7234,7 +11498,7 @@
         <v>53</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -7324,7 +11588,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>63</v>
@@ -7376,7 +11640,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>63</v>
@@ -7424,11 +11688,11 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -7448,7 +11712,7 @@
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -7464,11 +11728,11 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -7488,7 +11752,7 @@
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -7504,7 +11768,7 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
@@ -7528,7 +11792,7 @@
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -7626,7 +11890,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>53</v>
@@ -7652,7 +11916,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>54</v>
@@ -7684,7 +11948,7 @@
         <v>53</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>131</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -7704,7 +11968,7 @@
         <v>4</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>52</v>
@@ -7834,7 +12098,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>53</v>
@@ -7860,7 +12124,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>52</v>
@@ -7925,7 +12189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8115,7 +12379,7 @@
         <v>52</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -8131,7 +12395,7 @@
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>52</v>
@@ -8157,7 +12421,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>52</v>
@@ -8183,13 +12447,13 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -8205,13 +12469,13 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -8231,13 +12495,13 @@
         <v>4</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -8283,13 +12547,13 @@
         <v>4</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -8390,7 +12654,7 @@
         <v>49</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H18" s="4">
         <v>6</v>
@@ -8413,7 +12677,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>78</v>
@@ -8435,13 +12699,13 @@
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>78</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -8457,13 +12721,13 @@
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>78</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -8482,10 +12746,10 @@
         <v>59</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -8508,7 +12772,7 @@
         <v>62</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H23" s="4">
         <v>10</v>
@@ -8534,7 +12798,7 @@
         <v>49</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H24" s="4">
         <v>7</v>
@@ -8563,7 +12827,7 @@
         <v>78</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -8583,7 +12847,7 @@
         <v>4</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>78</v>
@@ -8661,7 +12925,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>52</v>
@@ -8687,7 +12951,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>63</v>
@@ -8741,7 +13005,7 @@
         <v>63</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -8757,13 +13021,13 @@
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>63</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -8785,7 +13049,7 @@
         <v>63</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -8811,7 +13075,7 @@
         <v>52</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -8831,7 +13095,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>52</v>
@@ -8883,7 +13147,7 @@
         <v>3</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>63</v>
@@ -9016,7 +13280,7 @@
         <v>98</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H43" s="4">
         <v>8</v>
@@ -9039,10 +13303,10 @@
         <v>2</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H44" s="4">
         <v>8</v>
@@ -9088,7 +13352,7 @@
         <v>114</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H46" t="s">
         <v>44</v>
@@ -9108,10 +13372,10 @@
         <v>108</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H47" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -9125,7 +13389,7 @@
         <v>34</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>52</v>
@@ -9151,7 +13415,7 @@
         <v>3</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>63</v>
@@ -9180,7 +13444,7 @@
         <v>105</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H50">
         <v>10</v>
@@ -9203,13 +13467,13 @@
         <v>3</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H51" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -9229,13 +13493,13 @@
         <v>3</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H52" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -9284,7 +13548,7 @@
         <v>61</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H54">
         <v>10</v>
@@ -9300,7 +13564,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9436,7 +13700,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>52</v>
@@ -9490,7 +13754,7 @@
         <v>52</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9512,7 +13776,7 @@
         <v>52</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -9534,7 +13798,7 @@
         <v>53</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -9550,13 +13814,13 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -9572,13 +13836,13 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>53</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -9594,13 +13858,13 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>53</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -9620,7 +13884,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>54</v>
@@ -9646,7 +13910,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>54</v>
@@ -9698,7 +13962,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>51</v>
@@ -9776,7 +14040,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>63</v>
@@ -9802,7 +14066,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>78</v>
@@ -9846,13 +14110,13 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>78</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -9868,7 +14132,7 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>63</v>
@@ -9890,7 +14154,7 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>78</v>
@@ -9912,13 +14176,13 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>78</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -9934,13 +14198,13 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>78</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -9960,7 +14224,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>51</v>
@@ -10038,7 +14302,7 @@
         <v>2</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>63</v>
@@ -10064,7 +14328,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>53</v>
@@ -10090,7 +14354,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>52</v>
@@ -10122,7 +14386,7 @@
         <v>78</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -10168,7 +14432,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>52</v>
@@ -10194,7 +14458,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>53</v>
@@ -10220,7 +14484,7 @@
         <v>3</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>54</v>
@@ -10272,7 +14536,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>53</v>
@@ -10298,7 +14562,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>54</v>
@@ -10317,7 +14581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10531,7 +14795,7 @@
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -10547,11 +14811,11 @@
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -10567,11 +14831,11 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -10587,11 +14851,11 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -10607,11 +14871,11 @@
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -10887,7 +15151,7 @@
         <v>63</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -10903,13 +15167,13 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>63</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -10925,13 +15189,13 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>52</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -10953,7 +15217,7 @@
         <v>78</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -10969,13 +15233,13 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>78</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -10991,7 +15255,7 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>78</v>
@@ -11017,7 +15281,7 @@
         <v>3</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>54</v>
@@ -11043,7 +15307,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>54</v>
@@ -11247,7 +15511,7 @@
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>53</v>
@@ -11269,13 +15533,13 @@
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>53</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -11289,13 +15553,13 @@
         <v>34</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>53</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -11309,7 +15573,7 @@
         <v>34</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>78</v>
@@ -11335,7 +15599,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>52</v>
@@ -11361,7 +15625,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>78</v>
@@ -11387,7 +15651,7 @@
         <v>3</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>63</v>
@@ -11413,7 +15677,7 @@
         <v>3</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>53</v>
@@ -11432,7 +15696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11477,359 +15741,699 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>33</v>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>37</v>
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>37</v>
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>43</v>
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
+        <v>1</v>
+      </c>
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="A14" s="7">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="F14" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="7">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="7">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="B17" s="8">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" s="7">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="7">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="A20" s="7">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="A22" s="7">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
@@ -11929,503 +16533,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>1</v>
-      </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C300" xr:uid="{00000000-0002-0000-0700-000000000000}">
-      <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45483B66-ECBF-4CCA-900B-63503DB0C757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE984B7-6242-4F44-8DCD-01E8599121C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="259">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -779,6 +779,42 @@
   </si>
   <si>
     <t>Abductores con tobilleras</t>
+  </si>
+  <si>
+    <t>Hang power Clean</t>
+  </si>
+  <si>
+    <t>Back Lunges jump</t>
+  </si>
+  <si>
+    <t>Knees jump + salto valla</t>
+  </si>
+  <si>
+    <t>Box jump + salto 2 vallas + broad jump</t>
+  </si>
+  <si>
+    <t>Single leg dead lift to box step up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box jump </t>
+  </si>
+  <si>
+    <t>Escalera coordinacion</t>
+  </si>
+  <si>
+    <t>Deck Squats</t>
+  </si>
+  <si>
+    <t>2 idas y vueltas</t>
+  </si>
+  <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>Back squats Jump</t>
+  </si>
+  <si>
+    <t>Sumo dead lift</t>
   </si>
 </sst>
 </file>
@@ -6849,7 +6885,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -6892,449 +6928,1147 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>33</v>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>37</v>
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>37</v>
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>43</v>
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H5" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>44</v>
+        <v>1</v>
+      </c>
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="F10" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" s="7">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="7">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="7">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="4">
+        <v>14</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10">
+        <v>2</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" s="7">
+        <v>1</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11">
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="7">
+        <v>1</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="A20" s="7">
+        <v>1</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11">
+        <v>2</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="10">
+        <v>20</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="A22" s="7">
+        <v>1</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11">
+        <v>2</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="10">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="10">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="4">
+        <v>4</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
+        <v>4</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="4">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="10">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2</v>
+      </c>
+      <c r="E30" s="4">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="A31" s="7">
+        <v>1</v>
+      </c>
+      <c r="B31" s="10">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4">
+        <v>4</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="4">
+        <v>40</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="10">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4">
+        <v>4</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="A33" s="7">
+        <v>1</v>
+      </c>
+      <c r="B33" s="12">
+        <v>3</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
+        <v>2</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="12">
+        <v>3</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="13">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13">
+        <v>2</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="7">
+        <v>1</v>
+      </c>
+      <c r="B35" s="12">
+        <v>3</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="13">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13">
+        <v>2</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="12">
+        <v>7</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="A36" s="7">
+        <v>1</v>
+      </c>
+      <c r="B36" s="12">
+        <v>3</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13">
+        <v>2</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H36" s="12">
+        <v>8</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="A37" s="7">
+        <v>1</v>
+      </c>
+      <c r="B37" s="12">
+        <v>3</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="13">
+        <v>2</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" s="12">
+        <v>20</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="A38" s="7">
+        <v>1</v>
+      </c>
+      <c r="B38" s="12">
+        <v>3</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="13">
+        <v>1</v>
+      </c>
+      <c r="E38" s="13">
+        <v>2</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H38" s="12">
+        <v>10</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
+      <c r="A39" s="7">
+        <v>1</v>
+      </c>
+      <c r="B39" s="12">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="F39" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>1</v>
+      </c>
+      <c r="B40" s="12">
+        <v>3</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2</v>
+      </c>
+      <c r="E40" s="13">
+        <v>4</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H40" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>1</v>
+      </c>
+      <c r="B41" s="12">
+        <v>3</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="13">
+        <v>2</v>
+      </c>
+      <c r="E41" s="13">
+        <v>4</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H41" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>1</v>
+      </c>
+      <c r="B42" s="12">
+        <v>3</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="13">
+        <v>2</v>
+      </c>
+      <c r="E42" s="13">
+        <v>4</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="12">
+        <v>3</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="13">
+        <v>3</v>
+      </c>
+      <c r="E43" s="13">
+        <v>4</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H43" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>1</v>
+      </c>
+      <c r="B44" s="12">
+        <v>3</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="13">
+        <v>3</v>
+      </c>
+      <c r="E44" s="13">
+        <v>4</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H44" s="12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>1</v>
+      </c>
+      <c r="B45" s="12">
+        <v>3</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="13">
+        <v>3</v>
+      </c>
+      <c r="E45" s="13">
+        <v>4</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>1</v>
+      </c>
+      <c r="B46" s="12">
+        <v>3</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="13">
+        <v>4</v>
+      </c>
+      <c r="E46" s="13">
+        <v>3</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>1</v>
+      </c>
+      <c r="B47" s="12">
+        <v>3</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="13">
+        <v>4</v>
+      </c>
+      <c r="E47" s="13">
+        <v>3</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE984B7-6242-4F44-8DCD-01E8599121C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\APP PROFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117B89BC-0A48-4CB2-8ECC-E86A9DF1916F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F39286-A7F9-4AB2-B742-83DCEE650949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3534" uniqueCount="314">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -13739,7 +13739,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F357C59-977B-4591-AD82-2B7621F6CA1A}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14860,9 +14860,1023 @@
         <v>20</v>
       </c>
     </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="17">
+        <v>2</v>
+      </c>
+      <c r="B46" s="20">
+        <v>1</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="20">
+        <v>1</v>
+      </c>
+      <c r="E46" s="20">
+        <v>2</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G46" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="17">
+        <v>2</v>
+      </c>
+      <c r="B47" s="20">
+        <v>1</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D47" s="20">
+        <v>1</v>
+      </c>
+      <c r="E47" s="20">
+        <v>2</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H47" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="17">
+        <v>2</v>
+      </c>
+      <c r="B48" s="20">
+        <v>1</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="20">
+        <v>1</v>
+      </c>
+      <c r="E48" s="20">
+        <v>2</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H48" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
+        <v>2</v>
+      </c>
+      <c r="B49" s="20">
+        <v>1</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="20">
+        <v>1</v>
+      </c>
+      <c r="E49" s="20">
+        <v>2</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H49" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
+        <v>2</v>
+      </c>
+      <c r="B50" s="20">
+        <v>1</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="20">
+        <v>1</v>
+      </c>
+      <c r="E50" s="20">
+        <v>2</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H50" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
+        <v>2</v>
+      </c>
+      <c r="B51" s="17">
+        <v>1</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
+        <v>2</v>
+      </c>
+      <c r="B52" s="17">
+        <v>1</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="17">
+        <v>2</v>
+      </c>
+      <c r="B53" s="17">
+        <v>1</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="17">
+        <v>2</v>
+      </c>
+      <c r="B54" s="17">
+        <v>1</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="17">
+        <v>2</v>
+      </c>
+      <c r="B55" s="17">
+        <v>1</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="17">
+        <v>2</v>
+      </c>
+      <c r="B56" s="17">
+        <v>1</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G56" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H56" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="17">
+        <v>2</v>
+      </c>
+      <c r="B57" s="17">
+        <v>1</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D57" s="18">
+        <v>2</v>
+      </c>
+      <c r="E57" s="18">
+        <v>3</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="17">
+        <v>2</v>
+      </c>
+      <c r="B58" s="17">
+        <v>1</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="18">
+        <v>2</v>
+      </c>
+      <c r="E58" s="18">
+        <v>3</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G58" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="17">
+        <v>2</v>
+      </c>
+      <c r="B59" s="17">
+        <v>1</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59" s="18">
+        <v>2</v>
+      </c>
+      <c r="E59" s="18">
+        <v>3</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="17">
+        <v>2</v>
+      </c>
+      <c r="B60" s="21">
+        <v>2</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" s="22">
+        <v>1</v>
+      </c>
+      <c r="E60" s="22">
+        <v>2</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H60" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="17">
+        <v>2</v>
+      </c>
+      <c r="B61" s="21">
+        <v>2</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="22">
+        <v>1</v>
+      </c>
+      <c r="E61" s="22">
+        <v>2</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G61" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H61" s="22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="17">
+        <v>2</v>
+      </c>
+      <c r="B62" s="21">
+        <v>2</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" s="22">
+        <v>1</v>
+      </c>
+      <c r="E62" s="22">
+        <v>2</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G62" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H62" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="17">
+        <v>2</v>
+      </c>
+      <c r="B63" s="21">
+        <v>2</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="22">
+        <v>1</v>
+      </c>
+      <c r="E63" s="22">
+        <v>2</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="17">
+        <v>2</v>
+      </c>
+      <c r="B64" s="21">
+        <v>2</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="22">
+        <v>1</v>
+      </c>
+      <c r="E64" s="22">
+        <v>2</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G64" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H64" s="22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="17">
+        <v>2</v>
+      </c>
+      <c r="B65" s="18">
+        <v>2</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="17">
+        <v>2</v>
+      </c>
+      <c r="B66" s="18">
+        <v>2</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="17">
+        <v>2</v>
+      </c>
+      <c r="B67" s="18">
+        <v>2</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="18"/>
+      <c r="E67" s="18"/>
+      <c r="F67" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G67" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="17">
+        <v>2</v>
+      </c>
+      <c r="B68" s="18">
+        <v>2</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="17">
+        <v>2</v>
+      </c>
+      <c r="B69" s="18">
+        <v>2</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G69" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H69" s="18" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="17">
+        <v>2</v>
+      </c>
+      <c r="B70" s="18">
+        <v>2</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="18">
+        <v>2</v>
+      </c>
+      <c r="E70" s="18">
+        <v>4</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H70" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="17">
+        <v>2</v>
+      </c>
+      <c r="B71" s="18">
+        <v>2</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="18">
+        <v>2</v>
+      </c>
+      <c r="E71" s="18">
+        <v>4</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H71" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="17">
+        <v>2</v>
+      </c>
+      <c r="B72" s="23">
+        <v>3</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="24">
+        <v>1</v>
+      </c>
+      <c r="E72" s="24">
+        <v>2</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H72" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="17">
+        <v>2</v>
+      </c>
+      <c r="B73" s="23">
+        <v>3</v>
+      </c>
+      <c r="C73" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="24">
+        <v>1</v>
+      </c>
+      <c r="E73" s="24">
+        <v>2</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G73" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H73" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="17">
+        <v>2</v>
+      </c>
+      <c r="B74" s="23">
+        <v>3</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="24">
+        <v>1</v>
+      </c>
+      <c r="E74" s="24">
+        <v>2</v>
+      </c>
+      <c r="F74" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G74" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="17">
+        <v>2</v>
+      </c>
+      <c r="B75" s="23">
+        <v>3</v>
+      </c>
+      <c r="C75" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="24">
+        <v>1</v>
+      </c>
+      <c r="E75" s="24">
+        <v>2</v>
+      </c>
+      <c r="F75" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G75" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H75" s="23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="17">
+        <v>2</v>
+      </c>
+      <c r="B76" s="23">
+        <v>3</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="24">
+        <v>1</v>
+      </c>
+      <c r="E76" s="24">
+        <v>2</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="H76" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="17">
+        <v>2</v>
+      </c>
+      <c r="B77" s="18">
+        <v>3</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H77" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="17">
+        <v>2</v>
+      </c>
+      <c r="B78" s="18">
+        <v>3</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="17">
+        <v>2</v>
+      </c>
+      <c r="B79" s="18">
+        <v>3</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="18">
+        <v>2</v>
+      </c>
+      <c r="E79" s="18">
+        <v>4</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G79" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H79" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="17">
+        <v>2</v>
+      </c>
+      <c r="B80" s="18">
+        <v>3</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="18">
+        <v>2</v>
+      </c>
+      <c r="E80" s="18">
+        <v>4</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G80" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H80" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="17">
+        <v>2</v>
+      </c>
+      <c r="B81" s="18">
+        <v>3</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" s="18">
+        <v>2</v>
+      </c>
+      <c r="E81" s="18">
+        <v>4</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H81" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="17">
+        <v>2</v>
+      </c>
+      <c r="B82" s="18">
+        <v>3</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="18">
+        <v>3</v>
+      </c>
+      <c r="E82" s="18">
+        <v>4</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H82" s="18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="17">
+        <v>2</v>
+      </c>
+      <c r="B83" s="18">
+        <v>3</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="18">
+        <v>3</v>
+      </c>
+      <c r="E83" s="18">
+        <v>4</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="17">
+        <v>2</v>
+      </c>
+      <c r="B84" s="18">
+        <v>3</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="18">
+        <v>3</v>
+      </c>
+      <c r="E84" s="18">
+        <v>4</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H84" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="17">
+        <v>2</v>
+      </c>
+      <c r="B85" s="18">
+        <v>3</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="18">
+        <v>4</v>
+      </c>
+      <c r="E85" s="18">
+        <v>4</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H85" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="17">
+        <v>2</v>
+      </c>
+      <c r="B86" s="18">
+        <v>3</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D86" s="18">
+        <v>4</v>
+      </c>
+      <c r="E86" s="18">
+        <v>4</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G86" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H86" s="18" t="s">
+        <v>282</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C45" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C86" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\APP PROFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F39286-A7F9-4AB2-B742-83DCEE650949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E65EE5-6668-4A78-A047-47B06C6147B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3534" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="319">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -980,6 +980,21 @@
   </si>
   <si>
     <t>Goblet lunges</t>
+  </si>
+  <si>
+    <t>3x5 cada pierna</t>
+  </si>
+  <si>
+    <t>Box step up con carga</t>
+  </si>
+  <si>
+    <t>Plank lateral + abduccion</t>
+  </si>
+  <si>
+    <t>Elevacion de gemelos de pie unilat</t>
+  </si>
+  <si>
+    <t>Push ups declinado</t>
   </si>
 </sst>
 </file>
@@ -10411,7 +10426,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -10454,25 +10469,25 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <v>2</v>
-      </c>
-      <c r="F2" s="7" t="s">
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8">
+        <v>2</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -10480,25 +10495,25 @@
       <c r="A3" s="7">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="B3" s="8">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>55</v>
       </c>
     </row>
@@ -10506,25 +10521,25 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="8">
         <v>10</v>
       </c>
     </row>
@@ -10532,25 +10547,25 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>2</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="B5" s="8">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="8">
         <v>8</v>
       </c>
     </row>
@@ -10558,357 +10573,1045 @@
       <c r="A6" s="7">
         <v>1</v>
       </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="B6" s="8">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>2</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" s="7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>2</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="A8" s="7">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="F8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="7">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="7">
+        <v>1</v>
+      </c>
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="7">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="7">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="A13" s="7">
+        <v>1</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" s="7">
+        <v>1</v>
+      </c>
+      <c r="B14" s="8">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="4">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="7">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
+        <v>3</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" s="7">
+        <v>1</v>
+      </c>
+      <c r="B16" s="8">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" s="7">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10">
+        <v>2</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <v>2</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" s="7">
+        <v>1</v>
+      </c>
+      <c r="B18" s="10">
+        <v>2</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="11">
+        <v>1</v>
+      </c>
+      <c r="E18" s="11">
+        <v>2</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" s="7">
+        <v>1</v>
+      </c>
+      <c r="B19" s="10">
+        <v>2</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="A20" s="7">
+        <v>1</v>
+      </c>
+      <c r="B20" s="10">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11">
+        <v>2</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="A21" s="7">
+        <v>1</v>
+      </c>
+      <c r="B21" s="10">
+        <v>2</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11">
+        <v>2</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="10">
+        <v>10</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="A22" s="7">
+        <v>1</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11">
+        <v>2</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
+      <c r="A23" s="7">
+        <v>1</v>
+      </c>
+      <c r="B23" s="10">
+        <v>2</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="F23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="10">
+        <v>2</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="F24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
+      <c r="A25" s="7">
+        <v>1</v>
+      </c>
+      <c r="B25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="F25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
+      <c r="A26" s="7">
+        <v>1</v>
+      </c>
+      <c r="B26" s="10">
+        <v>2</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="F26" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="A27" s="7">
+        <v>1</v>
+      </c>
+      <c r="B27" s="10">
+        <v>2</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="F27" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="A28" s="7">
+        <v>1</v>
+      </c>
+      <c r="B28" s="10">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="F28" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" s="7">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" s="7">
+        <v>1</v>
+      </c>
+      <c r="B30" s="10">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="4">
+        <v>2</v>
+      </c>
+      <c r="E30" s="4">
+        <v>3</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="A31" s="7">
+        <v>1</v>
+      </c>
+      <c r="B31" s="10">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4">
+        <v>3</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="4">
+        <v>20</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="A32" s="7">
+        <v>1</v>
+      </c>
+      <c r="B32" s="12">
+        <v>3</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="13">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13">
+        <v>2</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H32" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="A33" s="7">
+        <v>1</v>
+      </c>
+      <c r="B33" s="12">
+        <v>3</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="13">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
+        <v>2</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="12">
+        <v>3</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" s="13">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13">
+        <v>2</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="12">
+        <v>7</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" s="7">
+        <v>1</v>
+      </c>
+      <c r="B35" s="12">
+        <v>3</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="13">
+        <v>1</v>
+      </c>
+      <c r="E35" s="13">
+        <v>2</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" s="12">
+        <v>8</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="A36" s="7">
+        <v>1</v>
+      </c>
+      <c r="B36" s="12">
+        <v>3</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13">
+        <v>2</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H36" s="12">
+        <v>8</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="A37" s="7">
+        <v>1</v>
+      </c>
+      <c r="B37" s="12">
+        <v>3</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="13">
+        <v>2</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" s="12">
+        <v>10</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="A38" s="7">
+        <v>1</v>
+      </c>
+      <c r="B38" s="12">
+        <v>3</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="4">
+        <v>2</v>
+      </c>
+      <c r="E38" s="4">
+        <v>4</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="A39" s="7">
+        <v>1</v>
+      </c>
+      <c r="B39" s="12">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2</v>
+      </c>
+      <c r="E39" s="4">
+        <v>4</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>1</v>
+      </c>
+      <c r="B40" s="12">
+        <v>3</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="13">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4">
+        <v>4</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40" s="12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>1</v>
+      </c>
+      <c r="B41" s="12">
+        <v>3</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="13">
+        <v>3</v>
+      </c>
+      <c r="E41" s="4">
+        <v>4</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>1</v>
+      </c>
+      <c r="B42" s="12">
+        <v>3</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="13">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4">
+        <v>4</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>1</v>
+      </c>
+      <c r="B43" s="12">
+        <v>3</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="13">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4">
+        <v>4</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>1</v>
+      </c>
+      <c r="B44" s="12">
+        <v>3</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="13">
+        <v>4</v>
+      </c>
+      <c r="E44" s="4">
+        <v>4</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>1</v>
+      </c>
+      <c r="B45" s="12">
+        <v>3</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="13">
+        <v>4</v>
+      </c>
+      <c r="E45" s="4">
+        <v>4</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H45" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>1</v>
+      </c>
+      <c r="B46" s="12">
+        <v>3</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="13">
+        <v>4</v>
+      </c>
+      <c r="E46" s="4">
+        <v>4</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>1</v>
+      </c>
+      <c r="B47" s="12">
+        <v>3</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="13">
+        <v>4</v>
+      </c>
+      <c r="E47" s="4">
+        <v>4</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -13739,7 +14442,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F357C59-977B-4591-AD82-2B7621F6CA1A}">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -14860,1023 +15563,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="17">
-        <v>2</v>
-      </c>
-      <c r="B46" s="20">
-        <v>1</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="20">
-        <v>1</v>
-      </c>
-      <c r="E46" s="20">
-        <v>2</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="G46" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H46" s="20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="17">
-        <v>2</v>
-      </c>
-      <c r="B47" s="20">
-        <v>1</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="20">
-        <v>1</v>
-      </c>
-      <c r="E47" s="20">
-        <v>2</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="17">
-        <v>2</v>
-      </c>
-      <c r="B48" s="20">
-        <v>1</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="20">
-        <v>1</v>
-      </c>
-      <c r="E48" s="20">
-        <v>2</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H48" s="20">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="17">
-        <v>2</v>
-      </c>
-      <c r="B49" s="20">
-        <v>1</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="20">
-        <v>1</v>
-      </c>
-      <c r="E49" s="20">
-        <v>2</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="H49" s="20">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="17">
-        <v>2</v>
-      </c>
-      <c r="B50" s="20">
-        <v>1</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="20">
-        <v>1</v>
-      </c>
-      <c r="E50" s="20">
-        <v>2</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H50" s="20">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="17">
-        <v>2</v>
-      </c>
-      <c r="B51" s="17">
-        <v>1</v>
-      </c>
-      <c r="C51" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G51" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="H51" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
-        <v>2</v>
-      </c>
-      <c r="B52" s="17">
-        <v>1</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="17">
-        <v>2</v>
-      </c>
-      <c r="B53" s="17">
-        <v>1</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G53" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H53" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
-        <v>2</v>
-      </c>
-      <c r="B54" s="17">
-        <v>1</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G54" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H54" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="17">
-        <v>2</v>
-      </c>
-      <c r="B55" s="17">
-        <v>1</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H55" s="18" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="17">
-        <v>2</v>
-      </c>
-      <c r="B56" s="17">
-        <v>1</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G56" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H56" s="18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="17">
-        <v>2</v>
-      </c>
-      <c r="B57" s="17">
-        <v>1</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" s="18">
-        <v>2</v>
-      </c>
-      <c r="E57" s="18">
-        <v>3</v>
-      </c>
-      <c r="F57" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H57" s="18" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="17">
-        <v>2</v>
-      </c>
-      <c r="B58" s="17">
-        <v>1</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" s="18">
-        <v>2</v>
-      </c>
-      <c r="E58" s="18">
-        <v>3</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H58" s="18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="17">
-        <v>2</v>
-      </c>
-      <c r="B59" s="17">
-        <v>1</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59" s="18">
-        <v>2</v>
-      </c>
-      <c r="E59" s="18">
-        <v>3</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="G59" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H59" s="18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="17">
-        <v>2</v>
-      </c>
-      <c r="B60" s="21">
-        <v>2</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D60" s="22">
-        <v>1</v>
-      </c>
-      <c r="E60" s="22">
-        <v>2</v>
-      </c>
-      <c r="F60" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H60" s="22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="17">
-        <v>2</v>
-      </c>
-      <c r="B61" s="21">
-        <v>2</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D61" s="22">
-        <v>1</v>
-      </c>
-      <c r="E61" s="22">
-        <v>2</v>
-      </c>
-      <c r="F61" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H61" s="22">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="17">
-        <v>2</v>
-      </c>
-      <c r="B62" s="21">
-        <v>2</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D62" s="22">
-        <v>1</v>
-      </c>
-      <c r="E62" s="22">
-        <v>2</v>
-      </c>
-      <c r="F62" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="G62" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H62" s="22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="17">
-        <v>2</v>
-      </c>
-      <c r="B63" s="21">
-        <v>2</v>
-      </c>
-      <c r="C63" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D63" s="22">
-        <v>1</v>
-      </c>
-      <c r="E63" s="22">
-        <v>2</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="G63" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="H63" s="22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="17">
-        <v>2</v>
-      </c>
-      <c r="B64" s="21">
-        <v>2</v>
-      </c>
-      <c r="C64" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D64" s="22">
-        <v>1</v>
-      </c>
-      <c r="E64" s="22">
-        <v>2</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="G64" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="H64" s="22">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="17">
-        <v>2</v>
-      </c>
-      <c r="B65" s="18">
-        <v>2</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G65" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="17">
-        <v>2</v>
-      </c>
-      <c r="B66" s="18">
-        <v>2</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="G66" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="17">
-        <v>2</v>
-      </c>
-      <c r="B67" s="18">
-        <v>2</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D67" s="18"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G67" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="H67" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="17">
-        <v>2</v>
-      </c>
-      <c r="B68" s="18">
-        <v>2</v>
-      </c>
-      <c r="C68" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D68" s="18"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="G68" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H68" s="18" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="17">
-        <v>2</v>
-      </c>
-      <c r="B69" s="18">
-        <v>2</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D69" s="18"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G69" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H69" s="18" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="17">
-        <v>2</v>
-      </c>
-      <c r="B70" s="18">
-        <v>2</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D70" s="18">
-        <v>2</v>
-      </c>
-      <c r="E70" s="18">
-        <v>4</v>
-      </c>
-      <c r="F70" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="G70" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H70" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="17">
-        <v>2</v>
-      </c>
-      <c r="B71" s="18">
-        <v>2</v>
-      </c>
-      <c r="C71" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D71" s="18">
-        <v>2</v>
-      </c>
-      <c r="E71" s="18">
-        <v>4</v>
-      </c>
-      <c r="F71" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="G71" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H71" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="17">
-        <v>2</v>
-      </c>
-      <c r="B72" s="23">
-        <v>3</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D72" s="24">
-        <v>1</v>
-      </c>
-      <c r="E72" s="24">
-        <v>2</v>
-      </c>
-      <c r="F72" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G72" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H72" s="23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="17">
-        <v>2</v>
-      </c>
-      <c r="B73" s="23">
-        <v>3</v>
-      </c>
-      <c r="C73" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D73" s="24">
-        <v>1</v>
-      </c>
-      <c r="E73" s="24">
-        <v>2</v>
-      </c>
-      <c r="F73" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="G73" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H73" s="23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="17">
-        <v>2</v>
-      </c>
-      <c r="B74" s="23">
-        <v>3</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D74" s="24">
-        <v>1</v>
-      </c>
-      <c r="E74" s="24">
-        <v>2</v>
-      </c>
-      <c r="F74" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="G74" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H74" s="23" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="17">
-        <v>2</v>
-      </c>
-      <c r="B75" s="23">
-        <v>3</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" s="24">
-        <v>1</v>
-      </c>
-      <c r="E75" s="24">
-        <v>2</v>
-      </c>
-      <c r="F75" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" s="23">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="17">
-        <v>2</v>
-      </c>
-      <c r="B76" s="23">
-        <v>3</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" s="24">
-        <v>1</v>
-      </c>
-      <c r="E76" s="24">
-        <v>2</v>
-      </c>
-      <c r="F76" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="G76" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="H76" s="23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="17">
-        <v>2</v>
-      </c>
-      <c r="B77" s="18">
-        <v>3</v>
-      </c>
-      <c r="C77" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="G77" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H77" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="17">
-        <v>2</v>
-      </c>
-      <c r="B78" s="18">
-        <v>3</v>
-      </c>
-      <c r="C78" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="G78" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H78" s="18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="17">
-        <v>2</v>
-      </c>
-      <c r="B79" s="18">
-        <v>3</v>
-      </c>
-      <c r="C79" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D79" s="18">
-        <v>2</v>
-      </c>
-      <c r="E79" s="18">
-        <v>4</v>
-      </c>
-      <c r="F79" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G79" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H79" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="17">
-        <v>2</v>
-      </c>
-      <c r="B80" s="18">
-        <v>3</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D80" s="18">
-        <v>2</v>
-      </c>
-      <c r="E80" s="18">
-        <v>4</v>
-      </c>
-      <c r="F80" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="G80" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H80" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="17">
-        <v>2</v>
-      </c>
-      <c r="B81" s="18">
-        <v>3</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D81" s="18">
-        <v>2</v>
-      </c>
-      <c r="E81" s="18">
-        <v>4</v>
-      </c>
-      <c r="F81" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="G81" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H81" s="18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="17">
-        <v>2</v>
-      </c>
-      <c r="B82" s="18">
-        <v>3</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D82" s="18">
-        <v>3</v>
-      </c>
-      <c r="E82" s="18">
-        <v>4</v>
-      </c>
-      <c r="F82" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="G82" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H82" s="18" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="17">
-        <v>2</v>
-      </c>
-      <c r="B83" s="18">
-        <v>3</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D83" s="18">
-        <v>3</v>
-      </c>
-      <c r="E83" s="18">
-        <v>4</v>
-      </c>
-      <c r="F83" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="G83" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H83" s="18">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="17">
-        <v>2</v>
-      </c>
-      <c r="B84" s="18">
-        <v>3</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D84" s="18">
-        <v>3</v>
-      </c>
-      <c r="E84" s="18">
-        <v>4</v>
-      </c>
-      <c r="F84" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="G84" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H84" s="18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="17">
-        <v>2</v>
-      </c>
-      <c r="B85" s="18">
-        <v>3</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D85" s="18">
-        <v>4</v>
-      </c>
-      <c r="E85" s="18">
-        <v>4</v>
-      </c>
-      <c r="F85" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="G85" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H85" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="17">
-        <v>2</v>
-      </c>
-      <c r="B86" s="18">
-        <v>3</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D86" s="18">
-        <v>4</v>
-      </c>
-      <c r="E86" s="18">
-        <v>4</v>
-      </c>
-      <c r="F86" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="G86" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H86" s="18" t="s">
-        <v>282</v>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C86" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C45" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E65EE5-6668-4A78-A047-47B06C6147B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511C9BE4-6635-4918-9E86-EA2E1A44B287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3705" uniqueCount="331">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -995,6 +995,42 @@
   </si>
   <si>
     <t>Push ups declinado</t>
+  </si>
+  <si>
+    <t>Stand up</t>
+  </si>
+  <si>
+    <t>Dead lift cabra liviano</t>
+  </si>
+  <si>
+    <t>Prisioneros</t>
+  </si>
+  <si>
+    <t>3 cada pierna</t>
+  </si>
+  <si>
+    <t>Combo box + vallas</t>
+  </si>
+  <si>
+    <t>4x3</t>
+  </si>
+  <si>
+    <t>Doble box jump desplazando</t>
+  </si>
+  <si>
+    <t>2 in 2 out en step</t>
+  </si>
+  <si>
+    <t>Salto lateral en valla</t>
+  </si>
+  <si>
+    <t>3x4 cada pierna</t>
+  </si>
+  <si>
+    <t>4 cada pierna</t>
+  </si>
+  <si>
+    <t>Bug dead en polea</t>
   </si>
 </sst>
 </file>
@@ -11625,7 +11661,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -12807,6 +12843,1170 @@
         <v>54</v>
       </c>
       <c r="H47" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="17">
+        <v>2</v>
+      </c>
+      <c r="B48" s="20">
+        <v>1</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="20">
+        <v>1</v>
+      </c>
+      <c r="E48" s="20">
+        <v>2</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G48" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
+        <v>2</v>
+      </c>
+      <c r="B49" s="20">
+        <v>1</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="20">
+        <v>1</v>
+      </c>
+      <c r="E49" s="20">
+        <v>2</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G49" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49" s="20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
+        <v>2</v>
+      </c>
+      <c r="B50" s="20">
+        <v>1</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="20">
+        <v>1</v>
+      </c>
+      <c r="E50" s="20">
+        <v>2</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H50" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
+        <v>2</v>
+      </c>
+      <c r="B51" s="20">
+        <v>1</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="20">
+        <v>1</v>
+      </c>
+      <c r="E51" s="20">
+        <v>2</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
+        <v>2</v>
+      </c>
+      <c r="B52" s="20">
+        <v>1</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="20">
+        <v>1</v>
+      </c>
+      <c r="E52" s="20">
+        <v>2</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="G52" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H52" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="17">
+        <v>2</v>
+      </c>
+      <c r="B53" s="17">
+        <v>1</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="17">
+        <v>1</v>
+      </c>
+      <c r="E53" s="17">
+        <v>2</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="17">
+        <v>2</v>
+      </c>
+      <c r="B54" s="17">
+        <v>1</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="17">
+        <v>2</v>
+      </c>
+      <c r="B55" s="17">
+        <v>1</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="17">
+        <v>2</v>
+      </c>
+      <c r="B56" s="17">
+        <v>1</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G56" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H56" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="17">
+        <v>2</v>
+      </c>
+      <c r="B57" s="17">
+        <v>1</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="17">
+        <v>2</v>
+      </c>
+      <c r="B58" s="17">
+        <v>1</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="18">
+        <v>2</v>
+      </c>
+      <c r="E58" s="18">
+        <v>3</v>
+      </c>
+      <c r="F58" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="G58" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="17">
+        <v>2</v>
+      </c>
+      <c r="B59" s="17">
+        <v>1</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="18">
+        <v>2</v>
+      </c>
+      <c r="E59" s="18">
+        <v>3</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="17">
+        <v>2</v>
+      </c>
+      <c r="B60" s="17">
+        <v>1</v>
+      </c>
+      <c r="C60" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="18">
+        <v>3</v>
+      </c>
+      <c r="E60" s="18">
+        <v>3</v>
+      </c>
+      <c r="F60" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="17">
+        <v>2</v>
+      </c>
+      <c r="B61" s="17">
+        <v>1</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" s="18">
+        <v>3</v>
+      </c>
+      <c r="E61" s="18">
+        <v>3</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="17">
+        <v>2</v>
+      </c>
+      <c r="B62" s="17">
+        <v>1</v>
+      </c>
+      <c r="C62" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62" s="18">
+        <v>3</v>
+      </c>
+      <c r="E62" s="18">
+        <v>3</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H62" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="17">
+        <v>2</v>
+      </c>
+      <c r="B63" s="21">
+        <v>2</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="22">
+        <v>1</v>
+      </c>
+      <c r="E63" s="22">
+        <v>2</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G63" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="17">
+        <v>2</v>
+      </c>
+      <c r="B64" s="21">
+        <v>2</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="22">
+        <v>1</v>
+      </c>
+      <c r="E64" s="22">
+        <v>2</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G64" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H64" s="22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="17">
+        <v>2</v>
+      </c>
+      <c r="B65" s="21">
+        <v>2</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" s="22">
+        <v>1</v>
+      </c>
+      <c r="E65" s="22">
+        <v>2</v>
+      </c>
+      <c r="F65" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H65" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="17">
+        <v>2</v>
+      </c>
+      <c r="B66" s="21">
+        <v>2</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66" s="22">
+        <v>1</v>
+      </c>
+      <c r="E66" s="22">
+        <v>2</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G66" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="17">
+        <v>2</v>
+      </c>
+      <c r="B67" s="21">
+        <v>2</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="22">
+        <v>1</v>
+      </c>
+      <c r="E67" s="22">
+        <v>2</v>
+      </c>
+      <c r="F67" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="G67" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H67" s="22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="17">
+        <v>2</v>
+      </c>
+      <c r="B68" s="18">
+        <v>2</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="17">
+        <v>1</v>
+      </c>
+      <c r="E68" s="17">
+        <v>2</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="17">
+        <v>2</v>
+      </c>
+      <c r="B69" s="18">
+        <v>2</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="G69" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H69" s="18" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="17">
+        <v>2</v>
+      </c>
+      <c r="B70" s="18">
+        <v>2</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D70" s="18">
+        <v>2</v>
+      </c>
+      <c r="E70" s="18">
+        <v>4</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H70" s="18" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="17">
+        <v>2</v>
+      </c>
+      <c r="B71" s="18">
+        <v>2</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D71" s="18">
+        <v>2</v>
+      </c>
+      <c r="E71" s="18">
+        <v>4</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="17">
+        <v>2</v>
+      </c>
+      <c r="B72" s="18">
+        <v>2</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="17">
+        <v>2</v>
+      </c>
+      <c r="B73" s="18">
+        <v>2</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H73" s="18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="17">
+        <v>2</v>
+      </c>
+      <c r="B74" s="18">
+        <v>2</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74" s="18">
+        <v>3</v>
+      </c>
+      <c r="E74" s="18">
+        <v>4</v>
+      </c>
+      <c r="F74" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H74" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="17">
+        <v>2</v>
+      </c>
+      <c r="B75" s="18">
+        <v>2</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D75" s="18">
+        <v>3</v>
+      </c>
+      <c r="E75" s="18">
+        <v>4</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="G75" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="17">
+        <v>2</v>
+      </c>
+      <c r="B76" s="18">
+        <v>2</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D76" s="18">
+        <v>3</v>
+      </c>
+      <c r="E76" s="18">
+        <v>4</v>
+      </c>
+      <c r="F76" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G76" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H76" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="17">
+        <v>2</v>
+      </c>
+      <c r="B77" s="18">
+        <v>2</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D77" s="18">
+        <v>3</v>
+      </c>
+      <c r="E77" s="18">
+        <v>4</v>
+      </c>
+      <c r="F77" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H77" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="17">
+        <v>2</v>
+      </c>
+      <c r="B78" s="18">
+        <v>2</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D78" s="18">
+        <v>3</v>
+      </c>
+      <c r="E78" s="18">
+        <v>4</v>
+      </c>
+      <c r="F78" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H78" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="17">
+        <v>2</v>
+      </c>
+      <c r="B79" s="23">
+        <v>3</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="24">
+        <v>1</v>
+      </c>
+      <c r="E79" s="24">
+        <v>2</v>
+      </c>
+      <c r="F79" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G79" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H79" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="17">
+        <v>2</v>
+      </c>
+      <c r="B80" s="23">
+        <v>3</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D80" s="24">
+        <v>1</v>
+      </c>
+      <c r="E80" s="24">
+        <v>2</v>
+      </c>
+      <c r="F80" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G80" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H80" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="17">
+        <v>2</v>
+      </c>
+      <c r="B81" s="23">
+        <v>3</v>
+      </c>
+      <c r="C81" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81" s="24">
+        <v>1</v>
+      </c>
+      <c r="E81" s="24">
+        <v>2</v>
+      </c>
+      <c r="F81" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G81" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H81" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="17">
+        <v>2</v>
+      </c>
+      <c r="B82" s="23">
+        <v>3</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82" s="24">
+        <v>1</v>
+      </c>
+      <c r="E82" s="24">
+        <v>2</v>
+      </c>
+      <c r="F82" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G82" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" s="23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="17">
+        <v>2</v>
+      </c>
+      <c r="B83" s="23">
+        <v>3</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="24">
+        <v>1</v>
+      </c>
+      <c r="E83" s="24">
+        <v>2</v>
+      </c>
+      <c r="F83" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G83" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="H83" s="23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="17">
+        <v>2</v>
+      </c>
+      <c r="B84" s="18">
+        <v>3</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" s="17">
+        <v>1</v>
+      </c>
+      <c r="E84" s="17">
+        <v>2</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="17">
+        <v>2</v>
+      </c>
+      <c r="B85" s="18">
+        <v>3</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="17">
+        <v>2</v>
+      </c>
+      <c r="B86" s="18">
+        <v>3</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D86" s="17">
+        <v>2</v>
+      </c>
+      <c r="E86" s="17">
+        <v>4</v>
+      </c>
+      <c r="F86" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G86" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H86" s="18" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="17">
+        <v>2</v>
+      </c>
+      <c r="B87" s="18">
+        <v>3</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D87" s="17">
+        <v>2</v>
+      </c>
+      <c r="E87" s="17">
+        <v>4</v>
+      </c>
+      <c r="F87" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G87" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="17">
+        <v>2</v>
+      </c>
+      <c r="B88" s="18">
+        <v>3</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D88" s="17">
+        <v>2</v>
+      </c>
+      <c r="E88" s="17">
+        <v>4</v>
+      </c>
+      <c r="F88" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G88" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H88" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="17">
+        <v>2</v>
+      </c>
+      <c r="B89" s="18">
+        <v>3</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="17">
+        <v>3</v>
+      </c>
+      <c r="E89" s="17">
+        <v>4</v>
+      </c>
+      <c r="F89" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="G89" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H89" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="17">
+        <v>2</v>
+      </c>
+      <c r="B90" s="18">
+        <v>3</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="17">
+        <v>3</v>
+      </c>
+      <c r="E90" s="17">
+        <v>4</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G90" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H90" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="17">
+        <v>2</v>
+      </c>
+      <c r="B91" s="18">
+        <v>3</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="17">
+        <v>3</v>
+      </c>
+      <c r="E91" s="17">
+        <v>4</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="G91" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H91" s="18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="17">
+        <v>2</v>
+      </c>
+      <c r="B92" s="18">
+        <v>3</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="17">
+        <v>4</v>
+      </c>
+      <c r="E92" s="17">
+        <v>3</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="G92" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H92" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="17">
+        <v>2</v>
+      </c>
+      <c r="B93" s="18">
+        <v>3</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="17">
+        <v>4</v>
+      </c>
+      <c r="E93" s="17">
+        <v>3</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="G93" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H93" s="17" t="s">
         <v>70</v>
       </c>
     </row>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FD1863-2D17-42A6-B2F5-0BC47B32D453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17206974-C8A2-4E3A-BE0D-405DFDDF742A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5279" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5591" uniqueCount="379">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -1134,6 +1134,48 @@
   <si>
     <t>Bear crawl</t>
   </si>
+  <si>
+    <t>5x5 (70% RM)</t>
+  </si>
+  <si>
+    <t>Curl de biceps con manc</t>
+  </si>
+  <si>
+    <t>(Bonus) Press frances unilat en polea</t>
+  </si>
+  <si>
+    <t>3x12 cada brazo</t>
+  </si>
+  <si>
+    <t>(Bonus) Curl biceps unilat en polea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3x12 cada brazo </t>
+  </si>
+  <si>
+    <t>Curl de biceps unilat en polea</t>
+  </si>
+  <si>
+    <t>Lunges lateral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row 45 con mancuernas  </t>
+  </si>
+  <si>
+    <t>Face pull</t>
+  </si>
+  <si>
+    <t>Intermitente metabolico</t>
+  </si>
+  <si>
+    <t>Distancia a recorrer 90/95 mts</t>
+  </si>
+  <si>
+    <t>20''x20''x5' x4 ROUNDS</t>
+  </si>
+  <si>
+    <t>Descanso entre rounds 2'</t>
+  </si>
 </sst>
 </file>
 
@@ -26760,7 +26802,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -27748,24 +27790,952 @@
       <c r="J37" s="15"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="A38" s="17">
+        <v>2</v>
+      </c>
+      <c r="B38" s="33">
+        <v>1</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="33">
+        <v>1</v>
+      </c>
+      <c r="E38" s="33">
+        <v>2</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="A39" s="17">
+        <v>2</v>
+      </c>
+      <c r="B39" s="33">
+        <v>1</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="33">
+        <v>1</v>
+      </c>
+      <c r="E39" s="33">
+        <v>2</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="17">
+        <v>2</v>
+      </c>
+      <c r="B40" s="33">
+        <v>1</v>
+      </c>
+      <c r="C40" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="33">
+        <v>1</v>
+      </c>
+      <c r="E40" s="33">
+        <v>2</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H40" s="33">
+        <v>10</v>
+      </c>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="17">
+        <v>2</v>
+      </c>
+      <c r="B41" s="33">
+        <v>1</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="33">
+        <v>1</v>
+      </c>
+      <c r="E41" s="33">
+        <v>2</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" s="33">
+        <v>8</v>
+      </c>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="17">
+        <v>2</v>
+      </c>
+      <c r="B42" s="33">
+        <v>1</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="33">
+        <v>1</v>
+      </c>
+      <c r="E42" s="33">
+        <v>2</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42" s="33">
+        <v>8</v>
+      </c>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="17">
+        <v>2</v>
+      </c>
+      <c r="B43" s="17">
+        <v>1</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
+        <v>2</v>
+      </c>
+      <c r="B44" s="17">
+        <v>1</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="17">
+        <v>2</v>
+      </c>
+      <c r="B45" s="17">
+        <v>1</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="17">
+        <v>2</v>
+      </c>
+      <c r="B46" s="17">
+        <v>1</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="17">
+        <v>2</v>
+      </c>
+      <c r="B47" s="17">
+        <v>1</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="17">
+        <v>2</v>
+      </c>
+      <c r="B48" s="17">
+        <v>1</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
+        <v>2</v>
+      </c>
+      <c r="B49" s="16">
+        <v>2</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>1</v>
+      </c>
+      <c r="E49" s="14">
+        <v>2</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H49" s="16">
+        <v>10</v>
+      </c>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
+        <v>2</v>
+      </c>
+      <c r="B50" s="16">
+        <v>2</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="14">
+        <v>1</v>
+      </c>
+      <c r="E50" s="14">
+        <v>2</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H50" s="16">
+        <v>10</v>
+      </c>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
+        <v>2</v>
+      </c>
+      <c r="B51" s="16">
+        <v>2</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="14">
+        <v>1</v>
+      </c>
+      <c r="E51" s="14">
+        <v>2</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
+        <v>2</v>
+      </c>
+      <c r="B52" s="16">
+        <v>2</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D52" s="14">
+        <v>1</v>
+      </c>
+      <c r="E52" s="14">
+        <v>2</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="17">
+        <v>2</v>
+      </c>
+      <c r="B53" s="16">
+        <v>2</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>1</v>
+      </c>
+      <c r="E53" s="14">
+        <v>2</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H53" s="16">
+        <v>10</v>
+      </c>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="17">
+        <v>2</v>
+      </c>
+      <c r="B54" s="18">
+        <v>2</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="17">
+        <v>2</v>
+      </c>
+      <c r="B55" s="18">
+        <v>2</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="17">
+        <v>2</v>
+      </c>
+      <c r="B56" s="18">
+        <v>2</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="17">
+        <v>2</v>
+      </c>
+      <c r="B57" s="18">
+        <v>2</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="17">
+        <v>2</v>
+      </c>
+      <c r="B58" s="18">
+        <v>2</v>
+      </c>
+      <c r="C58" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="17">
+        <v>2</v>
+      </c>
+      <c r="B59" s="18">
+        <v>2</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I59" s="19"/>
+      <c r="J59" s="19"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="17">
+        <v>2</v>
+      </c>
+      <c r="B60" s="18">
+        <v>3</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" s="17">
+        <v>1</v>
+      </c>
+      <c r="E60" s="17">
+        <v>2</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H60" s="18">
+        <v>10</v>
+      </c>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="17">
+        <v>2</v>
+      </c>
+      <c r="B61" s="18">
+        <v>3</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" s="17">
+        <v>1</v>
+      </c>
+      <c r="E61" s="17">
+        <v>2</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="17">
+        <v>2</v>
+      </c>
+      <c r="B62" s="18">
+        <v>3</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" s="17">
+        <v>1</v>
+      </c>
+      <c r="E62" s="17">
+        <v>2</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="17">
+        <v>2</v>
+      </c>
+      <c r="B63" s="18">
+        <v>3</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="17">
+        <v>1</v>
+      </c>
+      <c r="E63" s="17">
+        <v>2</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="17">
+        <v>2</v>
+      </c>
+      <c r="B64" s="18">
+        <v>3</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64" s="17">
+        <v>1</v>
+      </c>
+      <c r="E64" s="17">
+        <v>2</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H64" s="18">
+        <v>8</v>
+      </c>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="17">
+        <v>2</v>
+      </c>
+      <c r="B65" s="18">
+        <v>3</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="18">
+        <v>2</v>
+      </c>
+      <c r="E65" s="18">
+        <v>4</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G65" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="17">
+        <v>2</v>
+      </c>
+      <c r="B66" s="18">
+        <v>3</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="18">
+        <v>2</v>
+      </c>
+      <c r="E66" s="18">
+        <v>4</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="17">
+        <v>2</v>
+      </c>
+      <c r="B67" s="18">
+        <v>3</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="18">
+        <v>2</v>
+      </c>
+      <c r="E67" s="18">
+        <v>4</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="G67" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="17">
+        <v>2</v>
+      </c>
+      <c r="B68" s="18">
+        <v>3</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="18">
+        <v>3</v>
+      </c>
+      <c r="E68" s="18">
+        <v>3</v>
+      </c>
+      <c r="F68" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H68" s="18">
+        <v>8</v>
+      </c>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="17">
+        <v>2</v>
+      </c>
+      <c r="B69" s="18">
+        <v>3</v>
+      </c>
+      <c r="C69" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="18">
+        <v>3</v>
+      </c>
+      <c r="E69" s="18">
+        <v>3</v>
+      </c>
+      <c r="F69" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="G69" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H69" s="18">
+        <v>10</v>
+      </c>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="17">
+        <v>2</v>
+      </c>
+      <c r="B70" s="18">
+        <v>3</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D70" s="18">
+        <v>3</v>
+      </c>
+      <c r="E70" s="18">
+        <v>3</v>
+      </c>
+      <c r="F70" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="G70" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H70" s="18">
+        <v>14</v>
+      </c>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="17">
+        <v>2</v>
+      </c>
+      <c r="B71" s="18">
+        <v>3</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D71" s="18">
+        <v>4</v>
+      </c>
+      <c r="E71" s="18">
+        <v>3</v>
+      </c>
+      <c r="F71" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G71" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H71" s="18">
+        <v>10</v>
+      </c>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="17">
+        <v>2</v>
+      </c>
+      <c r="B72" s="18">
+        <v>3</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D72" s="18">
+        <v>4</v>
+      </c>
+      <c r="E72" s="18">
+        <v>3</v>
+      </c>
+      <c r="F72" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="G72" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="17">
+        <v>2</v>
+      </c>
+      <c r="B73" s="18">
+        <v>3</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="18">
+        <v>4</v>
+      </c>
+      <c r="E73" s="18">
+        <v>3</v>
+      </c>
+      <c r="F73" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H73" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -31973,7 +32943,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -34265,6 +35235,1255 @@
       <c r="J82" s="19"/>
       <c r="K82" s="19"/>
     </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="30">
+        <v>3</v>
+      </c>
+      <c r="B83" s="20">
+        <v>1</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="20">
+        <v>1</v>
+      </c>
+      <c r="E83" s="20">
+        <v>2</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H83" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="I83" s="32"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="30">
+        <v>3</v>
+      </c>
+      <c r="B84" s="20">
+        <v>1</v>
+      </c>
+      <c r="C84" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" s="20">
+        <v>1</v>
+      </c>
+      <c r="E84" s="20">
+        <v>2</v>
+      </c>
+      <c r="F84" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G84" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H84" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="I84" s="32"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="30">
+        <v>3</v>
+      </c>
+      <c r="B85" s="20">
+        <v>1</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" s="20">
+        <v>1</v>
+      </c>
+      <c r="E85" s="20">
+        <v>2</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H85" s="20">
+        <v>10</v>
+      </c>
+      <c r="I85" s="32"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="30">
+        <v>3</v>
+      </c>
+      <c r="B86" s="20">
+        <v>1</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="20">
+        <v>1</v>
+      </c>
+      <c r="E86" s="20">
+        <v>2</v>
+      </c>
+      <c r="F86" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H86" s="20">
+        <v>8</v>
+      </c>
+      <c r="I86" s="32"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="30">
+        <v>3</v>
+      </c>
+      <c r="B87" s="20">
+        <v>1</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87" s="20">
+        <v>1</v>
+      </c>
+      <c r="E87" s="20">
+        <v>2</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G87" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H87" s="20">
+        <v>8</v>
+      </c>
+      <c r="I87" s="32"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="30">
+        <v>3</v>
+      </c>
+      <c r="B88" s="30">
+        <v>1</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="30">
+        <v>1</v>
+      </c>
+      <c r="E88" s="30">
+        <v>2</v>
+      </c>
+      <c r="F88" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="G88" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H88" s="31">
+        <v>8</v>
+      </c>
+      <c r="I88" s="32"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="30">
+        <v>3</v>
+      </c>
+      <c r="B89" s="30">
+        <v>1</v>
+      </c>
+      <c r="C89" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="31"/>
+      <c r="E89" s="31"/>
+      <c r="F89" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="G89" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H89" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I89" s="32"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="30">
+        <v>3</v>
+      </c>
+      <c r="B90" s="30">
+        <v>1</v>
+      </c>
+      <c r="C90" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="31"/>
+      <c r="E90" s="31"/>
+      <c r="F90" s="31" t="s">
+        <v>295</v>
+      </c>
+      <c r="G90" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H90" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="I90" s="32"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="30">
+        <v>3</v>
+      </c>
+      <c r="B91" s="30">
+        <v>1</v>
+      </c>
+      <c r="C91" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="31"/>
+      <c r="E91" s="31"/>
+      <c r="F91" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G91" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H91" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I91" s="32"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="30">
+        <v>3</v>
+      </c>
+      <c r="B92" s="30">
+        <v>1</v>
+      </c>
+      <c r="C92" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="31"/>
+      <c r="E92" s="31"/>
+      <c r="F92" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="G92" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H92" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="I92" s="32"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="30">
+        <v>3</v>
+      </c>
+      <c r="B93" s="30">
+        <v>1</v>
+      </c>
+      <c r="C93" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="31"/>
+      <c r="E93" s="31"/>
+      <c r="F93" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="G93" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H93" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="I93" s="32"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="30">
+        <v>3</v>
+      </c>
+      <c r="B94" s="30">
+        <v>1</v>
+      </c>
+      <c r="C94" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" s="31"/>
+      <c r="E94" s="31"/>
+      <c r="F94" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="G94" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I94" s="32"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="30">
+        <v>3</v>
+      </c>
+      <c r="B95" s="30">
+        <v>1</v>
+      </c>
+      <c r="C95" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D95" s="31">
+        <v>2</v>
+      </c>
+      <c r="E95" s="31">
+        <v>3</v>
+      </c>
+      <c r="F95" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="G95" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H95" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="I95" s="32"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="30">
+        <v>3</v>
+      </c>
+      <c r="B96" s="30">
+        <v>1</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D96" s="31">
+        <v>2</v>
+      </c>
+      <c r="E96" s="31">
+        <v>3</v>
+      </c>
+      <c r="F96" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="G96" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H96" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="I96" s="32"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="30">
+        <v>3</v>
+      </c>
+      <c r="B97" s="30">
+        <v>1</v>
+      </c>
+      <c r="C97" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="31">
+        <v>2</v>
+      </c>
+      <c r="E97" s="31">
+        <v>3</v>
+      </c>
+      <c r="F97" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="G97" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H97" s="31">
+        <v>20</v>
+      </c>
+      <c r="I97" s="32"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="30">
+        <v>3</v>
+      </c>
+      <c r="B98" s="21">
+        <v>2</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="22">
+        <v>1</v>
+      </c>
+      <c r="E98" s="22">
+        <v>2</v>
+      </c>
+      <c r="F98" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G98" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H98" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="I98" s="32"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="30">
+        <v>3</v>
+      </c>
+      <c r="B99" s="21">
+        <v>2</v>
+      </c>
+      <c r="C99" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99" s="22">
+        <v>1</v>
+      </c>
+      <c r="E99" s="22">
+        <v>2</v>
+      </c>
+      <c r="F99" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G99" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H99" s="22">
+        <v>12</v>
+      </c>
+      <c r="I99" s="32"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="30">
+        <v>3</v>
+      </c>
+      <c r="B100" s="21">
+        <v>2</v>
+      </c>
+      <c r="C100" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="22">
+        <v>1</v>
+      </c>
+      <c r="E100" s="22">
+        <v>2</v>
+      </c>
+      <c r="F100" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="G100" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H100" s="22">
+        <v>10</v>
+      </c>
+      <c r="I100" s="32"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="30">
+        <v>3</v>
+      </c>
+      <c r="B101" s="21">
+        <v>2</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" s="22">
+        <v>1</v>
+      </c>
+      <c r="E101" s="22">
+        <v>2</v>
+      </c>
+      <c r="F101" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="G101" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="H101" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="I101" s="32"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="30">
+        <v>3</v>
+      </c>
+      <c r="B102" s="21">
+        <v>2</v>
+      </c>
+      <c r="C102" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" s="22">
+        <v>1</v>
+      </c>
+      <c r="E102" s="22">
+        <v>2</v>
+      </c>
+      <c r="F102" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G102" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H102" s="22">
+        <v>8</v>
+      </c>
+      <c r="I102" s="32"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="30">
+        <v>3</v>
+      </c>
+      <c r="B103" s="31">
+        <v>2</v>
+      </c>
+      <c r="C103" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D103" s="30">
+        <v>1</v>
+      </c>
+      <c r="E103" s="30">
+        <v>2</v>
+      </c>
+      <c r="F103" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G103" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H103" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I103" s="32"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="30">
+        <v>3</v>
+      </c>
+      <c r="B104" s="31">
+        <v>2</v>
+      </c>
+      <c r="C104" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" s="31"/>
+      <c r="E104" s="31"/>
+      <c r="F104" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H104" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I104" s="32"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="30">
+        <v>3</v>
+      </c>
+      <c r="B105" s="31">
+        <v>2</v>
+      </c>
+      <c r="C105" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="31"/>
+      <c r="E105" s="31"/>
+      <c r="F105" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="G105" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H105" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="I105" s="32"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="30">
+        <v>3</v>
+      </c>
+      <c r="B106" s="31">
+        <v>2</v>
+      </c>
+      <c r="C106" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D106" s="31"/>
+      <c r="E106" s="31"/>
+      <c r="F106" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G106" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H106" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="I106" s="32"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="30">
+        <v>3</v>
+      </c>
+      <c r="B107" s="31">
+        <v>2</v>
+      </c>
+      <c r="C107" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" s="31"/>
+      <c r="E107" s="31"/>
+      <c r="F107" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G107" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H107" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I107" s="32"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="30">
+        <v>3</v>
+      </c>
+      <c r="B108" s="31">
+        <v>2</v>
+      </c>
+      <c r="C108" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" s="31"/>
+      <c r="E108" s="31"/>
+      <c r="F108" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="G108" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H108" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="I108" s="32"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="30">
+        <v>3</v>
+      </c>
+      <c r="B109" s="31">
+        <v>2</v>
+      </c>
+      <c r="C109" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="31"/>
+      <c r="E109" s="31"/>
+      <c r="F109" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="G109" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H109" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="I109" s="32"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="30">
+        <v>3</v>
+      </c>
+      <c r="B110" s="23">
+        <v>3</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D110" s="24">
+        <v>1</v>
+      </c>
+      <c r="E110" s="24">
+        <v>2</v>
+      </c>
+      <c r="F110" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="G110" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H110" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="I110" s="32"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="30">
+        <v>3</v>
+      </c>
+      <c r="B111" s="23">
+        <v>3</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D111" s="24">
+        <v>1</v>
+      </c>
+      <c r="E111" s="24">
+        <v>2</v>
+      </c>
+      <c r="F111" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G111" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H111" s="23">
+        <v>10</v>
+      </c>
+      <c r="I111" s="32"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="30">
+        <v>3</v>
+      </c>
+      <c r="B112" s="23">
+        <v>3</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D112" s="24">
+        <v>1</v>
+      </c>
+      <c r="E112" s="24">
+        <v>2</v>
+      </c>
+      <c r="F112" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="G112" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H112" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="I112" s="32"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="30">
+        <v>3</v>
+      </c>
+      <c r="B113" s="23">
+        <v>3</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D113" s="24">
+        <v>1</v>
+      </c>
+      <c r="E113" s="24">
+        <v>2</v>
+      </c>
+      <c r="F113" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="G113" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="H113" s="23">
+        <v>8</v>
+      </c>
+      <c r="I113" s="32"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="30">
+        <v>3</v>
+      </c>
+      <c r="B114" s="23">
+        <v>3</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D114" s="24">
+        <v>1</v>
+      </c>
+      <c r="E114" s="24">
+        <v>2</v>
+      </c>
+      <c r="F114" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G114" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="H114" s="23">
+        <v>10</v>
+      </c>
+      <c r="I114" s="32"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="30">
+        <v>3</v>
+      </c>
+      <c r="B115" s="31">
+        <v>3</v>
+      </c>
+      <c r="C115" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D115" s="30">
+        <v>1</v>
+      </c>
+      <c r="E115" s="30">
+        <v>2</v>
+      </c>
+      <c r="F115" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G115" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H115" s="31">
+        <v>10</v>
+      </c>
+      <c r="I115" s="32"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="30">
+        <v>3</v>
+      </c>
+      <c r="B116" s="31">
+        <v>3</v>
+      </c>
+      <c r="C116" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" s="31">
+        <v>2</v>
+      </c>
+      <c r="E116" s="31">
+        <v>3</v>
+      </c>
+      <c r="F116" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="G116" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H116" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I116" s="32"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="30">
+        <v>3</v>
+      </c>
+      <c r="B117" s="31">
+        <v>3</v>
+      </c>
+      <c r="C117" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" s="31">
+        <v>2</v>
+      </c>
+      <c r="E117" s="31">
+        <v>3</v>
+      </c>
+      <c r="F117" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="G117" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H117" s="31">
+        <v>10</v>
+      </c>
+      <c r="I117" s="32"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="30">
+        <v>3</v>
+      </c>
+      <c r="B118" s="31">
+        <v>3</v>
+      </c>
+      <c r="C118" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D118" s="31">
+        <v>2</v>
+      </c>
+      <c r="E118" s="31">
+        <v>3</v>
+      </c>
+      <c r="F118" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="G118" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H118" s="31">
+        <v>20</v>
+      </c>
+      <c r="I118" s="32"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="30">
+        <v>3</v>
+      </c>
+      <c r="B119" s="31">
+        <v>3</v>
+      </c>
+      <c r="C119" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D119" s="31">
+        <v>3</v>
+      </c>
+      <c r="E119" s="31">
+        <v>3</v>
+      </c>
+      <c r="F119" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="G119" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H119" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I119" s="32"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="30">
+        <v>3</v>
+      </c>
+      <c r="B120" s="31">
+        <v>3</v>
+      </c>
+      <c r="C120" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120" s="31">
+        <v>3</v>
+      </c>
+      <c r="E120" s="31">
+        <v>3</v>
+      </c>
+      <c r="F120" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="G120" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H120" s="31">
+        <v>12</v>
+      </c>
+      <c r="I120" s="32"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="30">
+        <v>3</v>
+      </c>
+      <c r="B121" s="31">
+        <v>3</v>
+      </c>
+      <c r="C121" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D121" s="31">
+        <v>3</v>
+      </c>
+      <c r="E121" s="31">
+        <v>3</v>
+      </c>
+      <c r="F121" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="G121" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H121" s="31">
+        <v>30</v>
+      </c>
+      <c r="I121" s="32"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="30">
+        <v>3</v>
+      </c>
+      <c r="B122" s="31">
+        <v>3</v>
+      </c>
+      <c r="C122" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D122" s="31">
+        <v>4</v>
+      </c>
+      <c r="E122" s="31">
+        <v>3</v>
+      </c>
+      <c r="F122" s="31" t="s">
+        <v>311</v>
+      </c>
+      <c r="G122" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H122" s="31">
+        <v>10</v>
+      </c>
+      <c r="I122" s="32"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="30">
+        <v>3</v>
+      </c>
+      <c r="B123" s="31">
+        <v>3</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" s="31">
+        <v>4</v>
+      </c>
+      <c r="E123" s="31">
+        <v>3</v>
+      </c>
+      <c r="F123" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="G123" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H123" s="31">
+        <v>5</v>
+      </c>
+      <c r="I123" s="32"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="30">
+        <v>3</v>
+      </c>
+      <c r="B124" s="31">
+        <v>3</v>
+      </c>
+      <c r="C124" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D124" s="31">
+        <v>4</v>
+      </c>
+      <c r="E124" s="31">
+        <v>3</v>
+      </c>
+      <c r="F124" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="G124" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H124" s="31">
+        <v>15</v>
+      </c>
+      <c r="I124" s="32"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="30">
+        <v>3</v>
+      </c>
+      <c r="B125" s="31">
+        <v>4</v>
+      </c>
+      <c r="C125" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D125" s="31">
+        <v>1</v>
+      </c>
+      <c r="E125" s="31">
+        <v>2</v>
+      </c>
+      <c r="F125" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="G125" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H125" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I125" s="32"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="30">
+        <v>3</v>
+      </c>
+      <c r="B126" s="31">
+        <v>4</v>
+      </c>
+      <c r="C126" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D126" s="31">
+        <v>1</v>
+      </c>
+      <c r="E126" s="31">
+        <v>2</v>
+      </c>
+      <c r="F126" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="G126" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H126" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I126" s="32"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="30">
+        <v>3</v>
+      </c>
+      <c r="B127" s="31">
+        <v>4</v>
+      </c>
+      <c r="C127" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D127" s="31">
+        <v>1</v>
+      </c>
+      <c r="E127" s="31">
+        <v>2</v>
+      </c>
+      <c r="F127" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="G127" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H127" s="31">
+        <v>10</v>
+      </c>
+      <c r="I127" s="32"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="30">
+        <v>3</v>
+      </c>
+      <c r="B128" s="31">
+        <v>4</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D128" s="31">
+        <v>1</v>
+      </c>
+      <c r="E128" s="31">
+        <v>2</v>
+      </c>
+      <c r="F128" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="G128" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H128" s="31">
+        <v>10</v>
+      </c>
+      <c r="I128" s="32"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="30">
+        <v>3</v>
+      </c>
+      <c r="B129" s="31">
+        <v>4</v>
+      </c>
+      <c r="C129" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" s="31">
+        <v>1</v>
+      </c>
+      <c r="E129" s="31">
+        <v>2</v>
+      </c>
+      <c r="F129" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="G129" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H129" s="31">
+        <v>20</v>
+      </c>
+      <c r="I129" s="32"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="30">
+        <v>3</v>
+      </c>
+      <c r="B130" s="31">
+        <v>4</v>
+      </c>
+      <c r="C130" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F130" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="G130" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H130" s="31" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F131" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="H131" t="s">
+        <v>378</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C303" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -34277,7 +36496,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -36862,11 +39081,13 @@
       <c r="D92" s="31"/>
       <c r="E92" s="31"/>
       <c r="F92" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="G92" s="31"/>
+        <v>57</v>
+      </c>
+      <c r="G92" s="31" t="s">
+        <v>52</v>
+      </c>
       <c r="H92" s="31" t="s">
-        <v>202</v>
+        <v>355</v>
       </c>
       <c r="I92" s="32"/>
     </row>
@@ -36885,7 +39106,9 @@
       <c r="F93" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="G93" s="31"/>
+      <c r="G93" s="31" t="s">
+        <v>52</v>
+      </c>
       <c r="H93" s="31" t="s">
         <v>65</v>
       </c>
@@ -36906,7 +39129,9 @@
       <c r="F94" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="G94" s="31"/>
+      <c r="G94" s="31" t="s">
+        <v>63</v>
+      </c>
       <c r="H94" s="31" t="s">
         <v>44</v>
       </c>
@@ -36927,7 +39152,9 @@
       <c r="F95" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="G95" s="31"/>
+      <c r="G95" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="H95" s="31" t="s">
         <v>355</v>
       </c>
@@ -36948,7 +39175,9 @@
       <c r="F96" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="G96" s="31"/>
+      <c r="G96" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="H96" s="31" t="s">
         <v>355</v>
       </c>
@@ -36969,7 +39198,9 @@
       <c r="F97" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="G97" s="31"/>
+      <c r="G97" s="31" t="s">
+        <v>53</v>
+      </c>
       <c r="H97" s="31" t="s">
         <v>65</v>
       </c>
@@ -36983,22 +39214,18 @@
         <v>1</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D98" s="31">
-        <v>2</v>
-      </c>
-      <c r="E98" s="31">
-        <v>3</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D98" s="31"/>
+      <c r="E98" s="31"/>
       <c r="F98" s="31" t="s">
-        <v>67</v>
+        <v>367</v>
       </c>
       <c r="G98" s="31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H98" s="31" t="s">
-        <v>159</v>
+        <v>368</v>
       </c>
       <c r="I98" s="32"/>
     </row>
@@ -37019,13 +39246,13 @@
         <v>3</v>
       </c>
       <c r="F99" s="31" t="s">
-        <v>332</v>
+        <v>67</v>
       </c>
       <c r="G99" s="31" t="s">
         <v>54</v>
       </c>
       <c r="H99" s="31" t="s">
-        <v>275</v>
+        <v>159</v>
       </c>
       <c r="I99" s="32"/>
     </row>
@@ -37046,13 +39273,13 @@
         <v>3</v>
       </c>
       <c r="F100" s="31" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="G100" s="31" t="s">
         <v>54</v>
       </c>
       <c r="H100" s="31" t="s">
-        <v>70</v>
+        <v>275</v>
       </c>
       <c r="I100" s="32"/>
     </row>
@@ -37060,26 +39287,26 @@
       <c r="A101" s="30">
         <v>3</v>
       </c>
-      <c r="B101" s="26">
-        <v>2</v>
-      </c>
-      <c r="C101" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D101" s="27">
-        <v>1</v>
-      </c>
-      <c r="E101" s="27">
-        <v>2</v>
-      </c>
-      <c r="F101" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="G101" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H101" s="26">
-        <v>10</v>
+      <c r="B101" s="30">
+        <v>1</v>
+      </c>
+      <c r="C101" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D101" s="31">
+        <v>2</v>
+      </c>
+      <c r="E101" s="31">
+        <v>3</v>
+      </c>
+      <c r="F101" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="G101" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H101" s="31" t="s">
+        <v>70</v>
       </c>
       <c r="I101" s="32"/>
     </row>
@@ -37100,13 +39327,13 @@
         <v>2</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="G102" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="H102" s="26" t="s">
-        <v>100</v>
+      <c r="H102" s="26">
+        <v>10</v>
       </c>
       <c r="I102" s="32"/>
     </row>
@@ -37127,13 +39354,13 @@
         <v>2</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="G103" s="26" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H103" s="26" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="I103" s="32"/>
     </row>
@@ -37154,13 +39381,13 @@
         <v>2</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G104" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="H104" s="26">
-        <v>6</v>
+        <v>54</v>
+      </c>
+      <c r="H104" s="26" t="s">
+        <v>56</v>
       </c>
       <c r="I104" s="32"/>
     </row>
@@ -37181,13 +39408,13 @@
         <v>2</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="G105" s="26" t="s">
-        <v>78</v>
+        <v>142</v>
       </c>
       <c r="H105" s="26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I105" s="32"/>
     </row>
@@ -37195,22 +39422,26 @@
       <c r="A106" s="30">
         <v>3</v>
       </c>
-      <c r="B106" s="31">
-        <v>2</v>
-      </c>
-      <c r="C106" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D106" s="31"/>
-      <c r="E106" s="31"/>
-      <c r="F106" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G106" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="H106" s="31" t="s">
-        <v>356</v>
+      <c r="B106" s="26">
+        <v>2</v>
+      </c>
+      <c r="C106" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D106" s="27">
+        <v>1</v>
+      </c>
+      <c r="E106" s="27">
+        <v>2</v>
+      </c>
+      <c r="F106" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="G106" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H106" s="26">
+        <v>8</v>
       </c>
       <c r="I106" s="32"/>
     </row>
@@ -37227,13 +39458,13 @@
       <c r="D107" s="31"/>
       <c r="E107" s="31"/>
       <c r="F107" s="31" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="G107" s="31" t="s">
         <v>63</v>
       </c>
       <c r="H107" s="31" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I107" s="32"/>
     </row>
@@ -37250,13 +39481,13 @@
       <c r="D108" s="31"/>
       <c r="E108" s="31"/>
       <c r="F108" s="31" t="s">
-        <v>313</v>
+        <v>149</v>
       </c>
       <c r="G108" s="31" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H108" s="31" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="I108" s="32"/>
     </row>
@@ -37273,13 +39504,13 @@
       <c r="D109" s="31"/>
       <c r="E109" s="31"/>
       <c r="F109" s="31" t="s">
-        <v>88</v>
+        <v>313</v>
       </c>
       <c r="G109" s="31" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="H109" s="31" t="s">
-        <v>44</v>
+        <v>349</v>
       </c>
       <c r="I109" s="32"/>
     </row>
@@ -37296,13 +39527,13 @@
       <c r="D110" s="31"/>
       <c r="E110" s="31"/>
       <c r="F110" s="31" t="s">
-        <v>206</v>
+        <v>88</v>
       </c>
       <c r="G110" s="31" t="s">
         <v>78</v>
       </c>
       <c r="H110" s="31" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="I110" s="32"/>
     </row>
@@ -37319,13 +39550,13 @@
       <c r="D111" s="31"/>
       <c r="E111" s="31"/>
       <c r="F111" s="31" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="G111" s="31" t="s">
         <v>78</v>
       </c>
       <c r="H111" s="31" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="I111" s="32"/>
     </row>
@@ -37337,22 +39568,18 @@
         <v>2</v>
       </c>
       <c r="C112" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D112" s="31">
-        <v>2</v>
-      </c>
-      <c r="E112" s="31">
-        <v>3</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D112" s="31"/>
+      <c r="E112" s="31"/>
       <c r="F112" s="31" t="s">
-        <v>68</v>
+        <v>171</v>
       </c>
       <c r="G112" s="31" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="H112" s="31" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="I112" s="32"/>
     </row>
@@ -37364,22 +39591,18 @@
         <v>2</v>
       </c>
       <c r="C113" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D113" s="31">
-        <v>2</v>
-      </c>
-      <c r="E113" s="31">
-        <v>3</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D113" s="31"/>
+      <c r="E113" s="31"/>
       <c r="F113" s="31" t="s">
-        <v>330</v>
+        <v>369</v>
       </c>
       <c r="G113" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="H113" s="31">
-        <v>20</v>
+        <v>78</v>
+      </c>
+      <c r="H113" s="31" t="s">
+        <v>368</v>
       </c>
       <c r="I113" s="32"/>
     </row>
@@ -37400,13 +39623,13 @@
         <v>3</v>
       </c>
       <c r="F114" s="31" t="s">
-        <v>351</v>
+        <v>68</v>
       </c>
       <c r="G114" s="31" t="s">
         <v>54</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>218</v>
+        <v>70</v>
       </c>
       <c r="I114" s="32"/>
     </row>
@@ -37414,26 +39637,26 @@
       <c r="A115" s="30">
         <v>3</v>
       </c>
-      <c r="B115" s="28">
-        <v>3</v>
-      </c>
-      <c r="C115" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D115" s="29">
-        <v>1</v>
-      </c>
-      <c r="E115" s="29">
-        <v>2</v>
-      </c>
-      <c r="F115" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="G115" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="H115" s="28" t="s">
-        <v>80</v>
+      <c r="B115" s="31">
+        <v>2</v>
+      </c>
+      <c r="C115" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D115" s="31">
+        <v>2</v>
+      </c>
+      <c r="E115" s="31">
+        <v>3</v>
+      </c>
+      <c r="F115" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="G115" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H115" s="31">
+        <v>20</v>
       </c>
       <c r="I115" s="32"/>
     </row>
@@ -37441,26 +39664,26 @@
       <c r="A116" s="30">
         <v>3</v>
       </c>
-      <c r="B116" s="28">
-        <v>3</v>
-      </c>
-      <c r="C116" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D116" s="29">
-        <v>1</v>
-      </c>
-      <c r="E116" s="29">
-        <v>2</v>
-      </c>
-      <c r="F116" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="G116" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H116" s="28">
-        <v>10</v>
+      <c r="B116" s="31">
+        <v>2</v>
+      </c>
+      <c r="C116" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D116" s="31">
+        <v>2</v>
+      </c>
+      <c r="E116" s="31">
+        <v>3</v>
+      </c>
+      <c r="F116" s="31" t="s">
+        <v>351</v>
+      </c>
+      <c r="G116" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H116" s="31" t="s">
+        <v>218</v>
       </c>
       <c r="I116" s="32"/>
     </row>
@@ -37481,13 +39704,13 @@
         <v>2</v>
       </c>
       <c r="F117" s="29" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="G117" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="H117" s="28">
-        <v>10</v>
+        <v>51</v>
+      </c>
+      <c r="H117" s="28" t="s">
+        <v>80</v>
       </c>
       <c r="I117" s="32"/>
     </row>
@@ -37508,13 +39731,13 @@
         <v>2</v>
       </c>
       <c r="F118" s="29" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="G118" s="29" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H118" s="28">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I118" s="32"/>
     </row>
@@ -37535,13 +39758,13 @@
         <v>2</v>
       </c>
       <c r="F119" s="29" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="G119" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="H119" s="28" t="s">
-        <v>70</v>
+        <v>52</v>
+      </c>
+      <c r="H119" s="28">
+        <v>10</v>
       </c>
       <c r="I119" s="32"/>
     </row>
@@ -37549,22 +39772,26 @@
       <c r="A120" s="30">
         <v>3</v>
       </c>
-      <c r="B120" s="31">
-        <v>3</v>
-      </c>
-      <c r="C120" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D120" s="31"/>
-      <c r="E120" s="31"/>
-      <c r="F120" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="G120" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="H120" s="31" t="s">
-        <v>44</v>
+      <c r="B120" s="28">
+        <v>3</v>
+      </c>
+      <c r="C120" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D120" s="29">
+        <v>1</v>
+      </c>
+      <c r="E120" s="29">
+        <v>2</v>
+      </c>
+      <c r="F120" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="G120" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H120" s="28">
+        <v>15</v>
       </c>
       <c r="I120" s="32"/>
     </row>
@@ -37572,22 +39799,26 @@
       <c r="A121" s="30">
         <v>3</v>
       </c>
-      <c r="B121" s="31">
-        <v>3</v>
-      </c>
-      <c r="C121" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D121" s="31"/>
-      <c r="E121" s="31"/>
-      <c r="F121" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="G121" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="H121" s="31" t="s">
-        <v>274</v>
+      <c r="B121" s="28">
+        <v>3</v>
+      </c>
+      <c r="C121" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D121" s="29">
+        <v>1</v>
+      </c>
+      <c r="E121" s="29">
+        <v>2</v>
+      </c>
+      <c r="F121" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G121" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="H121" s="28" t="s">
+        <v>70</v>
       </c>
       <c r="I121" s="32"/>
     </row>
@@ -37601,16 +39832,16 @@
       <c r="C122" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D122" s="32"/>
-      <c r="E122" s="32"/>
+      <c r="D122" s="31"/>
+      <c r="E122" s="31"/>
       <c r="F122" s="31" t="s">
-        <v>298</v>
+        <v>205</v>
       </c>
       <c r="G122" s="31" t="s">
         <v>53</v>
       </c>
       <c r="H122" s="31" t="s">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="I122" s="32"/>
     </row>
@@ -37624,16 +39855,16 @@
       <c r="C123" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D123" s="32"/>
-      <c r="E123" s="32"/>
+      <c r="D123" s="31"/>
+      <c r="E123" s="31"/>
       <c r="F123" s="31" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="G123" s="31" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="H123" s="31" t="s">
-        <v>44</v>
+        <v>274</v>
       </c>
       <c r="I123" s="32"/>
     </row>
@@ -37647,20 +39878,16 @@
       <c r="C124" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D124" s="32">
-        <v>2</v>
-      </c>
-      <c r="E124" s="32">
-        <v>3</v>
-      </c>
+      <c r="D124" s="32"/>
+      <c r="E124" s="32"/>
       <c r="F124" s="31" t="s">
-        <v>207</v>
+        <v>298</v>
       </c>
       <c r="G124" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H124" s="31" t="s">
-        <v>55</v>
+        <v>284</v>
       </c>
       <c r="I124" s="32"/>
     </row>
@@ -37674,20 +39901,16 @@
       <c r="C125" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D125" s="32">
-        <v>2</v>
-      </c>
-      <c r="E125" s="32">
-        <v>3</v>
-      </c>
+      <c r="D125" s="32"/>
+      <c r="E125" s="32"/>
       <c r="F125" s="31" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G125" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="H125" s="32">
-        <v>10</v>
+      <c r="H125" s="31" t="s">
+        <v>44</v>
       </c>
       <c r="I125" s="32"/>
     </row>
@@ -37702,16 +39925,16 @@
         <v>34</v>
       </c>
       <c r="D126" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E126" s="32">
         <v>3</v>
       </c>
       <c r="F126" s="31" t="s">
-        <v>126</v>
+        <v>207</v>
       </c>
       <c r="G126" s="31" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H126" s="31" t="s">
         <v>55</v>
@@ -37729,25 +39952,79 @@
         <v>34</v>
       </c>
       <c r="D127" s="32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E127" s="32">
         <v>3</v>
       </c>
       <c r="F127" s="31" t="s">
-        <v>357</v>
+        <v>208</v>
       </c>
       <c r="G127" s="31" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H127" s="32">
         <v>10</v>
       </c>
       <c r="I127" s="32"/>
     </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="30">
+        <v>3</v>
+      </c>
+      <c r="B128" s="31">
+        <v>3</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D128" s="32">
+        <v>3</v>
+      </c>
+      <c r="E128" s="32">
+        <v>3</v>
+      </c>
+      <c r="F128" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G128" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H128" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I128" s="32"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="30">
+        <v>3</v>
+      </c>
+      <c r="B129" s="31">
+        <v>3</v>
+      </c>
+      <c r="C129" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D129" s="32">
+        <v>3</v>
+      </c>
+      <c r="E129" s="32">
+        <v>3</v>
+      </c>
+      <c r="F129" s="31" t="s">
+        <v>357</v>
+      </c>
+      <c r="G129" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H129" s="32">
+        <v>10</v>
+      </c>
+      <c r="I129" s="32"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C297" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C299" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\APP PROFE\pwa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17206974-C8A2-4E3A-BE0D-405DFDDF742A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65756845-0F86-4BEE-B72A-D982BA96A86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5591" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5592" uniqueCount="379">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -36477,6 +36477,15 @@
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="30">
+        <v>3</v>
+      </c>
+      <c r="B131" s="31">
+        <v>4</v>
+      </c>
+      <c r="C131" s="31" t="s">
+        <v>40</v>
+      </c>
       <c r="F131" s="31" t="s">
         <v>376</v>
       </c>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\APP PROFE\pwa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65756845-0F86-4BEE-B72A-D982BA96A86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC27687-1C83-4269-AA50-152B163851C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5592" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5603" uniqueCount="379">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -11525,17 +11525,15 @@
         <v>34</v>
       </c>
       <c r="D58" s="18"/>
-      <c r="E58" s="18">
-        <v>4</v>
-      </c>
+      <c r="E58" s="18"/>
       <c r="F58" s="18" t="s">
         <v>57</v>
       </c>
       <c r="G58" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H58" s="18">
-        <v>8</v>
+      <c r="H58" s="18" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -11601,17 +11599,15 @@
         <v>34</v>
       </c>
       <c r="D61" s="18"/>
-      <c r="E61" s="18">
-        <v>4</v>
-      </c>
+      <c r="E61" s="18"/>
       <c r="F61" s="18" t="s">
         <v>86</v>
       </c>
       <c r="G61" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H61" s="18">
-        <v>8</v>
+      <c r="H61" s="18" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -11911,17 +11907,15 @@
         <v>34</v>
       </c>
       <c r="D73" s="18"/>
-      <c r="E73" s="18">
-        <v>4</v>
-      </c>
+      <c r="E73" s="18"/>
       <c r="F73" s="18" t="s">
         <v>155</v>
       </c>
       <c r="G73" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H73" s="18">
-        <v>6</v>
+      <c r="H73" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -11935,17 +11929,15 @@
         <v>34</v>
       </c>
       <c r="D74" s="18"/>
-      <c r="E74" s="18">
-        <v>4</v>
-      </c>
+      <c r="E74" s="18"/>
       <c r="F74" s="18" t="s">
         <v>59</v>
       </c>
       <c r="G74" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="H74" s="18">
-        <v>10</v>
+      <c r="H74" s="18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -11959,9 +11951,7 @@
         <v>34</v>
       </c>
       <c r="D75" s="18"/>
-      <c r="E75" s="18">
-        <v>4</v>
-      </c>
+      <c r="E75" s="18"/>
       <c r="F75" s="18" t="s">
         <v>241</v>
       </c>
@@ -11969,7 +11959,7 @@
         <v>52</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>55</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -11983,17 +11973,15 @@
         <v>34</v>
       </c>
       <c r="D76" s="18"/>
-      <c r="E76" s="18">
-        <v>4</v>
-      </c>
+      <c r="E76" s="18"/>
       <c r="F76" s="18" t="s">
         <v>149</v>
       </c>
       <c r="G76" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H76" s="18">
-        <v>12</v>
+      <c r="H76" s="18" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -12735,9 +12723,7 @@
         <v>34</v>
       </c>
       <c r="D105" s="31"/>
-      <c r="E105" s="31">
-        <v>4</v>
-      </c>
+      <c r="E105" s="31"/>
       <c r="F105" s="31" t="s">
         <v>57</v>
       </c>
@@ -12811,9 +12797,7 @@
         <v>34</v>
       </c>
       <c r="D108" s="31"/>
-      <c r="E108" s="31">
-        <v>4</v>
-      </c>
+      <c r="E108" s="31"/>
       <c r="F108" s="31" t="s">
         <v>86</v>
       </c>
@@ -13095,9 +13079,7 @@
         <v>34</v>
       </c>
       <c r="D119" s="31"/>
-      <c r="E119" s="31">
-        <v>4</v>
-      </c>
+      <c r="E119" s="31"/>
       <c r="F119" s="31" t="s">
         <v>155</v>
       </c>
@@ -13119,9 +13101,7 @@
         <v>34</v>
       </c>
       <c r="D120" s="31"/>
-      <c r="E120" s="31">
-        <v>4</v>
-      </c>
+      <c r="E120" s="31"/>
       <c r="F120" s="31" t="s">
         <v>59</v>
       </c>
@@ -13143,17 +13123,15 @@
         <v>34</v>
       </c>
       <c r="D121" s="31"/>
-      <c r="E121" s="31">
-        <v>4</v>
-      </c>
+      <c r="E121" s="31"/>
       <c r="F121" s="31" t="s">
         <v>132</v>
       </c>
       <c r="G121" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="H121" s="31">
-        <v>8</v>
+      <c r="H121" s="31" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -13167,9 +13145,7 @@
         <v>34</v>
       </c>
       <c r="D122" s="31"/>
-      <c r="E122" s="31">
-        <v>4</v>
-      </c>
+      <c r="E122" s="31"/>
       <c r="F122" s="31" t="s">
         <v>149</v>
       </c>
@@ -20092,7 +20068,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F357C59-977B-4591-AD82-2B7621F6CA1A}">
-  <dimension ref="A1:I127"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -23323,9 +23299,37 @@
       </c>
       <c r="I127" s="32"/>
     </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="30">
+        <v>3</v>
+      </c>
+      <c r="B128" s="31">
+        <v>4</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="F128" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="G128" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H128" s="31" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="129" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F129" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="H129" t="s">
+        <v>378</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C127" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C129" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -36477,15 +36481,6 @@
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="30">
-        <v>3</v>
-      </c>
-      <c r="B131" s="31">
-        <v>4</v>
-      </c>
-      <c r="C131" s="31" t="s">
-        <v>40</v>
-      </c>
       <c r="F131" s="31" t="s">
         <v>376</v>
       </c>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC27687-1C83-4269-AA50-152B163851C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8F590A-281C-4EA4-A817-A3B3C2482E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5603" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6691" uniqueCount="426">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -1176,6 +1176,147 @@
   <si>
     <t>Descanso entre rounds 2'</t>
   </si>
+  <si>
+    <t>4x8 (60% RM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single leg dead lift  </t>
+  </si>
+  <si>
+    <t>Pectoralera</t>
+  </si>
+  <si>
+    <t>Pallof Press dinamico con disco</t>
+  </si>
+  <si>
+    <t>Plank aductor</t>
+  </si>
+  <si>
+    <t>Bug dead con carga</t>
+  </si>
+  <si>
+    <t>Sldl to box step up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4x5 </t>
+  </si>
+  <si>
+    <t>4x4 cada pierna</t>
+  </si>
+  <si>
+    <t>Speed lunges jump</t>
+  </si>
+  <si>
+    <t>V ups alternadas</t>
+  </si>
+  <si>
+    <t>Walk out</t>
+  </si>
+  <si>
+    <t>1x7 (65%) 2x5 (75% RM) 2x4 (80%RM)</t>
+  </si>
+  <si>
+    <t>2x10 2x8</t>
+  </si>
+  <si>
+    <t>(Bonus) Press frances con soga en polea</t>
+  </si>
+  <si>
+    <t>V ups</t>
+  </si>
+  <si>
+    <t>4x5 (75% RM)</t>
+  </si>
+  <si>
+    <t>(Bonus) Curl biceps con soga en polea</t>
+  </si>
+  <si>
+    <t>Plank lat con carga</t>
+  </si>
+  <si>
+    <t>Roll out (ruedita)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Press arnold  </t>
+  </si>
+  <si>
+    <t>Pull down agarre neutro</t>
+  </si>
+  <si>
+    <t>Cable crossover bajo</t>
+  </si>
+  <si>
+    <t>Pistols</t>
+  </si>
+  <si>
+    <t>2x5 (70% RM) 3x3 (80%RM)</t>
+  </si>
+  <si>
+    <t>1x5 (70% RM) 3x3 (80%RM)</t>
+  </si>
+  <si>
+    <t>Plank saco pie</t>
+  </si>
+  <si>
+    <t>Roll out</t>
+  </si>
+  <si>
+    <t>Rotacion int + ext de cadera</t>
+  </si>
+  <si>
+    <t>Air squats</t>
+  </si>
+  <si>
+    <t>Rotacion de cadera para gluteos</t>
+  </si>
+  <si>
+    <t>Reverse lunges</t>
+  </si>
+  <si>
+    <t>Rotacion de cadera en cruz</t>
+  </si>
+  <si>
+    <t>5 cada lado</t>
+  </si>
+  <si>
+    <t>Rotacion externa de hombro</t>
+  </si>
+  <si>
+    <t>Vuelos frontales livianos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoulder press  </t>
+  </si>
+  <si>
+    <t>Pallof press dinamico con disco</t>
+  </si>
+  <si>
+    <t>Plank lateral con carga</t>
+  </si>
+  <si>
+    <t>Roll outs</t>
+  </si>
+  <si>
+    <t>Pull up</t>
+  </si>
+  <si>
+    <t>Curl de biceps en polea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row serrcho  </t>
+  </si>
+  <si>
+    <t>Goblet sumo Squats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumping jacks  </t>
+  </si>
+  <si>
+    <t>Good morning</t>
+  </si>
+  <si>
+    <t>1x7 1x5 3x2 (Aumentando la carga)</t>
+  </si>
 </sst>
 </file>
 
@@ -1225,7 +1366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1382,6 +1523,60 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1395,7 +1590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1432,6 +1627,20 @@
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1827,7 +2036,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -3580,6 +3789,864 @@
       </c>
       <c r="H67" s="18">
         <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="30">
+        <v>3</v>
+      </c>
+      <c r="B68" s="25">
+        <v>1</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="25">
+        <v>1</v>
+      </c>
+      <c r="E68" s="25">
+        <v>2</v>
+      </c>
+      <c r="F68" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="G68" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H68" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="30">
+        <v>3</v>
+      </c>
+      <c r="B69" s="25">
+        <v>1</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" s="25">
+        <v>1</v>
+      </c>
+      <c r="E69" s="25">
+        <v>2</v>
+      </c>
+      <c r="F69" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H69" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="30">
+        <v>3</v>
+      </c>
+      <c r="B70" s="25">
+        <v>1</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" s="25">
+        <v>1</v>
+      </c>
+      <c r="E70" s="25">
+        <v>2</v>
+      </c>
+      <c r="F70" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G70" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H70" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="30">
+        <v>3</v>
+      </c>
+      <c r="B71" s="25">
+        <v>1</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D71" s="25">
+        <v>1</v>
+      </c>
+      <c r="E71" s="25">
+        <v>2</v>
+      </c>
+      <c r="F71" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G71" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="30">
+        <v>3</v>
+      </c>
+      <c r="B72" s="25">
+        <v>1</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="25">
+        <v>1</v>
+      </c>
+      <c r="E72" s="25">
+        <v>2</v>
+      </c>
+      <c r="F72" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G72" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="H72" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="30">
+        <v>3</v>
+      </c>
+      <c r="B73" s="30">
+        <v>1</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D73" s="30">
+        <v>1</v>
+      </c>
+      <c r="E73" s="30">
+        <v>2</v>
+      </c>
+      <c r="F73" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G73" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H73" s="31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="30">
+        <v>3</v>
+      </c>
+      <c r="B74" s="30">
+        <v>1</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="31">
+        <v>2</v>
+      </c>
+      <c r="E74" s="31">
+        <v>4</v>
+      </c>
+      <c r="F74" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="31" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="30">
+        <v>3</v>
+      </c>
+      <c r="B75" s="30">
+        <v>1</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" s="31">
+        <v>2</v>
+      </c>
+      <c r="E75" s="31">
+        <v>4</v>
+      </c>
+      <c r="F75" s="31" t="s">
+        <v>319</v>
+      </c>
+      <c r="G75" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H75" s="31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="30">
+        <v>3</v>
+      </c>
+      <c r="B76" s="30">
+        <v>1</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D76" s="31">
+        <v>2</v>
+      </c>
+      <c r="E76" s="31">
+        <v>4</v>
+      </c>
+      <c r="F76" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G76" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H76" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="30">
+        <v>3</v>
+      </c>
+      <c r="B77" s="30">
+        <v>1</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D77" s="31">
+        <v>3</v>
+      </c>
+      <c r="E77" s="31">
+        <v>4</v>
+      </c>
+      <c r="F77" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G77" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H77" s="31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="30">
+        <v>3</v>
+      </c>
+      <c r="B78" s="30">
+        <v>1</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D78" s="31">
+        <v>3</v>
+      </c>
+      <c r="E78" s="31">
+        <v>4</v>
+      </c>
+      <c r="F78" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="G78" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H78" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="30">
+        <v>3</v>
+      </c>
+      <c r="B79" s="30">
+        <v>1</v>
+      </c>
+      <c r="C79" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="31">
+        <v>3</v>
+      </c>
+      <c r="E79" s="31">
+        <v>4</v>
+      </c>
+      <c r="F79" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G79" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H79" s="31" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="30">
+        <v>3</v>
+      </c>
+      <c r="B80" s="30">
+        <v>1</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D80" s="31">
+        <v>4</v>
+      </c>
+      <c r="E80" s="31">
+        <v>3</v>
+      </c>
+      <c r="F80" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H80" s="31" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="30">
+        <v>3</v>
+      </c>
+      <c r="B81" s="30">
+        <v>1</v>
+      </c>
+      <c r="C81" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D81" s="31">
+        <v>4</v>
+      </c>
+      <c r="E81" s="31">
+        <v>3</v>
+      </c>
+      <c r="F81" s="31" t="s">
+        <v>405</v>
+      </c>
+      <c r="G81" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H81" s="31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="30">
+        <v>3</v>
+      </c>
+      <c r="B82" s="30">
+        <v>1</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D82" s="31">
+        <v>4</v>
+      </c>
+      <c r="E82" s="31">
+        <v>3</v>
+      </c>
+      <c r="F82" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H82" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="30">
+        <v>3</v>
+      </c>
+      <c r="B83" s="28">
+        <v>3</v>
+      </c>
+      <c r="C83" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="29">
+        <v>1</v>
+      </c>
+      <c r="E83" s="29">
+        <v>2</v>
+      </c>
+      <c r="F83" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="G83" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="H83" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="30">
+        <v>3</v>
+      </c>
+      <c r="B84" s="28">
+        <v>3</v>
+      </c>
+      <c r="C84" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D84" s="29">
+        <v>1</v>
+      </c>
+      <c r="E84" s="29">
+        <v>2</v>
+      </c>
+      <c r="F84" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="G84" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H84" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="30">
+        <v>3</v>
+      </c>
+      <c r="B85" s="28">
+        <v>3</v>
+      </c>
+      <c r="C85" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" s="29">
+        <v>1</v>
+      </c>
+      <c r="E85" s="29">
+        <v>2</v>
+      </c>
+      <c r="F85" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H85" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="30">
+        <v>3</v>
+      </c>
+      <c r="B86" s="28">
+        <v>3</v>
+      </c>
+      <c r="C86" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="29">
+        <v>1</v>
+      </c>
+      <c r="E86" s="29">
+        <v>2</v>
+      </c>
+      <c r="F86" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="G86" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H86" s="28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="30">
+        <v>3</v>
+      </c>
+      <c r="B87" s="28">
+        <v>3</v>
+      </c>
+      <c r="C87" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87" s="29">
+        <v>1</v>
+      </c>
+      <c r="E87" s="29">
+        <v>2</v>
+      </c>
+      <c r="F87" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G87" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="H87" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="30">
+        <v>3</v>
+      </c>
+      <c r="B88" s="31">
+        <v>2</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="30">
+        <v>1</v>
+      </c>
+      <c r="E88" s="30">
+        <v>2</v>
+      </c>
+      <c r="F88" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="G88" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H88" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="30">
+        <v>3</v>
+      </c>
+      <c r="B89" s="31">
+        <v>2</v>
+      </c>
+      <c r="C89" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="31">
+        <v>2</v>
+      </c>
+      <c r="E89" s="31">
+        <v>4</v>
+      </c>
+      <c r="F89" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="G89" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H89" s="31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="30">
+        <v>3</v>
+      </c>
+      <c r="B90" s="31">
+        <v>2</v>
+      </c>
+      <c r="C90" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D90" s="31">
+        <v>2</v>
+      </c>
+      <c r="E90" s="31">
+        <v>4</v>
+      </c>
+      <c r="F90" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G90" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H90" s="31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="30">
+        <v>3</v>
+      </c>
+      <c r="B91" s="31">
+        <v>2</v>
+      </c>
+      <c r="C91" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D91" s="31">
+        <v>2</v>
+      </c>
+      <c r="E91" s="31">
+        <v>4</v>
+      </c>
+      <c r="F91" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G91" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H91" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="30">
+        <v>3</v>
+      </c>
+      <c r="B92" s="31">
+        <v>2</v>
+      </c>
+      <c r="C92" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="31">
+        <v>3</v>
+      </c>
+      <c r="E92" s="31">
+        <v>4</v>
+      </c>
+      <c r="F92" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="G92" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H92" s="31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="30">
+        <v>3</v>
+      </c>
+      <c r="B93" s="31">
+        <v>2</v>
+      </c>
+      <c r="C93" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="31">
+        <v>3</v>
+      </c>
+      <c r="E93" s="31">
+        <v>4</v>
+      </c>
+      <c r="F93" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="G93" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H93" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="30">
+        <v>3</v>
+      </c>
+      <c r="B94" s="31">
+        <v>2</v>
+      </c>
+      <c r="C94" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" s="31">
+        <v>3</v>
+      </c>
+      <c r="E94" s="31">
+        <v>4</v>
+      </c>
+      <c r="F94" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="G94" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H94" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="30">
+        <v>3</v>
+      </c>
+      <c r="B95" s="31">
+        <v>2</v>
+      </c>
+      <c r="C95" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D95" s="31">
+        <v>4</v>
+      </c>
+      <c r="E95" s="31">
+        <v>4</v>
+      </c>
+      <c r="F95" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="G95" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H95" s="31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="30">
+        <v>3</v>
+      </c>
+      <c r="B96" s="31">
+        <v>2</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D96" s="31">
+        <v>4</v>
+      </c>
+      <c r="E96" s="31">
+        <v>4</v>
+      </c>
+      <c r="F96" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="G96" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H96" s="31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="30">
+        <v>3</v>
+      </c>
+      <c r="B97" s="31">
+        <v>2</v>
+      </c>
+      <c r="C97" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D97" s="31">
+        <v>4</v>
+      </c>
+      <c r="E97" s="31">
+        <v>4</v>
+      </c>
+      <c r="F97" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="G97" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H97" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="30">
+        <v>3</v>
+      </c>
+      <c r="B98" s="31">
+        <v>2</v>
+      </c>
+      <c r="C98" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D98" s="31">
+        <v>4</v>
+      </c>
+      <c r="E98" s="31">
+        <v>4</v>
+      </c>
+      <c r="F98" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="G98" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H98" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="30">
+        <v>3</v>
+      </c>
+      <c r="B99" s="31">
+        <v>2</v>
+      </c>
+      <c r="C99" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D99" s="31">
+        <v>4</v>
+      </c>
+      <c r="E99" s="31">
+        <v>4</v>
+      </c>
+      <c r="F99" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G99" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H99" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="30">
+        <v>3</v>
+      </c>
+      <c r="B100" s="31">
+        <v>2</v>
+      </c>
+      <c r="C100" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D100" s="31">
+        <v>4</v>
+      </c>
+      <c r="E100" s="31">
+        <v>4</v>
+      </c>
+      <c r="F100" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="G100" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H100" s="31">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6380,7 +7447,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -10005,6 +11072,1176 @@
       </c>
       <c r="H139" s="30">
         <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="25">
+        <v>4</v>
+      </c>
+      <c r="B140" s="33">
+        <v>1</v>
+      </c>
+      <c r="C140" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D140" s="33">
+        <v>1</v>
+      </c>
+      <c r="E140" s="33">
+        <v>2</v>
+      </c>
+      <c r="F140" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G140" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H140" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="25">
+        <v>4</v>
+      </c>
+      <c r="B141" s="33">
+        <v>1</v>
+      </c>
+      <c r="C141" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D141" s="33">
+        <v>1</v>
+      </c>
+      <c r="E141" s="33">
+        <v>2</v>
+      </c>
+      <c r="F141" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G141" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H141" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="25">
+        <v>4</v>
+      </c>
+      <c r="B142" s="33">
+        <v>1</v>
+      </c>
+      <c r="C142" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D142" s="33">
+        <v>1</v>
+      </c>
+      <c r="E142" s="33">
+        <v>2</v>
+      </c>
+      <c r="F142" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G142" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H142" s="33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="25">
+        <v>4</v>
+      </c>
+      <c r="B143" s="33">
+        <v>1</v>
+      </c>
+      <c r="C143" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D143" s="33">
+        <v>1</v>
+      </c>
+      <c r="E143" s="33">
+        <v>2</v>
+      </c>
+      <c r="F143" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G143" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H143" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="25">
+        <v>4</v>
+      </c>
+      <c r="B144" s="33">
+        <v>1</v>
+      </c>
+      <c r="C144" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D144" s="33">
+        <v>1</v>
+      </c>
+      <c r="E144" s="33">
+        <v>2</v>
+      </c>
+      <c r="F144" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G144" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H144" s="33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="25">
+        <v>4</v>
+      </c>
+      <c r="B145" s="25">
+        <v>1</v>
+      </c>
+      <c r="C145" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D145" s="38">
+        <v>2</v>
+      </c>
+      <c r="E145" s="38">
+        <v>4</v>
+      </c>
+      <c r="F145" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G145" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H145" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="25">
+        <v>4</v>
+      </c>
+      <c r="B146" s="25">
+        <v>1</v>
+      </c>
+      <c r="C146" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D146" s="38">
+        <v>2</v>
+      </c>
+      <c r="E146" s="38">
+        <v>4</v>
+      </c>
+      <c r="F146" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="G146" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H146" s="38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="25">
+        <v>4</v>
+      </c>
+      <c r="B147" s="25">
+        <v>1</v>
+      </c>
+      <c r="C147" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D147" s="38">
+        <v>2</v>
+      </c>
+      <c r="E147" s="38">
+        <v>4</v>
+      </c>
+      <c r="F147" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G147" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H147" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="25">
+        <v>4</v>
+      </c>
+      <c r="B148" s="25">
+        <v>1</v>
+      </c>
+      <c r="C148" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D148" s="38">
+        <v>3</v>
+      </c>
+      <c r="E148" s="38">
+        <v>4</v>
+      </c>
+      <c r="F148" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G148" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H148" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="25">
+        <v>4</v>
+      </c>
+      <c r="B149" s="25">
+        <v>1</v>
+      </c>
+      <c r="C149" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D149" s="38">
+        <v>3</v>
+      </c>
+      <c r="E149" s="38">
+        <v>4</v>
+      </c>
+      <c r="F149" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="G149" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H149" s="38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="25">
+        <v>4</v>
+      </c>
+      <c r="B150" s="25">
+        <v>1</v>
+      </c>
+      <c r="C150" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" s="38">
+        <v>3</v>
+      </c>
+      <c r="E150" s="38">
+        <v>4</v>
+      </c>
+      <c r="F150" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G150" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H150" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="25">
+        <v>4</v>
+      </c>
+      <c r="B151" s="25">
+        <v>1</v>
+      </c>
+      <c r="C151" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D151" s="38">
+        <v>4</v>
+      </c>
+      <c r="E151" s="38">
+        <v>3</v>
+      </c>
+      <c r="F151" s="38" t="s">
+        <v>332</v>
+      </c>
+      <c r="G151" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H151" s="38" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="25">
+        <v>4</v>
+      </c>
+      <c r="B152" s="25">
+        <v>1</v>
+      </c>
+      <c r="C152" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D152" s="38">
+        <v>4</v>
+      </c>
+      <c r="E152" s="38">
+        <v>3</v>
+      </c>
+      <c r="F152" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="G152" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H152" s="38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="25">
+        <v>4</v>
+      </c>
+      <c r="B153" s="25">
+        <v>1</v>
+      </c>
+      <c r="C153" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D153" s="38">
+        <v>4</v>
+      </c>
+      <c r="E153" s="38">
+        <v>3</v>
+      </c>
+      <c r="F153" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G153" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H153" s="38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="25">
+        <v>4</v>
+      </c>
+      <c r="B154" s="16">
+        <v>2</v>
+      </c>
+      <c r="C154" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D154" s="14">
+        <v>1</v>
+      </c>
+      <c r="E154" s="14">
+        <v>2</v>
+      </c>
+      <c r="F154" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G154" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H154" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="25">
+        <v>4</v>
+      </c>
+      <c r="B155" s="16">
+        <v>2</v>
+      </c>
+      <c r="C155" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D155" s="14">
+        <v>1</v>
+      </c>
+      <c r="E155" s="14">
+        <v>2</v>
+      </c>
+      <c r="F155" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G155" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H155" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="25">
+        <v>4</v>
+      </c>
+      <c r="B156" s="16">
+        <v>2</v>
+      </c>
+      <c r="C156" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D156" s="14">
+        <v>1</v>
+      </c>
+      <c r="E156" s="14">
+        <v>2</v>
+      </c>
+      <c r="F156" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G156" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H156" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="25">
+        <v>4</v>
+      </c>
+      <c r="B157" s="16">
+        <v>2</v>
+      </c>
+      <c r="C157" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D157" s="14">
+        <v>1</v>
+      </c>
+      <c r="E157" s="14">
+        <v>2</v>
+      </c>
+      <c r="F157" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G157" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H157" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="25">
+        <v>4</v>
+      </c>
+      <c r="B158" s="16">
+        <v>2</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D158" s="14">
+        <v>1</v>
+      </c>
+      <c r="E158" s="14">
+        <v>2</v>
+      </c>
+      <c r="F158" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G158" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H158" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="25">
+        <v>4</v>
+      </c>
+      <c r="B159" s="38">
+        <v>2</v>
+      </c>
+      <c r="C159" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D159" s="38">
+        <v>2</v>
+      </c>
+      <c r="E159" s="38">
+        <v>4</v>
+      </c>
+      <c r="F159" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="G159" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H159" s="38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="25">
+        <v>4</v>
+      </c>
+      <c r="B160" s="38">
+        <v>2</v>
+      </c>
+      <c r="C160" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D160" s="38">
+        <v>2</v>
+      </c>
+      <c r="E160" s="38">
+        <v>4</v>
+      </c>
+      <c r="F160" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G160" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H160" s="38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="25">
+        <v>4</v>
+      </c>
+      <c r="B161" s="38">
+        <v>2</v>
+      </c>
+      <c r="C161" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D161" s="38">
+        <v>2</v>
+      </c>
+      <c r="E161" s="38">
+        <v>4</v>
+      </c>
+      <c r="F161" s="38" t="s">
+        <v>239</v>
+      </c>
+      <c r="G161" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H161" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="25">
+        <v>4</v>
+      </c>
+      <c r="B162" s="38">
+        <v>2</v>
+      </c>
+      <c r="C162" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D162" s="38">
+        <v>3</v>
+      </c>
+      <c r="E162" s="38">
+        <v>4</v>
+      </c>
+      <c r="F162" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G162" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H162" s="38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="25">
+        <v>4</v>
+      </c>
+      <c r="B163" s="38">
+        <v>2</v>
+      </c>
+      <c r="C163" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D163" s="38">
+        <v>3</v>
+      </c>
+      <c r="E163" s="38">
+        <v>4</v>
+      </c>
+      <c r="F163" s="38" t="s">
+        <v>415</v>
+      </c>
+      <c r="G163" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H163" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="25">
+        <v>4</v>
+      </c>
+      <c r="B164" s="38">
+        <v>2</v>
+      </c>
+      <c r="C164" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D164" s="38">
+        <v>3</v>
+      </c>
+      <c r="E164" s="38">
+        <v>4</v>
+      </c>
+      <c r="F164" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="G164" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H164" s="38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="25">
+        <v>4</v>
+      </c>
+      <c r="B165" s="38">
+        <v>2</v>
+      </c>
+      <c r="C165" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D165" s="38">
+        <v>4</v>
+      </c>
+      <c r="E165" s="38">
+        <v>4</v>
+      </c>
+      <c r="F165" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G165" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H165" s="38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="25">
+        <v>4</v>
+      </c>
+      <c r="B166" s="38">
+        <v>2</v>
+      </c>
+      <c r="C166" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D166" s="38">
+        <v>4</v>
+      </c>
+      <c r="E166" s="38">
+        <v>4</v>
+      </c>
+      <c r="F166" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G166" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H166" s="38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="25">
+        <v>4</v>
+      </c>
+      <c r="B167" s="38">
+        <v>2</v>
+      </c>
+      <c r="C167" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D167" s="38">
+        <v>4</v>
+      </c>
+      <c r="E167" s="38">
+        <v>4</v>
+      </c>
+      <c r="F167" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="G167" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H167" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="25">
+        <v>4</v>
+      </c>
+      <c r="B168" s="38">
+        <v>2</v>
+      </c>
+      <c r="C168" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D168" s="38">
+        <v>4</v>
+      </c>
+      <c r="E168" s="38">
+        <v>4</v>
+      </c>
+      <c r="F168" s="38" t="s">
+        <v>423</v>
+      </c>
+      <c r="G168" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H168" s="38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="25">
+        <v>4</v>
+      </c>
+      <c r="B169" s="38">
+        <v>2</v>
+      </c>
+      <c r="C169" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D169" s="38">
+        <v>4</v>
+      </c>
+      <c r="E169" s="38">
+        <v>4</v>
+      </c>
+      <c r="F169" s="38" t="s">
+        <v>390</v>
+      </c>
+      <c r="G169" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H169" s="38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="25">
+        <v>4</v>
+      </c>
+      <c r="B170" s="38">
+        <v>2</v>
+      </c>
+      <c r="C170" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D170" s="38">
+        <v>4</v>
+      </c>
+      <c r="E170" s="38">
+        <v>4</v>
+      </c>
+      <c r="F170" s="38" t="s">
+        <v>410</v>
+      </c>
+      <c r="G170" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H170" s="38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="25">
+        <v>4</v>
+      </c>
+      <c r="B171" s="18">
+        <v>3</v>
+      </c>
+      <c r="C171" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D171" s="17">
+        <v>1</v>
+      </c>
+      <c r="E171" s="17">
+        <v>2</v>
+      </c>
+      <c r="F171" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G171" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H171" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="25">
+        <v>4</v>
+      </c>
+      <c r="B172" s="18">
+        <v>3</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D172" s="17">
+        <v>1</v>
+      </c>
+      <c r="E172" s="17">
+        <v>2</v>
+      </c>
+      <c r="F172" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G172" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H172" s="18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="25">
+        <v>4</v>
+      </c>
+      <c r="B173" s="18">
+        <v>3</v>
+      </c>
+      <c r="C173" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D173" s="17">
+        <v>1</v>
+      </c>
+      <c r="E173" s="17">
+        <v>2</v>
+      </c>
+      <c r="F173" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G173" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H173" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="25">
+        <v>4</v>
+      </c>
+      <c r="B174" s="18">
+        <v>3</v>
+      </c>
+      <c r="C174" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D174" s="17">
+        <v>1</v>
+      </c>
+      <c r="E174" s="17">
+        <v>2</v>
+      </c>
+      <c r="F174" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G174" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H174" s="18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="25">
+        <v>4</v>
+      </c>
+      <c r="B175" s="18">
+        <v>3</v>
+      </c>
+      <c r="C175" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D175" s="17">
+        <v>1</v>
+      </c>
+      <c r="E175" s="17">
+        <v>2</v>
+      </c>
+      <c r="F175" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G175" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H175" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="25">
+        <v>4</v>
+      </c>
+      <c r="B176" s="38">
+        <v>3</v>
+      </c>
+      <c r="C176" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D176" s="25">
+        <v>2</v>
+      </c>
+      <c r="E176" s="25">
+        <v>4</v>
+      </c>
+      <c r="F176" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="G176" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H176" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="25">
+        <v>4</v>
+      </c>
+      <c r="B177" s="38">
+        <v>3</v>
+      </c>
+      <c r="C177" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D177" s="25">
+        <v>2</v>
+      </c>
+      <c r="E177" s="25">
+        <v>4</v>
+      </c>
+      <c r="F177" s="38" t="s">
+        <v>424</v>
+      </c>
+      <c r="G177" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H177" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="25">
+        <v>4</v>
+      </c>
+      <c r="B178" s="38">
+        <v>3</v>
+      </c>
+      <c r="C178" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D178" s="25">
+        <v>2</v>
+      </c>
+      <c r="E178" s="25">
+        <v>4</v>
+      </c>
+      <c r="F178" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="G178" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H178" s="38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="25">
+        <v>4</v>
+      </c>
+      <c r="B179" s="38">
+        <v>3</v>
+      </c>
+      <c r="C179" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D179" s="25">
+        <v>3</v>
+      </c>
+      <c r="E179" s="25">
+        <v>4</v>
+      </c>
+      <c r="F179" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G179" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H179" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="25">
+        <v>4</v>
+      </c>
+      <c r="B180" s="38">
+        <v>3</v>
+      </c>
+      <c r="C180" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D180" s="25">
+        <v>3</v>
+      </c>
+      <c r="E180" s="25">
+        <v>4</v>
+      </c>
+      <c r="F180" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="G180" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H180" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="25">
+        <v>4</v>
+      </c>
+      <c r="B181" s="38">
+        <v>3</v>
+      </c>
+      <c r="C181" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D181" s="25">
+        <v>3</v>
+      </c>
+      <c r="E181" s="25">
+        <v>4</v>
+      </c>
+      <c r="F181" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G181" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H181" s="25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="25">
+        <v>4</v>
+      </c>
+      <c r="B182" s="38">
+        <v>3</v>
+      </c>
+      <c r="C182" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D182" s="25">
+        <v>4</v>
+      </c>
+      <c r="E182" s="25">
+        <v>4</v>
+      </c>
+      <c r="F182" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="G182" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H182" s="25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="25">
+        <v>4</v>
+      </c>
+      <c r="B183" s="38">
+        <v>3</v>
+      </c>
+      <c r="C183" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D183" s="25">
+        <v>4</v>
+      </c>
+      <c r="E183" s="25">
+        <v>4</v>
+      </c>
+      <c r="F183" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G183" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H183" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="25">
+        <v>4</v>
+      </c>
+      <c r="B184" s="38">
+        <v>3</v>
+      </c>
+      <c r="C184" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D184" s="25">
+        <v>4</v>
+      </c>
+      <c r="E184" s="25">
+        <v>4</v>
+      </c>
+      <c r="F184" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G184" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H184" s="25">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -20068,7 +22305,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F357C59-977B-4591-AD82-2B7621F6CA1A}">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -23319,7 +25556,16 @@
         <v>377</v>
       </c>
     </row>
-    <row r="129" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="30">
+        <v>3</v>
+      </c>
+      <c r="B129" s="31">
+        <v>4</v>
+      </c>
+      <c r="C129" s="31" t="s">
+        <v>40</v>
+      </c>
       <c r="F129" s="31" t="s">
         <v>376</v>
       </c>
@@ -23327,9 +25573,736 @@
         <v>378</v>
       </c>
     </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="25">
+        <v>4</v>
+      </c>
+      <c r="B130" s="33">
+        <v>1</v>
+      </c>
+      <c r="C130" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="33">
+        <v>1</v>
+      </c>
+      <c r="E130" s="33">
+        <v>2</v>
+      </c>
+      <c r="F130" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G130" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H130" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I130" s="37"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="25">
+        <v>4</v>
+      </c>
+      <c r="B131" s="33">
+        <v>1</v>
+      </c>
+      <c r="C131" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D131" s="33">
+        <v>1</v>
+      </c>
+      <c r="E131" s="33">
+        <v>2</v>
+      </c>
+      <c r="F131" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G131" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H131" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I131" s="37"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="25">
+        <v>4</v>
+      </c>
+      <c r="B132" s="33">
+        <v>1</v>
+      </c>
+      <c r="C132" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="33">
+        <v>1</v>
+      </c>
+      <c r="E132" s="33">
+        <v>2</v>
+      </c>
+      <c r="F132" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G132" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H132" s="33">
+        <v>10</v>
+      </c>
+      <c r="I132" s="37"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="25">
+        <v>4</v>
+      </c>
+      <c r="B133" s="33">
+        <v>1</v>
+      </c>
+      <c r="C133" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D133" s="33">
+        <v>1</v>
+      </c>
+      <c r="E133" s="33">
+        <v>2</v>
+      </c>
+      <c r="F133" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G133" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H133" s="33">
+        <v>8</v>
+      </c>
+      <c r="I133" s="37"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="25">
+        <v>4</v>
+      </c>
+      <c r="B134" s="33">
+        <v>1</v>
+      </c>
+      <c r="C134" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D134" s="33">
+        <v>1</v>
+      </c>
+      <c r="E134" s="33">
+        <v>2</v>
+      </c>
+      <c r="F134" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="G134" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="H134" s="33">
+        <v>8</v>
+      </c>
+      <c r="I134" s="37"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="25">
+        <v>4</v>
+      </c>
+      <c r="B135" s="25">
+        <v>1</v>
+      </c>
+      <c r="C135" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D135" s="25">
+        <v>1</v>
+      </c>
+      <c r="E135" s="25">
+        <v>2</v>
+      </c>
+      <c r="F135" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="G135" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H135" s="38">
+        <v>8</v>
+      </c>
+      <c r="I135" s="37"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="25">
+        <v>4</v>
+      </c>
+      <c r="B136" s="25">
+        <v>1</v>
+      </c>
+      <c r="C136" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D136" s="38"/>
+      <c r="E136" s="38"/>
+      <c r="F136" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G136" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H136" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I136" s="37"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="25">
+        <v>4</v>
+      </c>
+      <c r="B137" s="25">
+        <v>1</v>
+      </c>
+      <c r="C137" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" s="38"/>
+      <c r="E137" s="38"/>
+      <c r="F137" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="G137" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H137" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I137" s="37"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="25">
+        <v>4</v>
+      </c>
+      <c r="B138" s="25">
+        <v>1</v>
+      </c>
+      <c r="C138" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" s="38"/>
+      <c r="E138" s="38"/>
+      <c r="F138" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G138" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H138" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="I138" s="37"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="25">
+        <v>4</v>
+      </c>
+      <c r="B139" s="25">
+        <v>1</v>
+      </c>
+      <c r="C139" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" s="38"/>
+      <c r="E139" s="38"/>
+      <c r="F139" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G139" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H139" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I139" s="37"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="25">
+        <v>4</v>
+      </c>
+      <c r="B140" s="25">
+        <v>1</v>
+      </c>
+      <c r="C140" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D140" s="38"/>
+      <c r="E140" s="38"/>
+      <c r="F140" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="G140" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H140" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="I140" s="37"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="25">
+        <v>4</v>
+      </c>
+      <c r="B141" s="25">
+        <v>1</v>
+      </c>
+      <c r="C141" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="38"/>
+      <c r="E141" s="38"/>
+      <c r="F141" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="G141" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H141" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="I141" s="37"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="25">
+        <v>4</v>
+      </c>
+      <c r="B142" s="25">
+        <v>1</v>
+      </c>
+      <c r="C142" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" s="38"/>
+      <c r="E142" s="38"/>
+      <c r="F142" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="G142" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H142" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I142" s="37"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="25">
+        <v>4</v>
+      </c>
+      <c r="B143" s="25">
+        <v>1</v>
+      </c>
+      <c r="C143" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D143" s="38">
+        <v>2</v>
+      </c>
+      <c r="E143" s="38">
+        <v>3</v>
+      </c>
+      <c r="F143" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="G143" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H143" s="38">
+        <v>20</v>
+      </c>
+      <c r="I143" s="37"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="25">
+        <v>4</v>
+      </c>
+      <c r="B144" s="25">
+        <v>1</v>
+      </c>
+      <c r="C144" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D144" s="38">
+        <v>2</v>
+      </c>
+      <c r="E144" s="38">
+        <v>3</v>
+      </c>
+      <c r="F144" s="38" t="s">
+        <v>416</v>
+      </c>
+      <c r="G144" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H144" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I144" s="37"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="25">
+        <v>4</v>
+      </c>
+      <c r="B145" s="25">
+        <v>1</v>
+      </c>
+      <c r="C145" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D145" s="38">
+        <v>2</v>
+      </c>
+      <c r="E145" s="38">
+        <v>3</v>
+      </c>
+      <c r="F145" s="38" t="s">
+        <v>417</v>
+      </c>
+      <c r="G145" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H145" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I145" s="37"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="25">
+        <v>4</v>
+      </c>
+      <c r="B146" s="16">
+        <v>2</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="14">
+        <v>1</v>
+      </c>
+      <c r="E146" s="14">
+        <v>2</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G146" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H146" s="16">
+        <v>10</v>
+      </c>
+      <c r="I146" s="37"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="25">
+        <v>4</v>
+      </c>
+      <c r="B147" s="16">
+        <v>2</v>
+      </c>
+      <c r="C147" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="14">
+        <v>1</v>
+      </c>
+      <c r="E147" s="14">
+        <v>2</v>
+      </c>
+      <c r="F147" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G147" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H147" s="16">
+        <v>10</v>
+      </c>
+      <c r="I147" s="37"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="25">
+        <v>4</v>
+      </c>
+      <c r="B148" s="16">
+        <v>2</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D148" s="14">
+        <v>1</v>
+      </c>
+      <c r="E148" s="14">
+        <v>2</v>
+      </c>
+      <c r="F148" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G148" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H148" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I148" s="37"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="25">
+        <v>4</v>
+      </c>
+      <c r="B149" s="16">
+        <v>2</v>
+      </c>
+      <c r="C149" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D149" s="14">
+        <v>1</v>
+      </c>
+      <c r="E149" s="14">
+        <v>2</v>
+      </c>
+      <c r="F149" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G149" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H149" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I149" s="37"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="25">
+        <v>4</v>
+      </c>
+      <c r="B150" s="16">
+        <v>2</v>
+      </c>
+      <c r="C150" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D150" s="14">
+        <v>1</v>
+      </c>
+      <c r="E150" s="14">
+        <v>2</v>
+      </c>
+      <c r="F150" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G150" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H150" s="16">
+        <v>8</v>
+      </c>
+      <c r="I150" s="37"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="25">
+        <v>4</v>
+      </c>
+      <c r="B151" s="38">
+        <v>2</v>
+      </c>
+      <c r="C151" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D151" s="25">
+        <v>1</v>
+      </c>
+      <c r="E151" s="25">
+        <v>2</v>
+      </c>
+      <c r="F151" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G151" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H151" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I151" s="37"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="25">
+        <v>4</v>
+      </c>
+      <c r="B152" s="38">
+        <v>2</v>
+      </c>
+      <c r="C152" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D152" s="38"/>
+      <c r="E152" s="38"/>
+      <c r="F152" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G152" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H152" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I152" s="37"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="25">
+        <v>4</v>
+      </c>
+      <c r="B153" s="38">
+        <v>2</v>
+      </c>
+      <c r="C153" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="38"/>
+      <c r="E153" s="38"/>
+      <c r="F153" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="G153" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H153" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="I153" s="37"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="25">
+        <v>4</v>
+      </c>
+      <c r="B154" s="38">
+        <v>2</v>
+      </c>
+      <c r="C154" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="38"/>
+      <c r="E154" s="38"/>
+      <c r="F154" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="G154" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H154" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I154" s="37"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="25">
+        <v>4</v>
+      </c>
+      <c r="B155" s="38">
+        <v>2</v>
+      </c>
+      <c r="C155" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D155" s="38"/>
+      <c r="E155" s="38"/>
+      <c r="F155" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="G155" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H155" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I155" s="37"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="25">
+        <v>4</v>
+      </c>
+      <c r="B156" s="38">
+        <v>2</v>
+      </c>
+      <c r="C156" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D156" s="38"/>
+      <c r="E156" s="38"/>
+      <c r="F156" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="G156" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H156" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="I156" s="37"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="25">
+        <v>4</v>
+      </c>
+      <c r="B157" s="38">
+        <v>2</v>
+      </c>
+      <c r="C157" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D157" s="38"/>
+      <c r="E157" s="38"/>
+      <c r="F157" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="G157" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H157" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="I157" s="37"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="25">
+        <v>4</v>
+      </c>
+      <c r="B158" s="38">
+        <v>2</v>
+      </c>
+      <c r="C158" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D158" s="38"/>
+      <c r="E158" s="38"/>
+      <c r="F158" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G158" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H158" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I158" s="37"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C129" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C158" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23339,7 +26312,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -26794,6 +29767,1061 @@
       </c>
       <c r="I127" s="32"/>
     </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="34">
+        <v>4</v>
+      </c>
+      <c r="B128" s="33">
+        <v>1</v>
+      </c>
+      <c r="C128" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D128" s="33">
+        <v>1</v>
+      </c>
+      <c r="E128" s="33">
+        <v>2</v>
+      </c>
+      <c r="F128" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G128" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H128" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I128" s="35"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="34">
+        <v>4</v>
+      </c>
+      <c r="B129" s="33">
+        <v>1</v>
+      </c>
+      <c r="C129" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D129" s="33">
+        <v>1</v>
+      </c>
+      <c r="E129" s="33">
+        <v>2</v>
+      </c>
+      <c r="F129" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G129" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H129" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I129" s="35"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="34">
+        <v>4</v>
+      </c>
+      <c r="B130" s="33">
+        <v>1</v>
+      </c>
+      <c r="C130" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="33">
+        <v>1</v>
+      </c>
+      <c r="E130" s="33">
+        <v>2</v>
+      </c>
+      <c r="F130" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G130" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H130" s="33">
+        <v>10</v>
+      </c>
+      <c r="I130" s="35"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="34">
+        <v>4</v>
+      </c>
+      <c r="B131" s="33">
+        <v>1</v>
+      </c>
+      <c r="C131" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D131" s="33">
+        <v>1</v>
+      </c>
+      <c r="E131" s="33">
+        <v>2</v>
+      </c>
+      <c r="F131" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G131" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H131" s="33">
+        <v>8</v>
+      </c>
+      <c r="I131" s="35"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="34">
+        <v>4</v>
+      </c>
+      <c r="B132" s="33">
+        <v>1</v>
+      </c>
+      <c r="C132" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="33">
+        <v>1</v>
+      </c>
+      <c r="E132" s="33">
+        <v>2</v>
+      </c>
+      <c r="F132" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G132" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H132" s="33">
+        <v>8</v>
+      </c>
+      <c r="I132" s="35"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="34">
+        <v>4</v>
+      </c>
+      <c r="B133" s="34">
+        <v>1</v>
+      </c>
+      <c r="C133" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D133" s="36"/>
+      <c r="E133" s="36"/>
+      <c r="F133" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="G133" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H133" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="I133" s="35"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="34">
+        <v>4</v>
+      </c>
+      <c r="B134" s="34">
+        <v>1</v>
+      </c>
+      <c r="C134" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D134" s="36"/>
+      <c r="E134" s="36"/>
+      <c r="F134" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="G134" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H134" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="I134" s="35"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="34">
+        <v>4</v>
+      </c>
+      <c r="B135" s="34">
+        <v>1</v>
+      </c>
+      <c r="C135" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" s="36"/>
+      <c r="E135" s="36"/>
+      <c r="F135" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G135" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H135" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="I135" s="35"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="34">
+        <v>4</v>
+      </c>
+      <c r="B136" s="34">
+        <v>1</v>
+      </c>
+      <c r="C136" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="G136" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H136" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="I136" s="35"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="34">
+        <v>4</v>
+      </c>
+      <c r="B137" s="34">
+        <v>1</v>
+      </c>
+      <c r="C137" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" s="36"/>
+      <c r="E137" s="36"/>
+      <c r="F137" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="G137" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H137" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I137" s="35"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="34">
+        <v>4</v>
+      </c>
+      <c r="B138" s="34">
+        <v>1</v>
+      </c>
+      <c r="C138" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="G138" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H138" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I138" s="35"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="34">
+        <v>4</v>
+      </c>
+      <c r="B139" s="34">
+        <v>1</v>
+      </c>
+      <c r="C139" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D139" s="36">
+        <v>2</v>
+      </c>
+      <c r="E139" s="36">
+        <v>3</v>
+      </c>
+      <c r="F139" s="36" t="s">
+        <v>383</v>
+      </c>
+      <c r="G139" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H139" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I139" s="35"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="34">
+        <v>4</v>
+      </c>
+      <c r="B140" s="34">
+        <v>1</v>
+      </c>
+      <c r="C140" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D140" s="36">
+        <v>2</v>
+      </c>
+      <c r="E140" s="36">
+        <v>3</v>
+      </c>
+      <c r="F140" s="36" t="s">
+        <v>382</v>
+      </c>
+      <c r="G140" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H140" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I140" s="35"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="34">
+        <v>4</v>
+      </c>
+      <c r="B141" s="34">
+        <v>1</v>
+      </c>
+      <c r="C141" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D141" s="36">
+        <v>2</v>
+      </c>
+      <c r="E141" s="36">
+        <v>3</v>
+      </c>
+      <c r="F141" s="36" t="s">
+        <v>384</v>
+      </c>
+      <c r="G141" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H141" s="36">
+        <v>20</v>
+      </c>
+      <c r="I141" s="35"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="34">
+        <v>4</v>
+      </c>
+      <c r="B142" s="16">
+        <v>2</v>
+      </c>
+      <c r="C142" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D142" s="14">
+        <v>1</v>
+      </c>
+      <c r="E142" s="14">
+        <v>2</v>
+      </c>
+      <c r="F142" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G142" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H142" s="16">
+        <v>10</v>
+      </c>
+      <c r="I142" s="35"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="34">
+        <v>4</v>
+      </c>
+      <c r="B143" s="16">
+        <v>2</v>
+      </c>
+      <c r="C143" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D143" s="14">
+        <v>1</v>
+      </c>
+      <c r="E143" s="14">
+        <v>2</v>
+      </c>
+      <c r="F143" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G143" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H143" s="16">
+        <v>10</v>
+      </c>
+      <c r="I143" s="35"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="34">
+        <v>4</v>
+      </c>
+      <c r="B144" s="16">
+        <v>2</v>
+      </c>
+      <c r="C144" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D144" s="14">
+        <v>1</v>
+      </c>
+      <c r="E144" s="14">
+        <v>2</v>
+      </c>
+      <c r="F144" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G144" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H144" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I144" s="35"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="34">
+        <v>4</v>
+      </c>
+      <c r="B145" s="16">
+        <v>2</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="14">
+        <v>1</v>
+      </c>
+      <c r="E145" s="14">
+        <v>2</v>
+      </c>
+      <c r="F145" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G145" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H145" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I145" s="35"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="34">
+        <v>4</v>
+      </c>
+      <c r="B146" s="16">
+        <v>2</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="14">
+        <v>1</v>
+      </c>
+      <c r="E146" s="14">
+        <v>2</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G146" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H146" s="16">
+        <v>10</v>
+      </c>
+      <c r="I146" s="35"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="34">
+        <v>4</v>
+      </c>
+      <c r="B147" s="36">
+        <v>2</v>
+      </c>
+      <c r="C147" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D147" s="36"/>
+      <c r="E147" s="36"/>
+      <c r="F147" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="G147" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H147" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="I147" s="35"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="34">
+        <v>4</v>
+      </c>
+      <c r="B148" s="36">
+        <v>2</v>
+      </c>
+      <c r="C148" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36" t="s">
+        <v>385</v>
+      </c>
+      <c r="G148" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H148" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="I148" s="35"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="34">
+        <v>4</v>
+      </c>
+      <c r="B149" s="36">
+        <v>2</v>
+      </c>
+      <c r="C149" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D149" s="36"/>
+      <c r="E149" s="36"/>
+      <c r="F149" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="G149" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H149" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="I149" s="35"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="34">
+        <v>4</v>
+      </c>
+      <c r="B150" s="36">
+        <v>2</v>
+      </c>
+      <c r="C150" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" s="36"/>
+      <c r="E150" s="36"/>
+      <c r="F150" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G150" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H150" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="I150" s="35"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="34">
+        <v>4</v>
+      </c>
+      <c r="B151" s="36">
+        <v>2</v>
+      </c>
+      <c r="C151" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" s="36"/>
+      <c r="E151" s="36"/>
+      <c r="F151" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="G151" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H151" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I151" s="35"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="34">
+        <v>4</v>
+      </c>
+      <c r="B152" s="36">
+        <v>2</v>
+      </c>
+      <c r="C152" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D152" s="36">
+        <v>2</v>
+      </c>
+      <c r="E152" s="36">
+        <v>4</v>
+      </c>
+      <c r="F152" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="G152" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H152" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="I152" s="35"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="34">
+        <v>4</v>
+      </c>
+      <c r="B153" s="36">
+        <v>2</v>
+      </c>
+      <c r="C153" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="36">
+        <v>2</v>
+      </c>
+      <c r="E153" s="36">
+        <v>4</v>
+      </c>
+      <c r="F153" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="G153" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H153" s="36">
+        <v>10</v>
+      </c>
+      <c r="I153" s="35"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="34">
+        <v>4</v>
+      </c>
+      <c r="B154" s="18">
+        <v>3</v>
+      </c>
+      <c r="C154" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D154" s="17">
+        <v>1</v>
+      </c>
+      <c r="E154" s="17">
+        <v>2</v>
+      </c>
+      <c r="F154" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G154" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H154" s="18">
+        <v>10</v>
+      </c>
+      <c r="I154" s="35"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="34">
+        <v>4</v>
+      </c>
+      <c r="B155" s="18">
+        <v>3</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D155" s="17">
+        <v>1</v>
+      </c>
+      <c r="E155" s="17">
+        <v>2</v>
+      </c>
+      <c r="F155" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G155" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H155" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="I155" s="35"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="34">
+        <v>4</v>
+      </c>
+      <c r="B156" s="18">
+        <v>3</v>
+      </c>
+      <c r="C156" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D156" s="17">
+        <v>1</v>
+      </c>
+      <c r="E156" s="17">
+        <v>2</v>
+      </c>
+      <c r="F156" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G156" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H156" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I156" s="35"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="34">
+        <v>4</v>
+      </c>
+      <c r="B157" s="18">
+        <v>3</v>
+      </c>
+      <c r="C157" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D157" s="17">
+        <v>1</v>
+      </c>
+      <c r="E157" s="17">
+        <v>2</v>
+      </c>
+      <c r="F157" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G157" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H157" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I157" s="35"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="34">
+        <v>4</v>
+      </c>
+      <c r="B158" s="18">
+        <v>3</v>
+      </c>
+      <c r="C158" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D158" s="17">
+        <v>1</v>
+      </c>
+      <c r="E158" s="17">
+        <v>2</v>
+      </c>
+      <c r="F158" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G158" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H158" s="18">
+        <v>8</v>
+      </c>
+      <c r="I158" s="35"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="34">
+        <v>4</v>
+      </c>
+      <c r="B159" s="36">
+        <v>3</v>
+      </c>
+      <c r="C159" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="G159" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H159" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="I159" s="35"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="34">
+        <v>4</v>
+      </c>
+      <c r="B160" s="36">
+        <v>3</v>
+      </c>
+      <c r="C160" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="D160" s="36"/>
+      <c r="E160" s="36"/>
+      <c r="F160" s="36" t="s">
+        <v>388</v>
+      </c>
+      <c r="G160" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="H160" s="36" t="s">
+        <v>387</v>
+      </c>
+      <c r="I160" s="35"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="34">
+        <v>4</v>
+      </c>
+      <c r="B161" s="36">
+        <v>3</v>
+      </c>
+      <c r="C161" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D161" s="36">
+        <v>2</v>
+      </c>
+      <c r="E161" s="36">
+        <v>4</v>
+      </c>
+      <c r="F161" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G161" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H161" s="36">
+        <v>10</v>
+      </c>
+      <c r="I161" s="35"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="34">
+        <v>4</v>
+      </c>
+      <c r="B162" s="36">
+        <v>3</v>
+      </c>
+      <c r="C162" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D162" s="36">
+        <v>2</v>
+      </c>
+      <c r="E162" s="36">
+        <v>4</v>
+      </c>
+      <c r="F162" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="G162" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H162" s="36">
+        <v>10</v>
+      </c>
+      <c r="I162" s="35"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="34">
+        <v>4</v>
+      </c>
+      <c r="B163" s="36">
+        <v>3</v>
+      </c>
+      <c r="C163" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D163" s="36">
+        <v>2</v>
+      </c>
+      <c r="E163" s="36">
+        <v>4</v>
+      </c>
+      <c r="F163" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="G163" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H163" s="36">
+        <v>20</v>
+      </c>
+      <c r="I163" s="35"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="34">
+        <v>4</v>
+      </c>
+      <c r="B164" s="36">
+        <v>3</v>
+      </c>
+      <c r="C164" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D164" s="36">
+        <v>3</v>
+      </c>
+      <c r="E164" s="36">
+        <v>4</v>
+      </c>
+      <c r="F164" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G164" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H164" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="I164" s="35"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="34">
+        <v>4</v>
+      </c>
+      <c r="B165" s="36">
+        <v>3</v>
+      </c>
+      <c r="C165" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" s="36">
+        <v>3</v>
+      </c>
+      <c r="E165" s="36">
+        <v>4</v>
+      </c>
+      <c r="F165" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="G165" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H165" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="I165" s="35"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="34">
+        <v>4</v>
+      </c>
+      <c r="B166" s="36">
+        <v>3</v>
+      </c>
+      <c r="C166" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" s="36">
+        <v>3</v>
+      </c>
+      <c r="E166" s="36">
+        <v>4</v>
+      </c>
+      <c r="F166" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="G166" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H166" s="36">
+        <v>20</v>
+      </c>
+      <c r="I166" s="35"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="34">
+        <v>4</v>
+      </c>
+      <c r="B167" s="36">
+        <v>3</v>
+      </c>
+      <c r="C167" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="36">
+        <v>4</v>
+      </c>
+      <c r="E167" s="36">
+        <v>4</v>
+      </c>
+      <c r="F167" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="G167" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H167" s="36">
+        <v>6</v>
+      </c>
+      <c r="I167" s="35"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="34">
+        <v>4</v>
+      </c>
+      <c r="B168" s="36">
+        <v>3</v>
+      </c>
+      <c r="C168" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" s="36">
+        <v>4</v>
+      </c>
+      <c r="E168" s="36">
+        <v>4</v>
+      </c>
+      <c r="F168" s="36" t="s">
+        <v>390</v>
+      </c>
+      <c r="G168" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H168" s="36">
+        <v>5</v>
+      </c>
+      <c r="I168" s="35"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C297" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -26806,7 +30834,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -28741,10 +32769,1003 @@
       <c r="I73" s="19"/>
       <c r="J73" s="19"/>
     </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="30">
+        <v>3</v>
+      </c>
+      <c r="B74" s="8">
+        <v>1</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D74" s="8">
+        <v>1</v>
+      </c>
+      <c r="E74" s="8">
+        <v>2</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I74" s="32"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="30">
+        <v>3</v>
+      </c>
+      <c r="B75" s="8">
+        <v>1</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="8">
+        <v>1</v>
+      </c>
+      <c r="E75" s="8">
+        <v>2</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I75" s="32"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="30">
+        <v>3</v>
+      </c>
+      <c r="B76" s="8">
+        <v>1</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="8">
+        <v>1</v>
+      </c>
+      <c r="E76" s="8">
+        <v>2</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H76" s="8">
+        <v>10</v>
+      </c>
+      <c r="I76" s="32"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="30">
+        <v>3</v>
+      </c>
+      <c r="B77" s="8">
+        <v>1</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="8">
+        <v>1</v>
+      </c>
+      <c r="E77" s="8">
+        <v>2</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H77" s="8">
+        <v>8</v>
+      </c>
+      <c r="I77" s="32"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="30">
+        <v>3</v>
+      </c>
+      <c r="B78" s="8">
+        <v>1</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78" s="8">
+        <v>1</v>
+      </c>
+      <c r="E78" s="8">
+        <v>2</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H78" s="8">
+        <v>8</v>
+      </c>
+      <c r="I78" s="32"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="30">
+        <v>3</v>
+      </c>
+      <c r="B79" s="8">
+        <v>1</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="8">
+        <v>1</v>
+      </c>
+      <c r="E79" s="8">
+        <v>2</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I79" s="32"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="30">
+        <v>3</v>
+      </c>
+      <c r="B80" s="30">
+        <v>1</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D80" s="31"/>
+      <c r="E80" s="31"/>
+      <c r="F80" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H80" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="I80" s="32"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="30">
+        <v>3</v>
+      </c>
+      <c r="B81" s="30">
+        <v>1</v>
+      </c>
+      <c r="C81" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D81" s="31"/>
+      <c r="E81" s="31"/>
+      <c r="F81" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="G81" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H81" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="I81" s="32"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="30">
+        <v>3</v>
+      </c>
+      <c r="B82" s="30">
+        <v>1</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="31"/>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H82" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="I82" s="32"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="30">
+        <v>3</v>
+      </c>
+      <c r="B83" s="30">
+        <v>1</v>
+      </c>
+      <c r="C83" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G83" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H83" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="I83" s="32"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="30">
+        <v>3</v>
+      </c>
+      <c r="B84" s="30">
+        <v>1</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="31"/>
+      <c r="E84" s="31"/>
+      <c r="F84" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="G84" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="I84" s="32"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="30">
+        <v>3</v>
+      </c>
+      <c r="B85" s="30">
+        <v>1</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85" s="31"/>
+      <c r="E85" s="31"/>
+      <c r="F85" s="31" t="s">
+        <v>401</v>
+      </c>
+      <c r="G85" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H85" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I85" s="32"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="30">
+        <v>3</v>
+      </c>
+      <c r="B86" s="10">
+        <v>2</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="11">
+        <v>1</v>
+      </c>
+      <c r="E86" s="11">
+        <v>2</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I86" s="32"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="30">
+        <v>3</v>
+      </c>
+      <c r="B87" s="10">
+        <v>2</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87" s="11">
+        <v>1</v>
+      </c>
+      <c r="E87" s="11">
+        <v>2</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H87" s="10">
+        <v>10</v>
+      </c>
+      <c r="I87" s="32"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="30">
+        <v>3</v>
+      </c>
+      <c r="B88" s="10">
+        <v>2</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D88" s="11">
+        <v>1</v>
+      </c>
+      <c r="E88" s="11">
+        <v>2</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H88" s="10">
+        <v>10</v>
+      </c>
+      <c r="I88" s="32"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="30">
+        <v>3</v>
+      </c>
+      <c r="B89" s="10">
+        <v>2</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D89" s="11">
+        <v>1</v>
+      </c>
+      <c r="E89" s="11">
+        <v>2</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I89" s="32"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="30">
+        <v>3</v>
+      </c>
+      <c r="B90" s="10">
+        <v>2</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D90" s="11">
+        <v>1</v>
+      </c>
+      <c r="E90" s="11">
+        <v>2</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H90" s="10">
+        <v>10</v>
+      </c>
+      <c r="I90" s="32"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="30">
+        <v>3</v>
+      </c>
+      <c r="B91" s="10">
+        <v>2</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D91" s="11">
+        <v>1</v>
+      </c>
+      <c r="E91" s="11">
+        <v>2</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I91" s="32"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="30">
+        <v>3</v>
+      </c>
+      <c r="B92" s="31">
+        <v>2</v>
+      </c>
+      <c r="C92" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" s="31"/>
+      <c r="E92" s="31"/>
+      <c r="F92" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="G92" s="31"/>
+      <c r="H92" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="I92" s="32"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="30">
+        <v>3</v>
+      </c>
+      <c r="B93" s="31">
+        <v>2</v>
+      </c>
+      <c r="C93" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" s="31"/>
+      <c r="E93" s="31"/>
+      <c r="F93" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="G93" s="31"/>
+      <c r="H93" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="I93" s="32"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="30">
+        <v>3</v>
+      </c>
+      <c r="B94" s="31">
+        <v>2</v>
+      </c>
+      <c r="C94" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D94" s="31"/>
+      <c r="E94" s="31"/>
+      <c r="F94" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="G94" s="31"/>
+      <c r="H94" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="I94" s="32"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="30">
+        <v>3</v>
+      </c>
+      <c r="B95" s="31">
+        <v>2</v>
+      </c>
+      <c r="C95" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" s="31"/>
+      <c r="E95" s="31"/>
+      <c r="F95" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G95" s="31"/>
+      <c r="H95" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="I95" s="32"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="30">
+        <v>3</v>
+      </c>
+      <c r="B96" s="31">
+        <v>2</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D96" s="31"/>
+      <c r="E96" s="31"/>
+      <c r="F96" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="G96" s="31"/>
+      <c r="H96" s="31" t="s">
+        <v>302</v>
+      </c>
+      <c r="I96" s="32"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="30">
+        <v>3</v>
+      </c>
+      <c r="B97" s="31">
+        <v>2</v>
+      </c>
+      <c r="C97" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D97" s="31"/>
+      <c r="E97" s="31"/>
+      <c r="F97" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G97" s="31"/>
+      <c r="H97" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="I97" s="32"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="30">
+        <v>3</v>
+      </c>
+      <c r="B98" s="12">
+        <v>3</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D98" s="13">
+        <v>1</v>
+      </c>
+      <c r="E98" s="13">
+        <v>2</v>
+      </c>
+      <c r="F98" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G98" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H98" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I98" s="32"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="30">
+        <v>3</v>
+      </c>
+      <c r="B99" s="12">
+        <v>3</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99" s="13">
+        <v>1</v>
+      </c>
+      <c r="E99" s="13">
+        <v>2</v>
+      </c>
+      <c r="F99" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G99" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H99" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="I99" s="32"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="30">
+        <v>3</v>
+      </c>
+      <c r="B100" s="12">
+        <v>3</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="13">
+        <v>1</v>
+      </c>
+      <c r="E100" s="13">
+        <v>2</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G100" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H100" s="12">
+        <v>7</v>
+      </c>
+      <c r="I100" s="32"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="30">
+        <v>3</v>
+      </c>
+      <c r="B101" s="12">
+        <v>3</v>
+      </c>
+      <c r="C101" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D101" s="13">
+        <v>1</v>
+      </c>
+      <c r="E101" s="13">
+        <v>2</v>
+      </c>
+      <c r="F101" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G101" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H101" s="12">
+        <v>8</v>
+      </c>
+      <c r="I101" s="32"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="30">
+        <v>3</v>
+      </c>
+      <c r="B102" s="12">
+        <v>3</v>
+      </c>
+      <c r="C102" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D102" s="13">
+        <v>1</v>
+      </c>
+      <c r="E102" s="13">
+        <v>2</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G102" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H102" s="12">
+        <v>8</v>
+      </c>
+      <c r="I102" s="32"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="30">
+        <v>3</v>
+      </c>
+      <c r="B103" s="12">
+        <v>3</v>
+      </c>
+      <c r="C103" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D103" s="13">
+        <v>1</v>
+      </c>
+      <c r="E103" s="13">
+        <v>2</v>
+      </c>
+      <c r="F103" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G103" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H103" s="12">
+        <v>10</v>
+      </c>
+      <c r="I103" s="32"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="30">
+        <v>3</v>
+      </c>
+      <c r="B104" s="31">
+        <v>3</v>
+      </c>
+      <c r="C104" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" s="31">
+        <v>2</v>
+      </c>
+      <c r="E104" s="31">
+        <v>4</v>
+      </c>
+      <c r="F104" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H104" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="I104" s="32"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="30">
+        <v>3</v>
+      </c>
+      <c r="B105" s="31">
+        <v>3</v>
+      </c>
+      <c r="C105" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" s="31">
+        <v>2</v>
+      </c>
+      <c r="E105" s="31">
+        <v>4</v>
+      </c>
+      <c r="F105" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="G105" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H105" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I105" s="32"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="30">
+        <v>3</v>
+      </c>
+      <c r="B106" s="31">
+        <v>3</v>
+      </c>
+      <c r="C106" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D106" s="31">
+        <v>2</v>
+      </c>
+      <c r="E106" s="31">
+        <v>4</v>
+      </c>
+      <c r="F106" s="31" t="s">
+        <v>405</v>
+      </c>
+      <c r="G106" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H106" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="I106" s="32"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="30">
+        <v>3</v>
+      </c>
+      <c r="B107" s="31">
+        <v>3</v>
+      </c>
+      <c r="C107" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D107" s="31">
+        <v>3</v>
+      </c>
+      <c r="E107" s="31">
+        <v>3</v>
+      </c>
+      <c r="F107" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G107" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H107" s="31">
+        <v>8</v>
+      </c>
+      <c r="I107" s="32"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="30">
+        <v>3</v>
+      </c>
+      <c r="B108" s="31">
+        <v>3</v>
+      </c>
+      <c r="C108" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D108" s="31">
+        <v>3</v>
+      </c>
+      <c r="E108" s="31">
+        <v>3</v>
+      </c>
+      <c r="F108" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="G108" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H108" s="31">
+        <v>10</v>
+      </c>
+      <c r="I108" s="32"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="30">
+        <v>3</v>
+      </c>
+      <c r="B109" s="31">
+        <v>3</v>
+      </c>
+      <c r="C109" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="31">
+        <v>3</v>
+      </c>
+      <c r="E109" s="31">
+        <v>3</v>
+      </c>
+      <c r="F109" s="31" t="s">
+        <v>394</v>
+      </c>
+      <c r="G109" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H109" s="31">
+        <v>14</v>
+      </c>
+      <c r="I109" s="32"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="30">
+        <v>3</v>
+      </c>
+      <c r="B110" s="31">
+        <v>3</v>
+      </c>
+      <c r="C110" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D110" s="31">
+        <v>4</v>
+      </c>
+      <c r="E110" s="31">
+        <v>3</v>
+      </c>
+      <c r="F110" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G110" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="H110" s="31">
+        <v>10</v>
+      </c>
+      <c r="I110" s="32"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="30">
+        <v>3</v>
+      </c>
+      <c r="B111" s="31">
+        <v>3</v>
+      </c>
+      <c r="C111" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D111" s="31">
+        <v>4</v>
+      </c>
+      <c r="E111" s="31">
+        <v>3</v>
+      </c>
+      <c r="F111" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="G111" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H111" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="I111" s="32"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="30">
+        <v>3</v>
+      </c>
+      <c r="B112" s="31">
+        <v>3</v>
+      </c>
+      <c r="C112" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D112" s="31">
+        <v>4</v>
+      </c>
+      <c r="E112" s="31">
+        <v>3</v>
+      </c>
+      <c r="F112" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="G112" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="H112" s="31">
+        <v>10</v>
+      </c>
+      <c r="I112" s="32"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C300" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C303" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>
@@ -32947,7 +37968,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K180"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -36481,12 +41502,1253 @@
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="30">
+        <v>3</v>
+      </c>
+      <c r="B131" s="31">
+        <v>4</v>
+      </c>
+      <c r="C131" s="31" t="s">
+        <v>40</v>
+      </c>
       <c r="F131" s="31" t="s">
         <v>376</v>
       </c>
+      <c r="G131" s="31" t="s">
+        <v>40</v>
+      </c>
       <c r="H131" t="s">
         <v>378</v>
       </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="25">
+        <v>4</v>
+      </c>
+      <c r="B132" s="39">
+        <v>1</v>
+      </c>
+      <c r="C132" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="40">
+        <v>1</v>
+      </c>
+      <c r="E132" s="40">
+        <v>2</v>
+      </c>
+      <c r="F132" s="41" t="s">
+        <v>338</v>
+      </c>
+      <c r="G132" s="41"/>
+      <c r="H132" s="41">
+        <v>10</v>
+      </c>
+      <c r="I132" s="37"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="25">
+        <v>4</v>
+      </c>
+      <c r="B133" s="39">
+        <v>1</v>
+      </c>
+      <c r="C133" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D133" s="40">
+        <v>1</v>
+      </c>
+      <c r="E133" s="40">
+        <v>2</v>
+      </c>
+      <c r="F133" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="G133" s="41"/>
+      <c r="H133" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="I133" s="37"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="25">
+        <v>4</v>
+      </c>
+      <c r="B134" s="39">
+        <v>1</v>
+      </c>
+      <c r="C134" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D134" s="40">
+        <v>1</v>
+      </c>
+      <c r="E134" s="40">
+        <v>2</v>
+      </c>
+      <c r="F134" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="G134" s="41"/>
+      <c r="H134" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I134" s="37"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="25">
+        <v>4</v>
+      </c>
+      <c r="B135" s="39">
+        <v>1</v>
+      </c>
+      <c r="C135" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D135" s="40">
+        <v>1</v>
+      </c>
+      <c r="E135" s="40">
+        <v>2</v>
+      </c>
+      <c r="F135" s="41" t="s">
+        <v>408</v>
+      </c>
+      <c r="G135" s="41"/>
+      <c r="H135" s="41">
+        <v>10</v>
+      </c>
+      <c r="I135" s="37"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="25">
+        <v>4</v>
+      </c>
+      <c r="B136" s="39">
+        <v>1</v>
+      </c>
+      <c r="C136" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D136" s="40">
+        <v>1</v>
+      </c>
+      <c r="E136" s="40">
+        <v>2</v>
+      </c>
+      <c r="F136" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="G136" s="41"/>
+      <c r="H136" s="41">
+        <v>8</v>
+      </c>
+      <c r="I136" s="37"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="25">
+        <v>4</v>
+      </c>
+      <c r="B137" s="39">
+        <v>1</v>
+      </c>
+      <c r="C137" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D137" s="40">
+        <v>1</v>
+      </c>
+      <c r="E137" s="40">
+        <v>2</v>
+      </c>
+      <c r="F137" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G137" s="41"/>
+      <c r="H137" s="41">
+        <v>10</v>
+      </c>
+      <c r="I137" s="37"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="25">
+        <v>4</v>
+      </c>
+      <c r="B138" s="25">
+        <v>1</v>
+      </c>
+      <c r="C138" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" s="38"/>
+      <c r="E138" s="38"/>
+      <c r="F138" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G138" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H138" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="I138" s="37"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="25">
+        <v>4</v>
+      </c>
+      <c r="B139" s="25">
+        <v>1</v>
+      </c>
+      <c r="C139" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" s="38"/>
+      <c r="E139" s="38"/>
+      <c r="F139" s="38" t="s">
+        <v>295</v>
+      </c>
+      <c r="G139" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H139" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="I139" s="37"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="25">
+        <v>4</v>
+      </c>
+      <c r="B140" s="25">
+        <v>1</v>
+      </c>
+      <c r="C140" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D140" s="38"/>
+      <c r="E140" s="38"/>
+      <c r="F140" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G140" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H140" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="I140" s="37"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="25">
+        <v>4</v>
+      </c>
+      <c r="B141" s="25">
+        <v>1</v>
+      </c>
+      <c r="C141" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="38"/>
+      <c r="E141" s="38"/>
+      <c r="F141" s="38" t="s">
+        <v>415</v>
+      </c>
+      <c r="G141" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H141" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="I141" s="37"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="25">
+        <v>4</v>
+      </c>
+      <c r="B142" s="25">
+        <v>1</v>
+      </c>
+      <c r="C142" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" s="38"/>
+      <c r="E142" s="38"/>
+      <c r="F142" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="G142" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H142" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="I142" s="37"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="25">
+        <v>4</v>
+      </c>
+      <c r="B143" s="25">
+        <v>1</v>
+      </c>
+      <c r="C143" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D143" s="38"/>
+      <c r="E143" s="38"/>
+      <c r="F143" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="G143" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H143" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="I143" s="37"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="25">
+        <v>4</v>
+      </c>
+      <c r="B144" s="25">
+        <v>1</v>
+      </c>
+      <c r="C144" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D144" s="38">
+        <v>2</v>
+      </c>
+      <c r="E144" s="38">
+        <v>3</v>
+      </c>
+      <c r="F144" s="38" t="s">
+        <v>416</v>
+      </c>
+      <c r="G144" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H144" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="I144" s="37"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="25">
+        <v>4</v>
+      </c>
+      <c r="B145" s="25">
+        <v>1</v>
+      </c>
+      <c r="C145" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D145" s="38">
+        <v>2</v>
+      </c>
+      <c r="E145" s="38">
+        <v>3</v>
+      </c>
+      <c r="F145" s="38" t="s">
+        <v>417</v>
+      </c>
+      <c r="G145" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H145" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I145" s="37"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="25">
+        <v>4</v>
+      </c>
+      <c r="B146" s="25">
+        <v>1</v>
+      </c>
+      <c r="C146" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D146" s="38">
+        <v>2</v>
+      </c>
+      <c r="E146" s="38">
+        <v>3</v>
+      </c>
+      <c r="F146" s="38" t="s">
+        <v>418</v>
+      </c>
+      <c r="G146" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H146" s="38">
+        <v>10</v>
+      </c>
+      <c r="I146" s="37"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="25">
+        <v>4</v>
+      </c>
+      <c r="B147" s="42">
+        <v>2</v>
+      </c>
+      <c r="C147" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="43">
+        <v>1</v>
+      </c>
+      <c r="E147" s="43">
+        <v>2</v>
+      </c>
+      <c r="F147" s="44" t="s">
+        <v>409</v>
+      </c>
+      <c r="G147" s="44"/>
+      <c r="H147" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="I147" s="37"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="25">
+        <v>4</v>
+      </c>
+      <c r="B148" s="42">
+        <v>2</v>
+      </c>
+      <c r="C148" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D148" s="43">
+        <v>1</v>
+      </c>
+      <c r="E148" s="43">
+        <v>2</v>
+      </c>
+      <c r="F148" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G148" s="44"/>
+      <c r="H148" s="44">
+        <v>10</v>
+      </c>
+      <c r="I148" s="37"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="25">
+        <v>4</v>
+      </c>
+      <c r="B149" s="42">
+        <v>2</v>
+      </c>
+      <c r="C149" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D149" s="43">
+        <v>1</v>
+      </c>
+      <c r="E149" s="43">
+        <v>2</v>
+      </c>
+      <c r="F149" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="G149" s="44"/>
+      <c r="H149" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="I149" s="37"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="25">
+        <v>4</v>
+      </c>
+      <c r="B150" s="42">
+        <v>2</v>
+      </c>
+      <c r="C150" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D150" s="43">
+        <v>1</v>
+      </c>
+      <c r="E150" s="43">
+        <v>2</v>
+      </c>
+      <c r="F150" s="44" t="s">
+        <v>410</v>
+      </c>
+      <c r="G150" s="44"/>
+      <c r="H150" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="I150" s="37"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="25">
+        <v>4</v>
+      </c>
+      <c r="B151" s="42">
+        <v>2</v>
+      </c>
+      <c r="C151" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D151" s="43">
+        <v>1</v>
+      </c>
+      <c r="E151" s="43">
+        <v>2</v>
+      </c>
+      <c r="F151" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="G151" s="44"/>
+      <c r="H151" s="44">
+        <v>10</v>
+      </c>
+      <c r="I151" s="37"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="25">
+        <v>4</v>
+      </c>
+      <c r="B152" s="42">
+        <v>2</v>
+      </c>
+      <c r="C152" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="D152" s="43">
+        <v>1</v>
+      </c>
+      <c r="E152" s="43">
+        <v>2</v>
+      </c>
+      <c r="F152" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="G152" s="44"/>
+      <c r="H152" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="I152" s="37"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="25">
+        <v>4</v>
+      </c>
+      <c r="B153" s="38">
+        <v>2</v>
+      </c>
+      <c r="C153" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="38"/>
+      <c r="E153" s="38"/>
+      <c r="F153" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G153" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H153" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="I153" s="37"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="25">
+        <v>4</v>
+      </c>
+      <c r="B154" s="38">
+        <v>2</v>
+      </c>
+      <c r="C154" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="38"/>
+      <c r="E154" s="38"/>
+      <c r="F154" s="38" t="s">
+        <v>419</v>
+      </c>
+      <c r="G154" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H154" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="I154" s="37"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="25">
+        <v>4</v>
+      </c>
+      <c r="B155" s="38">
+        <v>2</v>
+      </c>
+      <c r="C155" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D155" s="38"/>
+      <c r="E155" s="38"/>
+      <c r="F155" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G155" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H155" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I155" s="37"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="25">
+        <v>4</v>
+      </c>
+      <c r="B156" s="38">
+        <v>2</v>
+      </c>
+      <c r="C156" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D156" s="38"/>
+      <c r="E156" s="38"/>
+      <c r="F156" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="G156" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H156" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="I156" s="37"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="25">
+        <v>4</v>
+      </c>
+      <c r="B157" s="38">
+        <v>2</v>
+      </c>
+      <c r="C157" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D157" s="38"/>
+      <c r="E157" s="38"/>
+      <c r="F157" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G157" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H157" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="I157" s="37"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="25">
+        <v>4</v>
+      </c>
+      <c r="B158" s="38">
+        <v>2</v>
+      </c>
+      <c r="C158" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D158" s="38"/>
+      <c r="E158" s="38"/>
+      <c r="F158" s="38" t="s">
+        <v>420</v>
+      </c>
+      <c r="G158" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H158" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="I158" s="37"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="25">
+        <v>4</v>
+      </c>
+      <c r="B159" s="45">
+        <v>3</v>
+      </c>
+      <c r="C159" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D159" s="46">
+        <v>1</v>
+      </c>
+      <c r="E159" s="46">
+        <v>2</v>
+      </c>
+      <c r="F159" s="47" t="s">
+        <v>411</v>
+      </c>
+      <c r="G159" s="47"/>
+      <c r="H159" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="I159" s="37"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="25">
+        <v>4</v>
+      </c>
+      <c r="B160" s="45">
+        <v>3</v>
+      </c>
+      <c r="C160" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D160" s="46">
+        <v>1</v>
+      </c>
+      <c r="E160" s="46">
+        <v>2</v>
+      </c>
+      <c r="F160" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="G160" s="47"/>
+      <c r="H160" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="I160" s="37"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="25">
+        <v>4</v>
+      </c>
+      <c r="B161" s="45">
+        <v>3</v>
+      </c>
+      <c r="C161" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D161" s="46">
+        <v>1</v>
+      </c>
+      <c r="E161" s="46">
+        <v>2</v>
+      </c>
+      <c r="F161" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="G161" s="47"/>
+      <c r="H161" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="I161" s="37"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="25">
+        <v>4</v>
+      </c>
+      <c r="B162" s="45">
+        <v>3</v>
+      </c>
+      <c r="C162" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D162" s="46">
+        <v>1</v>
+      </c>
+      <c r="E162" s="46">
+        <v>2</v>
+      </c>
+      <c r="F162" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="G162" s="47"/>
+      <c r="H162" s="47">
+        <v>5</v>
+      </c>
+      <c r="I162" s="37"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="25">
+        <v>4</v>
+      </c>
+      <c r="B163" s="45">
+        <v>3</v>
+      </c>
+      <c r="C163" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D163" s="46">
+        <v>1</v>
+      </c>
+      <c r="E163" s="46">
+        <v>2</v>
+      </c>
+      <c r="F163" s="47" t="s">
+        <v>414</v>
+      </c>
+      <c r="G163" s="47"/>
+      <c r="H163" s="47">
+        <v>10</v>
+      </c>
+      <c r="I163" s="37"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="25">
+        <v>4</v>
+      </c>
+      <c r="B164" s="45">
+        <v>3</v>
+      </c>
+      <c r="C164" s="46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D164" s="46">
+        <v>1</v>
+      </c>
+      <c r="E164" s="46">
+        <v>2</v>
+      </c>
+      <c r="F164" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="G164" s="47"/>
+      <c r="H164" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="I164" s="37"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="25">
+        <v>4</v>
+      </c>
+      <c r="B165" s="38">
+        <v>3</v>
+      </c>
+      <c r="C165" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" s="38">
+        <v>2</v>
+      </c>
+      <c r="E165" s="38">
+        <v>3</v>
+      </c>
+      <c r="F165" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G165" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H165" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I165" s="37"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="25">
+        <v>4</v>
+      </c>
+      <c r="B166" s="38">
+        <v>3</v>
+      </c>
+      <c r="C166" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" s="38">
+        <v>2</v>
+      </c>
+      <c r="E166" s="38">
+        <v>3</v>
+      </c>
+      <c r="F166" s="38" t="s">
+        <v>421</v>
+      </c>
+      <c r="G166" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H166" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="I166" s="37"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="25">
+        <v>4</v>
+      </c>
+      <c r="B167" s="38">
+        <v>3</v>
+      </c>
+      <c r="C167" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="38">
+        <v>2</v>
+      </c>
+      <c r="E167" s="38">
+        <v>3</v>
+      </c>
+      <c r="F167" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="G167" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H167" s="38">
+        <v>20</v>
+      </c>
+      <c r="I167" s="37"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="25">
+        <v>4</v>
+      </c>
+      <c r="B168" s="38">
+        <v>3</v>
+      </c>
+      <c r="C168" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" s="38">
+        <v>3</v>
+      </c>
+      <c r="E168" s="38">
+        <v>3</v>
+      </c>
+      <c r="F168" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="G168" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H168" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I168" s="37"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="25">
+        <v>4</v>
+      </c>
+      <c r="B169" s="38">
+        <v>3</v>
+      </c>
+      <c r="C169" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D169" s="38">
+        <v>3</v>
+      </c>
+      <c r="E169" s="38">
+        <v>3</v>
+      </c>
+      <c r="F169" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="G169" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H169" s="38">
+        <v>12</v>
+      </c>
+      <c r="I169" s="37"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="25">
+        <v>4</v>
+      </c>
+      <c r="B170" s="38">
+        <v>3</v>
+      </c>
+      <c r="C170" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D170" s="38">
+        <v>3</v>
+      </c>
+      <c r="E170" s="38">
+        <v>3</v>
+      </c>
+      <c r="F170" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G170" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H170" s="38">
+        <v>20</v>
+      </c>
+      <c r="I170" s="37"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="25">
+        <v>4</v>
+      </c>
+      <c r="B171" s="38">
+        <v>3</v>
+      </c>
+      <c r="C171" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D171" s="38">
+        <v>4</v>
+      </c>
+      <c r="E171" s="38">
+        <v>3</v>
+      </c>
+      <c r="F171" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="G171" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H171" s="38">
+        <v>10</v>
+      </c>
+      <c r="I171" s="37"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="25">
+        <v>4</v>
+      </c>
+      <c r="B172" s="38">
+        <v>3</v>
+      </c>
+      <c r="C172" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D172" s="38">
+        <v>4</v>
+      </c>
+      <c r="E172" s="38">
+        <v>3</v>
+      </c>
+      <c r="F172" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G172" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H172" s="38">
+        <v>5</v>
+      </c>
+      <c r="I172" s="37"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="25">
+        <v>4</v>
+      </c>
+      <c r="B173" s="38">
+        <v>3</v>
+      </c>
+      <c r="C173" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D173" s="38">
+        <v>4</v>
+      </c>
+      <c r="E173" s="38">
+        <v>3</v>
+      </c>
+      <c r="F173" s="38" t="s">
+        <v>267</v>
+      </c>
+      <c r="G173" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H173" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="I173" s="37"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="25">
+        <v>4</v>
+      </c>
+      <c r="B174" s="38">
+        <v>4</v>
+      </c>
+      <c r="C174" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D174" s="38">
+        <v>1</v>
+      </c>
+      <c r="E174" s="38">
+        <v>2</v>
+      </c>
+      <c r="F174" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G174" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H174" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="I174" s="37"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="25">
+        <v>4</v>
+      </c>
+      <c r="B175" s="38">
+        <v>4</v>
+      </c>
+      <c r="C175" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D175" s="38">
+        <v>1</v>
+      </c>
+      <c r="E175" s="38">
+        <v>2</v>
+      </c>
+      <c r="F175" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G175" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H175" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="I175" s="37"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="25">
+        <v>4</v>
+      </c>
+      <c r="B176" s="38">
+        <v>4</v>
+      </c>
+      <c r="C176" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D176" s="38">
+        <v>1</v>
+      </c>
+      <c r="E176" s="38">
+        <v>2</v>
+      </c>
+      <c r="F176" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="G176" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H176" s="38">
+        <v>10</v>
+      </c>
+      <c r="I176" s="37"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="25">
+        <v>4</v>
+      </c>
+      <c r="B177" s="38">
+        <v>4</v>
+      </c>
+      <c r="C177" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D177" s="38">
+        <v>1</v>
+      </c>
+      <c r="E177" s="38">
+        <v>2</v>
+      </c>
+      <c r="F177" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="G177" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H177" s="38">
+        <v>10</v>
+      </c>
+      <c r="I177" s="37"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="25">
+        <v>4</v>
+      </c>
+      <c r="B178" s="38">
+        <v>4</v>
+      </c>
+      <c r="C178" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D178" s="38">
+        <v>1</v>
+      </c>
+      <c r="E178" s="38">
+        <v>2</v>
+      </c>
+      <c r="F178" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="G178" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H178" s="38">
+        <v>20</v>
+      </c>
+      <c r="I178" s="37"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="25">
+        <v>4</v>
+      </c>
+      <c r="B179" s="38">
+        <v>4</v>
+      </c>
+      <c r="C179" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D179" s="37"/>
+      <c r="E179" s="37"/>
+      <c r="F179" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="G179" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H179" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="I179" s="37"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="25">
+        <v>4</v>
+      </c>
+      <c r="B180" s="38">
+        <v>4</v>
+      </c>
+      <c r="C180" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D180" s="37"/>
+      <c r="E180" s="37"/>
+      <c r="F180" s="38" t="s">
+        <v>376</v>
+      </c>
+      <c r="G180" s="37"/>
+      <c r="H180" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="I180" s="37"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -36500,7 +42762,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L172"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -40026,6 +46288,1095 @@
       </c>
       <c r="I129" s="32"/>
     </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="34">
+        <v>4</v>
+      </c>
+      <c r="B130" s="33">
+        <v>1</v>
+      </c>
+      <c r="C130" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D130" s="33">
+        <v>1</v>
+      </c>
+      <c r="E130" s="33">
+        <v>2</v>
+      </c>
+      <c r="F130" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G130" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H130" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I130" s="35"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="34">
+        <v>4</v>
+      </c>
+      <c r="B131" s="33">
+        <v>1</v>
+      </c>
+      <c r="C131" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D131" s="33">
+        <v>1</v>
+      </c>
+      <c r="E131" s="33">
+        <v>2</v>
+      </c>
+      <c r="F131" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G131" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H131" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I131" s="35"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="34">
+        <v>4</v>
+      </c>
+      <c r="B132" s="33">
+        <v>1</v>
+      </c>
+      <c r="C132" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D132" s="33">
+        <v>1</v>
+      </c>
+      <c r="E132" s="33">
+        <v>2</v>
+      </c>
+      <c r="F132" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G132" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H132" s="33">
+        <v>10</v>
+      </c>
+      <c r="I132" s="35"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="34">
+        <v>4</v>
+      </c>
+      <c r="B133" s="33">
+        <v>1</v>
+      </c>
+      <c r="C133" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D133" s="33">
+        <v>1</v>
+      </c>
+      <c r="E133" s="33">
+        <v>2</v>
+      </c>
+      <c r="F133" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G133" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H133" s="33">
+        <v>8</v>
+      </c>
+      <c r="I133" s="35"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="34">
+        <v>4</v>
+      </c>
+      <c r="B134" s="33">
+        <v>1</v>
+      </c>
+      <c r="C134" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D134" s="33">
+        <v>1</v>
+      </c>
+      <c r="E134" s="33">
+        <v>2</v>
+      </c>
+      <c r="F134" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="G134" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H134" s="33">
+        <v>8</v>
+      </c>
+      <c r="I134" s="35"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="34">
+        <v>4</v>
+      </c>
+      <c r="B135" s="34">
+        <v>1</v>
+      </c>
+      <c r="C135" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" s="36"/>
+      <c r="E135" s="36"/>
+      <c r="F135" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="G135" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H135" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="I135" s="35"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="34">
+        <v>4</v>
+      </c>
+      <c r="B136" s="34">
+        <v>1</v>
+      </c>
+      <c r="C136" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="G136" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H136" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="I136" s="35"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="34">
+        <v>4</v>
+      </c>
+      <c r="B137" s="34">
+        <v>1</v>
+      </c>
+      <c r="C137" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D137" s="36"/>
+      <c r="E137" s="36"/>
+      <c r="F137" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="G137" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H137" s="36" t="s">
+        <v>356</v>
+      </c>
+      <c r="I137" s="35"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="34">
+        <v>4</v>
+      </c>
+      <c r="B138" s="34">
+        <v>1</v>
+      </c>
+      <c r="C138" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="G138" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H138" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="I138" s="35"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="34">
+        <v>4</v>
+      </c>
+      <c r="B139" s="34">
+        <v>1</v>
+      </c>
+      <c r="C139" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D139" s="36"/>
+      <c r="E139" s="36"/>
+      <c r="F139" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="G139" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H139" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="I139" s="35"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="34">
+        <v>4</v>
+      </c>
+      <c r="B140" s="34">
+        <v>1</v>
+      </c>
+      <c r="C140" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D140" s="36"/>
+      <c r="E140" s="36"/>
+      <c r="F140" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="G140" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H140" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="I140" s="35"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="34">
+        <v>4</v>
+      </c>
+      <c r="B141" s="34">
+        <v>1</v>
+      </c>
+      <c r="C141" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D141" s="36"/>
+      <c r="E141" s="36"/>
+      <c r="F141" s="36" t="s">
+        <v>393</v>
+      </c>
+      <c r="G141" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H141" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="I141" s="35"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="34">
+        <v>4</v>
+      </c>
+      <c r="B142" s="34">
+        <v>1</v>
+      </c>
+      <c r="C142" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D142" s="36">
+        <v>2</v>
+      </c>
+      <c r="E142" s="36">
+        <v>3</v>
+      </c>
+      <c r="F142" s="36" t="s">
+        <v>382</v>
+      </c>
+      <c r="G142" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H142" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I142" s="35"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="34">
+        <v>4</v>
+      </c>
+      <c r="B143" s="34">
+        <v>1</v>
+      </c>
+      <c r="C143" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D143" s="36">
+        <v>2</v>
+      </c>
+      <c r="E143" s="36">
+        <v>3</v>
+      </c>
+      <c r="F143" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G143" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H143" s="36">
+        <v>20</v>
+      </c>
+      <c r="I143" s="35"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="34">
+        <v>4</v>
+      </c>
+      <c r="B144" s="34">
+        <v>1</v>
+      </c>
+      <c r="C144" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D144" s="36">
+        <v>2</v>
+      </c>
+      <c r="E144" s="36">
+        <v>3</v>
+      </c>
+      <c r="F144" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="G144" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H144" s="36">
+        <v>20</v>
+      </c>
+      <c r="I144" s="35"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="34">
+        <v>4</v>
+      </c>
+      <c r="B145" s="16">
+        <v>2</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="14">
+        <v>1</v>
+      </c>
+      <c r="E145" s="14">
+        <v>2</v>
+      </c>
+      <c r="F145" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G145" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H145" s="16">
+        <v>10</v>
+      </c>
+      <c r="I145" s="35"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="34">
+        <v>4</v>
+      </c>
+      <c r="B146" s="16">
+        <v>2</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="14">
+        <v>1</v>
+      </c>
+      <c r="E146" s="14">
+        <v>2</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G146" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H146" s="16">
+        <v>10</v>
+      </c>
+      <c r="I146" s="35"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="34">
+        <v>4</v>
+      </c>
+      <c r="B147" s="16">
+        <v>2</v>
+      </c>
+      <c r="C147" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="14">
+        <v>1</v>
+      </c>
+      <c r="E147" s="14">
+        <v>2</v>
+      </c>
+      <c r="F147" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G147" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H147" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I147" s="35"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="34">
+        <v>4</v>
+      </c>
+      <c r="B148" s="16">
+        <v>2</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D148" s="14">
+        <v>1</v>
+      </c>
+      <c r="E148" s="14">
+        <v>2</v>
+      </c>
+      <c r="F148" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G148" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H148" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I148" s="35"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="34">
+        <v>4</v>
+      </c>
+      <c r="B149" s="16">
+        <v>2</v>
+      </c>
+      <c r="C149" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D149" s="14">
+        <v>1</v>
+      </c>
+      <c r="E149" s="14">
+        <v>2</v>
+      </c>
+      <c r="F149" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G149" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H149" s="16">
+        <v>10</v>
+      </c>
+      <c r="I149" s="35"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="34">
+        <v>4</v>
+      </c>
+      <c r="B150" s="36">
+        <v>2</v>
+      </c>
+      <c r="C150" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" s="36"/>
+      <c r="E150" s="36"/>
+      <c r="F150" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="G150" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H150" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="I150" s="35"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="34">
+        <v>4</v>
+      </c>
+      <c r="B151" s="36">
+        <v>2</v>
+      </c>
+      <c r="C151" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" s="36"/>
+      <c r="E151" s="36"/>
+      <c r="F151" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="G151" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H151" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="I151" s="35"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="34">
+        <v>4</v>
+      </c>
+      <c r="B152" s="36">
+        <v>2</v>
+      </c>
+      <c r="C152" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D152" s="36"/>
+      <c r="E152" s="36"/>
+      <c r="F152" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="G152" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H152" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="I152" s="35"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="34">
+        <v>4</v>
+      </c>
+      <c r="B153" s="36">
+        <v>2</v>
+      </c>
+      <c r="C153" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="36"/>
+      <c r="E153" s="36"/>
+      <c r="F153" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="G153" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H153" s="36" t="s">
+        <v>395</v>
+      </c>
+      <c r="I153" s="35"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="34">
+        <v>4</v>
+      </c>
+      <c r="B154" s="36">
+        <v>2</v>
+      </c>
+      <c r="C154" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="36"/>
+      <c r="E154" s="36"/>
+      <c r="F154" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="G154" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H154" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="I154" s="35"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="34">
+        <v>4</v>
+      </c>
+      <c r="B155" s="36">
+        <v>2</v>
+      </c>
+      <c r="C155" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D155" s="36"/>
+      <c r="E155" s="36"/>
+      <c r="F155" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="G155" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H155" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="I155" s="35"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="34">
+        <v>4</v>
+      </c>
+      <c r="B156" s="36">
+        <v>2</v>
+      </c>
+      <c r="C156" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D156" s="36"/>
+      <c r="E156" s="36"/>
+      <c r="F156" s="36" t="s">
+        <v>396</v>
+      </c>
+      <c r="G156" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H156" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="I156" s="35"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="34">
+        <v>4</v>
+      </c>
+      <c r="B157" s="36">
+        <v>2</v>
+      </c>
+      <c r="C157" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D157" s="36">
+        <v>2</v>
+      </c>
+      <c r="E157" s="36">
+        <v>3</v>
+      </c>
+      <c r="F157" s="36" t="s">
+        <v>397</v>
+      </c>
+      <c r="G157" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H157" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I157" s="35"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="34">
+        <v>4</v>
+      </c>
+      <c r="B158" s="36">
+        <v>2</v>
+      </c>
+      <c r="C158" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D158" s="36">
+        <v>2</v>
+      </c>
+      <c r="E158" s="36">
+        <v>3</v>
+      </c>
+      <c r="F158" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="G158" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H158" s="36">
+        <v>20</v>
+      </c>
+      <c r="I158" s="35"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="34">
+        <v>4</v>
+      </c>
+      <c r="B159" s="36">
+        <v>2</v>
+      </c>
+      <c r="C159" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="D159" s="36">
+        <v>2</v>
+      </c>
+      <c r="E159" s="36">
+        <v>3</v>
+      </c>
+      <c r="F159" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="G159" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="H159" s="36">
+        <v>10</v>
+      </c>
+      <c r="I159" s="35"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="34">
+        <v>4</v>
+      </c>
+      <c r="B160" s="18">
+        <v>3</v>
+      </c>
+      <c r="C160" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D160" s="17">
+        <v>1</v>
+      </c>
+      <c r="E160" s="17">
+        <v>2</v>
+      </c>
+      <c r="F160" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G160" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H160" s="18">
+        <v>10</v>
+      </c>
+      <c r="I160" s="35"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="34">
+        <v>4</v>
+      </c>
+      <c r="B161" s="18">
+        <v>3</v>
+      </c>
+      <c r="C161" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D161" s="17">
+        <v>1</v>
+      </c>
+      <c r="E161" s="17">
+        <v>2</v>
+      </c>
+      <c r="F161" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="G161" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H161" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="I161" s="35"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="34">
+        <v>4</v>
+      </c>
+      <c r="B162" s="18">
+        <v>3</v>
+      </c>
+      <c r="C162" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D162" s="17">
+        <v>1</v>
+      </c>
+      <c r="E162" s="17">
+        <v>2</v>
+      </c>
+      <c r="F162" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G162" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H162" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="I162" s="35"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="34">
+        <v>4</v>
+      </c>
+      <c r="B163" s="18">
+        <v>3</v>
+      </c>
+      <c r="C163" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D163" s="17">
+        <v>1</v>
+      </c>
+      <c r="E163" s="17">
+        <v>2</v>
+      </c>
+      <c r="F163" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G163" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="H163" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="I163" s="35"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="34">
+        <v>4</v>
+      </c>
+      <c r="B164" s="18">
+        <v>3</v>
+      </c>
+      <c r="C164" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D164" s="17">
+        <v>1</v>
+      </c>
+      <c r="E164" s="17">
+        <v>2</v>
+      </c>
+      <c r="F164" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G164" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H164" s="18">
+        <v>8</v>
+      </c>
+      <c r="I164" s="35"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="34">
+        <v>4</v>
+      </c>
+      <c r="B165" s="36">
+        <v>3</v>
+      </c>
+      <c r="C165" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" s="36"/>
+      <c r="E165" s="36"/>
+      <c r="F165" s="36" t="s">
+        <v>399</v>
+      </c>
+      <c r="G165" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H165" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="I165" s="35"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="34">
+        <v>4</v>
+      </c>
+      <c r="B166" s="36">
+        <v>3</v>
+      </c>
+      <c r="C166" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" s="36"/>
+      <c r="E166" s="36"/>
+      <c r="F166" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="G166" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H166" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="I166" s="35"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="34">
+        <v>4</v>
+      </c>
+      <c r="B167" s="36">
+        <v>3</v>
+      </c>
+      <c r="C167" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="35"/>
+      <c r="E167" s="35"/>
+      <c r="F167" s="36" t="s">
+        <v>401</v>
+      </c>
+      <c r="G167" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H167" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="I167" s="35"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="34">
+        <v>4</v>
+      </c>
+      <c r="B168" s="36">
+        <v>3</v>
+      </c>
+      <c r="C168" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" s="35"/>
+      <c r="E168" s="35"/>
+      <c r="F168" s="36" t="s">
+        <v>400</v>
+      </c>
+      <c r="G168" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H168" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="I168" s="35"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="34">
+        <v>4</v>
+      </c>
+      <c r="B169" s="36">
+        <v>3</v>
+      </c>
+      <c r="C169" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D169" s="35">
+        <v>2</v>
+      </c>
+      <c r="E169" s="35">
+        <v>3</v>
+      </c>
+      <c r="F169" s="36" t="s">
+        <v>402</v>
+      </c>
+      <c r="G169" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H169" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="I169" s="35"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="34">
+        <v>4</v>
+      </c>
+      <c r="B170" s="36">
+        <v>3</v>
+      </c>
+      <c r="C170" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D170" s="35">
+        <v>2</v>
+      </c>
+      <c r="E170" s="35">
+        <v>3</v>
+      </c>
+      <c r="F170" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="G170" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H170" s="35">
+        <v>10</v>
+      </c>
+      <c r="I170" s="35"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="34">
+        <v>4</v>
+      </c>
+      <c r="B171" s="36">
+        <v>3</v>
+      </c>
+      <c r="C171" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D171" s="35">
+        <v>3</v>
+      </c>
+      <c r="E171" s="35">
+        <v>3</v>
+      </c>
+      <c r="F171" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="G171" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H171" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="I171" s="35"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="34">
+        <v>4</v>
+      </c>
+      <c r="B172" s="36">
+        <v>3</v>
+      </c>
+      <c r="C172" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D172" s="35">
+        <v>3</v>
+      </c>
+      <c r="E172" s="35">
+        <v>3</v>
+      </c>
+      <c r="F172" s="36" t="s">
+        <v>357</v>
+      </c>
+      <c r="G172" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="H172" s="35">
+        <v>10</v>
+      </c>
+      <c r="I172" s="35"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C299" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -40038,7 +47389,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J170"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -43702,6 +51053,733 @@
       </c>
       <c r="I141" s="32"/>
     </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="25">
+        <v>4</v>
+      </c>
+      <c r="B142" s="33">
+        <v>1</v>
+      </c>
+      <c r="C142" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D142" s="33">
+        <v>1</v>
+      </c>
+      <c r="E142" s="33">
+        <v>2</v>
+      </c>
+      <c r="F142" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G142" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H142" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I142" s="37"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="25">
+        <v>4</v>
+      </c>
+      <c r="B143" s="33">
+        <v>1</v>
+      </c>
+      <c r="C143" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D143" s="33">
+        <v>1</v>
+      </c>
+      <c r="E143" s="33">
+        <v>2</v>
+      </c>
+      <c r="F143" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="G143" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H143" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I143" s="37"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="25">
+        <v>4</v>
+      </c>
+      <c r="B144" s="33">
+        <v>1</v>
+      </c>
+      <c r="C144" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D144" s="33">
+        <v>1</v>
+      </c>
+      <c r="E144" s="33">
+        <v>2</v>
+      </c>
+      <c r="F144" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G144" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H144" s="33">
+        <v>10</v>
+      </c>
+      <c r="I144" s="37"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="25">
+        <v>4</v>
+      </c>
+      <c r="B145" s="33">
+        <v>1</v>
+      </c>
+      <c r="C145" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="33">
+        <v>1</v>
+      </c>
+      <c r="E145" s="33">
+        <v>2</v>
+      </c>
+      <c r="F145" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="G145" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H145" s="33">
+        <v>8</v>
+      </c>
+      <c r="I145" s="37"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="25">
+        <v>4</v>
+      </c>
+      <c r="B146" s="33">
+        <v>1</v>
+      </c>
+      <c r="C146" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="33">
+        <v>1</v>
+      </c>
+      <c r="E146" s="33">
+        <v>2</v>
+      </c>
+      <c r="F146" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="G146" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="H146" s="33">
+        <v>8</v>
+      </c>
+      <c r="I146" s="37"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="25">
+        <v>4</v>
+      </c>
+      <c r="B147" s="25">
+        <v>1</v>
+      </c>
+      <c r="C147" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="25">
+        <v>1</v>
+      </c>
+      <c r="E147" s="25">
+        <v>2</v>
+      </c>
+      <c r="F147" s="38" t="s">
+        <v>145</v>
+      </c>
+      <c r="G147" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H147" s="38">
+        <v>8</v>
+      </c>
+      <c r="I147" s="37"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="25">
+        <v>4</v>
+      </c>
+      <c r="B148" s="25">
+        <v>1</v>
+      </c>
+      <c r="C148" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D148" s="38"/>
+      <c r="E148" s="38"/>
+      <c r="F148" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G148" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H148" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I148" s="37"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="25">
+        <v>4</v>
+      </c>
+      <c r="B149" s="25">
+        <v>1</v>
+      </c>
+      <c r="C149" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D149" s="38"/>
+      <c r="E149" s="38"/>
+      <c r="F149" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="G149" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H149" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I149" s="37"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="25">
+        <v>4</v>
+      </c>
+      <c r="B150" s="25">
+        <v>1</v>
+      </c>
+      <c r="C150" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" s="38"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G150" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H150" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="I150" s="37"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="25">
+        <v>4</v>
+      </c>
+      <c r="B151" s="25">
+        <v>1</v>
+      </c>
+      <c r="C151" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" s="38"/>
+      <c r="E151" s="38"/>
+      <c r="F151" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G151" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H151" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I151" s="37"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="25">
+        <v>4</v>
+      </c>
+      <c r="B152" s="25">
+        <v>1</v>
+      </c>
+      <c r="C152" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D152" s="38"/>
+      <c r="E152" s="38"/>
+      <c r="F152" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="G152" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H152" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="I152" s="37"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="25">
+        <v>4</v>
+      </c>
+      <c r="B153" s="25">
+        <v>1</v>
+      </c>
+      <c r="C153" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="38"/>
+      <c r="E153" s="38"/>
+      <c r="F153" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="G153" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H153" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="I153" s="37"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="25">
+        <v>4</v>
+      </c>
+      <c r="B154" s="25">
+        <v>1</v>
+      </c>
+      <c r="C154" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="38"/>
+      <c r="E154" s="38"/>
+      <c r="F154" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="G154" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H154" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I154" s="37"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="25">
+        <v>4</v>
+      </c>
+      <c r="B155" s="25">
+        <v>1</v>
+      </c>
+      <c r="C155" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D155" s="38">
+        <v>2</v>
+      </c>
+      <c r="E155" s="38">
+        <v>3</v>
+      </c>
+      <c r="F155" s="38" t="s">
+        <v>348</v>
+      </c>
+      <c r="G155" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H155" s="38">
+        <v>20</v>
+      </c>
+      <c r="I155" s="37"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="25">
+        <v>4</v>
+      </c>
+      <c r="B156" s="25">
+        <v>1</v>
+      </c>
+      <c r="C156" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D156" s="38">
+        <v>2</v>
+      </c>
+      <c r="E156" s="38">
+        <v>3</v>
+      </c>
+      <c r="F156" s="38" t="s">
+        <v>416</v>
+      </c>
+      <c r="G156" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H156" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I156" s="37"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="25">
+        <v>4</v>
+      </c>
+      <c r="B157" s="25">
+        <v>1</v>
+      </c>
+      <c r="C157" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D157" s="38">
+        <v>2</v>
+      </c>
+      <c r="E157" s="38">
+        <v>3</v>
+      </c>
+      <c r="F157" s="38" t="s">
+        <v>417</v>
+      </c>
+      <c r="G157" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H157" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I157" s="37"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="25">
+        <v>4</v>
+      </c>
+      <c r="B158" s="16">
+        <v>2</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D158" s="14">
+        <v>1</v>
+      </c>
+      <c r="E158" s="14">
+        <v>2</v>
+      </c>
+      <c r="F158" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="G158" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H158" s="16">
+        <v>10</v>
+      </c>
+      <c r="I158" s="37"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="25">
+        <v>4</v>
+      </c>
+      <c r="B159" s="16">
+        <v>2</v>
+      </c>
+      <c r="C159" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D159" s="14">
+        <v>1</v>
+      </c>
+      <c r="E159" s="14">
+        <v>2</v>
+      </c>
+      <c r="F159" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G159" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H159" s="16">
+        <v>10</v>
+      </c>
+      <c r="I159" s="37"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="25">
+        <v>4</v>
+      </c>
+      <c r="B160" s="16">
+        <v>2</v>
+      </c>
+      <c r="C160" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D160" s="14">
+        <v>1</v>
+      </c>
+      <c r="E160" s="14">
+        <v>2</v>
+      </c>
+      <c r="F160" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G160" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="H160" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="I160" s="37"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="25">
+        <v>4</v>
+      </c>
+      <c r="B161" s="16">
+        <v>2</v>
+      </c>
+      <c r="C161" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D161" s="14">
+        <v>1</v>
+      </c>
+      <c r="E161" s="14">
+        <v>2</v>
+      </c>
+      <c r="F161" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="G161" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H161" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I161" s="37"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="25">
+        <v>4</v>
+      </c>
+      <c r="B162" s="16">
+        <v>2</v>
+      </c>
+      <c r="C162" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D162" s="14">
+        <v>1</v>
+      </c>
+      <c r="E162" s="14">
+        <v>2</v>
+      </c>
+      <c r="F162" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G162" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="H162" s="16">
+        <v>8</v>
+      </c>
+      <c r="I162" s="37"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="25">
+        <v>4</v>
+      </c>
+      <c r="B163" s="38">
+        <v>2</v>
+      </c>
+      <c r="C163" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D163" s="25">
+        <v>1</v>
+      </c>
+      <c r="E163" s="25">
+        <v>2</v>
+      </c>
+      <c r="F163" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G163" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H163" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I163" s="37"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="25">
+        <v>4</v>
+      </c>
+      <c r="B164" s="38">
+        <v>2</v>
+      </c>
+      <c r="C164" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D164" s="38"/>
+      <c r="E164" s="38"/>
+      <c r="F164" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G164" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H164" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I164" s="37"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="25">
+        <v>4</v>
+      </c>
+      <c r="B165" s="38">
+        <v>2</v>
+      </c>
+      <c r="C165" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" s="38"/>
+      <c r="E165" s="38"/>
+      <c r="F165" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="G165" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H165" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="I165" s="37"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="25">
+        <v>4</v>
+      </c>
+      <c r="B166" s="38">
+        <v>2</v>
+      </c>
+      <c r="C166" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" s="38"/>
+      <c r="E166" s="38"/>
+      <c r="F166" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="G166" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H166" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I166" s="37"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="25">
+        <v>4</v>
+      </c>
+      <c r="B167" s="38">
+        <v>2</v>
+      </c>
+      <c r="C167" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="38"/>
+      <c r="E167" s="38"/>
+      <c r="F167" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="G167" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H167" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="I167" s="37"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="25">
+        <v>4</v>
+      </c>
+      <c r="B168" s="38">
+        <v>2</v>
+      </c>
+      <c r="C168" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" s="38"/>
+      <c r="E168" s="38"/>
+      <c r="F168" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="G168" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H168" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="I168" s="37"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="25">
+        <v>4</v>
+      </c>
+      <c r="B169" s="38">
+        <v>2</v>
+      </c>
+      <c r="C169" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D169" s="38"/>
+      <c r="E169" s="38"/>
+      <c r="F169" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="G169" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H169" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="I169" s="37"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="25">
+        <v>4</v>
+      </c>
+      <c r="B170" s="38">
+        <v>2</v>
+      </c>
+      <c r="C170" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D170" s="38"/>
+      <c r="E170" s="38"/>
+      <c r="F170" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="G170" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H170" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="I170" s="37"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C299" xr:uid="{00000000-0002-0000-0600-000000000000}">

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B8F590A-281C-4EA4-A817-A3B3C2482E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1D04CA-B9F4-49E5-BB28-2C8FC71069E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="18" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6691" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6739" uniqueCount="433">
   <si>
     <t>Cómo completar cada pestaña de alumno</t>
   </si>
@@ -1317,6 +1317,27 @@
   <si>
     <t>1x7 1x5 3x2 (Aumentando la carga)</t>
   </si>
+  <si>
+    <t>3x7 2x5 (Aumentando la carga)</t>
+  </si>
+  <si>
+    <t>3x10 2x8 (Aumentando la carga)</t>
+  </si>
+  <si>
+    <t>Curl de biceps con barra</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>300 mts</t>
+  </si>
+  <si>
+    <t>15 de cada lado</t>
+  </si>
+  <si>
+    <t>Plank lateral + vuelo</t>
+  </si>
 </sst>
 </file>
 
@@ -12256,7 +12277,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -15963,6 +15984,1152 @@
       </c>
       <c r="H144" s="30">
         <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" s="25">
+        <v>4</v>
+      </c>
+      <c r="B145" s="25">
+        <v>1</v>
+      </c>
+      <c r="C145" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D145" s="25">
+        <v>1</v>
+      </c>
+      <c r="E145" s="25">
+        <v>2</v>
+      </c>
+      <c r="F145" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="G145" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H145" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="25">
+        <v>4</v>
+      </c>
+      <c r="B146" s="25">
+        <v>1</v>
+      </c>
+      <c r="C146" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D146" s="25">
+        <v>1</v>
+      </c>
+      <c r="E146" s="25">
+        <v>2</v>
+      </c>
+      <c r="F146" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="G146" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H146" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="25">
+        <v>4</v>
+      </c>
+      <c r="B147" s="25">
+        <v>1</v>
+      </c>
+      <c r="C147" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="25">
+        <v>1</v>
+      </c>
+      <c r="E147" s="25">
+        <v>2</v>
+      </c>
+      <c r="F147" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G147" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="H147" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="25">
+        <v>4</v>
+      </c>
+      <c r="B148" s="25">
+        <v>1</v>
+      </c>
+      <c r="C148" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D148" s="25">
+        <v>1</v>
+      </c>
+      <c r="E148" s="25">
+        <v>2</v>
+      </c>
+      <c r="F148" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G148" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H148" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="25">
+        <v>4</v>
+      </c>
+      <c r="B149" s="25">
+        <v>1</v>
+      </c>
+      <c r="C149" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D149" s="25">
+        <v>1</v>
+      </c>
+      <c r="E149" s="25">
+        <v>2</v>
+      </c>
+      <c r="F149" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G149" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="H149" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" s="25">
+        <v>4</v>
+      </c>
+      <c r="B150" s="25">
+        <v>1</v>
+      </c>
+      <c r="C150" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D150" s="38"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G150" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H150" s="38" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="25">
+        <v>4</v>
+      </c>
+      <c r="B151" s="25">
+        <v>1</v>
+      </c>
+      <c r="C151" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D151" s="38">
+        <v>2</v>
+      </c>
+      <c r="E151" s="38">
+        <v>4</v>
+      </c>
+      <c r="F151" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="G151" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H151" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="25">
+        <v>4</v>
+      </c>
+      <c r="B152" s="25">
+        <v>1</v>
+      </c>
+      <c r="C152" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D152" s="38">
+        <v>2</v>
+      </c>
+      <c r="E152" s="38">
+        <v>4</v>
+      </c>
+      <c r="F152" s="38" t="s">
+        <v>428</v>
+      </c>
+      <c r="G152" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H152" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="25">
+        <v>4</v>
+      </c>
+      <c r="B153" s="25">
+        <v>1</v>
+      </c>
+      <c r="C153" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D153" s="38"/>
+      <c r="E153" s="38"/>
+      <c r="F153" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="G153" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H153" s="38" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="25">
+        <v>4</v>
+      </c>
+      <c r="B154" s="25">
+        <v>1</v>
+      </c>
+      <c r="C154" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D154" s="38">
+        <v>3</v>
+      </c>
+      <c r="E154" s="38">
+        <v>4</v>
+      </c>
+      <c r="F154" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G154" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H154" s="38" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" s="25">
+        <v>4</v>
+      </c>
+      <c r="B155" s="25">
+        <v>1</v>
+      </c>
+      <c r="C155" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D155" s="38">
+        <v>3</v>
+      </c>
+      <c r="E155" s="38">
+        <v>4</v>
+      </c>
+      <c r="F155" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="G155" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H155" s="38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" s="25">
+        <v>4</v>
+      </c>
+      <c r="B156" s="25">
+        <v>1</v>
+      </c>
+      <c r="C156" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D156" s="38">
+        <v>4</v>
+      </c>
+      <c r="E156" s="38">
+        <v>3</v>
+      </c>
+      <c r="F156" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="G156" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H156" s="38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="25">
+        <v>4</v>
+      </c>
+      <c r="B157" s="25">
+        <v>1</v>
+      </c>
+      <c r="C157" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D157" s="38">
+        <v>4</v>
+      </c>
+      <c r="E157" s="38">
+        <v>3</v>
+      </c>
+      <c r="F157" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G157" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H157" s="38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" s="25">
+        <v>4</v>
+      </c>
+      <c r="B158" s="25">
+        <v>1</v>
+      </c>
+      <c r="C158" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D158" s="38">
+        <v>4</v>
+      </c>
+      <c r="E158" s="38">
+        <v>3</v>
+      </c>
+      <c r="F158" s="38" t="s">
+        <v>390</v>
+      </c>
+      <c r="G158" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H158" s="38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="25">
+        <v>4</v>
+      </c>
+      <c r="B159" s="26">
+        <v>2</v>
+      </c>
+      <c r="C159" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D159" s="27">
+        <v>1</v>
+      </c>
+      <c r="E159" s="27">
+        <v>2</v>
+      </c>
+      <c r="F159" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G159" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H159" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="25">
+        <v>4</v>
+      </c>
+      <c r="B160" s="26">
+        <v>2</v>
+      </c>
+      <c r="C160" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D160" s="27">
+        <v>1</v>
+      </c>
+      <c r="E160" s="27">
+        <v>2</v>
+      </c>
+      <c r="F160" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="G160" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="H160" s="26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="25">
+        <v>4</v>
+      </c>
+      <c r="B161" s="26">
+        <v>2</v>
+      </c>
+      <c r="C161" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D161" s="27">
+        <v>1</v>
+      </c>
+      <c r="E161" s="27">
+        <v>2</v>
+      </c>
+      <c r="F161" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G161" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="H161" s="26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="25">
+        <v>4</v>
+      </c>
+      <c r="B162" s="26">
+        <v>2</v>
+      </c>
+      <c r="C162" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D162" s="27">
+        <v>1</v>
+      </c>
+      <c r="E162" s="27">
+        <v>2</v>
+      </c>
+      <c r="F162" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="G162" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="H162" s="26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="25">
+        <v>4</v>
+      </c>
+      <c r="B163" s="26">
+        <v>2</v>
+      </c>
+      <c r="C163" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="D163" s="27">
+        <v>1</v>
+      </c>
+      <c r="E163" s="27">
+        <v>2</v>
+      </c>
+      <c r="F163" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="G163" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H163" s="26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="25">
+        <v>4</v>
+      </c>
+      <c r="B164" s="38">
+        <v>2</v>
+      </c>
+      <c r="C164" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D164" s="38"/>
+      <c r="E164" s="38"/>
+      <c r="F164" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="G164" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H164" s="38" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="25">
+        <v>4</v>
+      </c>
+      <c r="B165" s="38">
+        <v>2</v>
+      </c>
+      <c r="C165" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D165" s="38"/>
+      <c r="E165" s="38"/>
+      <c r="F165" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="G165" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H165" s="38" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="25">
+        <v>4</v>
+      </c>
+      <c r="B166" s="38">
+        <v>2</v>
+      </c>
+      <c r="C166" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D166" s="38"/>
+      <c r="E166" s="38"/>
+      <c r="F166" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="G166" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H166" s="38" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="25">
+        <v>4</v>
+      </c>
+      <c r="B167" s="38">
+        <v>2</v>
+      </c>
+      <c r="C167" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="38"/>
+      <c r="E167" s="38"/>
+      <c r="F167" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="G167" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H167" s="38" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="25">
+        <v>4</v>
+      </c>
+      <c r="B168" s="38">
+        <v>2</v>
+      </c>
+      <c r="C168" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D168" s="38">
+        <v>2</v>
+      </c>
+      <c r="E168" s="38">
+        <v>4</v>
+      </c>
+      <c r="F168" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="G168" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H168" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="25">
+        <v>4</v>
+      </c>
+      <c r="B169" s="38">
+        <v>2</v>
+      </c>
+      <c r="C169" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D169" s="38">
+        <v>2</v>
+      </c>
+      <c r="E169" s="38">
+        <v>4</v>
+      </c>
+      <c r="F169" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G169" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H169" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" s="25">
+        <v>4</v>
+      </c>
+      <c r="B170" s="38">
+        <v>2</v>
+      </c>
+      <c r="C170" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D170" s="38">
+        <v>3</v>
+      </c>
+      <c r="E170" s="38">
+        <v>4</v>
+      </c>
+      <c r="F170" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G170" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H170" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="25">
+        <v>4</v>
+      </c>
+      <c r="B171" s="38">
+        <v>2</v>
+      </c>
+      <c r="C171" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D171" s="38">
+        <v>3</v>
+      </c>
+      <c r="E171" s="38">
+        <v>4</v>
+      </c>
+      <c r="F171" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="G171" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H171" s="38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="25">
+        <v>4</v>
+      </c>
+      <c r="B172" s="38">
+        <v>2</v>
+      </c>
+      <c r="C172" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D172" s="38">
+        <v>3</v>
+      </c>
+      <c r="E172" s="38">
+        <v>4</v>
+      </c>
+      <c r="F172" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G172" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H172" s="38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="25">
+        <v>4</v>
+      </c>
+      <c r="B173" s="38">
+        <v>2</v>
+      </c>
+      <c r="C173" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D173" s="38">
+        <v>3</v>
+      </c>
+      <c r="E173" s="38">
+        <v>4</v>
+      </c>
+      <c r="F173" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="G173" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H173" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" s="25">
+        <v>4</v>
+      </c>
+      <c r="B174" s="38">
+        <v>2</v>
+      </c>
+      <c r="C174" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D174" s="38">
+        <v>3</v>
+      </c>
+      <c r="E174" s="38">
+        <v>4</v>
+      </c>
+      <c r="F174" s="38" t="s">
+        <v>429</v>
+      </c>
+      <c r="G174" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H174" s="38" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="25">
+        <v>4</v>
+      </c>
+      <c r="B175" s="38">
+        <v>2</v>
+      </c>
+      <c r="C175" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="D175" s="38">
+        <v>3</v>
+      </c>
+      <c r="E175" s="38">
+        <v>4</v>
+      </c>
+      <c r="F175" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="G175" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H175" s="38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="25">
+        <v>4</v>
+      </c>
+      <c r="B176" s="28">
+        <v>3</v>
+      </c>
+      <c r="C176" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D176" s="29">
+        <v>1</v>
+      </c>
+      <c r="E176" s="29">
+        <v>2</v>
+      </c>
+      <c r="F176" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="G176" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="H176" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="25">
+        <v>4</v>
+      </c>
+      <c r="B177" s="28">
+        <v>3</v>
+      </c>
+      <c r="C177" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D177" s="29">
+        <v>1</v>
+      </c>
+      <c r="E177" s="29">
+        <v>2</v>
+      </c>
+      <c r="F177" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="G177" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H177" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="25">
+        <v>4</v>
+      </c>
+      <c r="B178" s="28">
+        <v>3</v>
+      </c>
+      <c r="C178" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D178" s="29">
+        <v>1</v>
+      </c>
+      <c r="E178" s="29">
+        <v>2</v>
+      </c>
+      <c r="F178" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="G178" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H178" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" s="25">
+        <v>4</v>
+      </c>
+      <c r="B179" s="28">
+        <v>3</v>
+      </c>
+      <c r="C179" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D179" s="29">
+        <v>1</v>
+      </c>
+      <c r="E179" s="29">
+        <v>2</v>
+      </c>
+      <c r="F179" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="G179" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H179" s="28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="25">
+        <v>4</v>
+      </c>
+      <c r="B180" s="28">
+        <v>3</v>
+      </c>
+      <c r="C180" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="D180" s="29">
+        <v>1</v>
+      </c>
+      <c r="E180" s="29">
+        <v>2</v>
+      </c>
+      <c r="F180" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G180" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="H180" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="25">
+        <v>4</v>
+      </c>
+      <c r="B181" s="38">
+        <v>3</v>
+      </c>
+      <c r="C181" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D181" s="25">
+        <v>2</v>
+      </c>
+      <c r="E181" s="25">
+        <v>4</v>
+      </c>
+      <c r="F181" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="G181" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H181" s="38" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="25">
+        <v>4</v>
+      </c>
+      <c r="B182" s="38">
+        <v>3</v>
+      </c>
+      <c r="C182" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D182" s="25">
+        <v>2</v>
+      </c>
+      <c r="E182" s="25">
+        <v>4</v>
+      </c>
+      <c r="F182" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="G182" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H182" s="25" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" s="25">
+        <v>4</v>
+      </c>
+      <c r="B183" s="38">
+        <v>3</v>
+      </c>
+      <c r="C183" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D183" s="25">
+        <v>2</v>
+      </c>
+      <c r="E183" s="25">
+        <v>4</v>
+      </c>
+      <c r="F183" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="G183" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H183" s="38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="25">
+        <v>4</v>
+      </c>
+      <c r="B184" s="38">
+        <v>3</v>
+      </c>
+      <c r="C184" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D184" s="25">
+        <v>3</v>
+      </c>
+      <c r="E184" s="25">
+        <v>4</v>
+      </c>
+      <c r="F184" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G184" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H184" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="25">
+        <v>4</v>
+      </c>
+      <c r="B185" s="38">
+        <v>3</v>
+      </c>
+      <c r="C185" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D185" s="25">
+        <v>3</v>
+      </c>
+      <c r="E185" s="25">
+        <v>4</v>
+      </c>
+      <c r="F185" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="G185" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="H185" s="38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="25">
+        <v>4</v>
+      </c>
+      <c r="B186" s="38">
+        <v>3</v>
+      </c>
+      <c r="C186" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D186" s="25">
+        <v>3</v>
+      </c>
+      <c r="E186" s="25">
+        <v>4</v>
+      </c>
+      <c r="F186" s="38" t="s">
+        <v>432</v>
+      </c>
+      <c r="G186" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H186" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="25">
+        <v>4</v>
+      </c>
+      <c r="B187" s="38">
+        <v>3</v>
+      </c>
+      <c r="C187" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D187" s="25">
+        <v>4</v>
+      </c>
+      <c r="E187" s="25">
+        <v>4</v>
+      </c>
+      <c r="F187" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="G187" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H187" s="25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="25">
+        <v>4</v>
+      </c>
+      <c r="B188" s="38">
+        <v>3</v>
+      </c>
+      <c r="C188" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D188" s="25">
+        <v>4</v>
+      </c>
+      <c r="E188" s="25">
+        <v>4</v>
+      </c>
+      <c r="F188" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="G188" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H188" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="25">
+        <v>4</v>
+      </c>
+      <c r="B189" s="38">
+        <v>3</v>
+      </c>
+      <c r="C189" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D189" s="25">
+        <v>4</v>
+      </c>
+      <c r="E189" s="25">
+        <v>4</v>
+      </c>
+      <c r="F189" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="G189" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H189" s="25">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -22305,7 +23472,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F357C59-977B-4591-AD82-2B7621F6CA1A}">
-  <dimension ref="A1:I158"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -25556,16 +26723,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="30">
-        <v>3</v>
-      </c>
-      <c r="B129" s="31">
-        <v>4</v>
-      </c>
-      <c r="C129" s="31" t="s">
-        <v>40</v>
-      </c>
+    <row r="129" spans="6:8" x14ac:dyDescent="0.25">
       <c r="F129" s="31" t="s">
         <v>376</v>
       </c>
@@ -25573,736 +26731,9 @@
         <v>378</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="25">
-        <v>4</v>
-      </c>
-      <c r="B130" s="33">
-        <v>1</v>
-      </c>
-      <c r="C130" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D130" s="33">
-        <v>1</v>
-      </c>
-      <c r="E130" s="33">
-        <v>2</v>
-      </c>
-      <c r="F130" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="G130" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="H130" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="I130" s="37"/>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="25">
-        <v>4</v>
-      </c>
-      <c r="B131" s="33">
-        <v>1</v>
-      </c>
-      <c r="C131" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D131" s="33">
-        <v>1</v>
-      </c>
-      <c r="E131" s="33">
-        <v>2</v>
-      </c>
-      <c r="F131" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="G131" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="H131" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="I131" s="37"/>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="25">
-        <v>4</v>
-      </c>
-      <c r="B132" s="33">
-        <v>1</v>
-      </c>
-      <c r="C132" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D132" s="33">
-        <v>1</v>
-      </c>
-      <c r="E132" s="33">
-        <v>2</v>
-      </c>
-      <c r="F132" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="G132" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="H132" s="33">
-        <v>10</v>
-      </c>
-      <c r="I132" s="37"/>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="25">
-        <v>4</v>
-      </c>
-      <c r="B133" s="33">
-        <v>1</v>
-      </c>
-      <c r="C133" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D133" s="33">
-        <v>1</v>
-      </c>
-      <c r="E133" s="33">
-        <v>2</v>
-      </c>
-      <c r="F133" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G133" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="H133" s="33">
-        <v>8</v>
-      </c>
-      <c r="I133" s="37"/>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="25">
-        <v>4</v>
-      </c>
-      <c r="B134" s="33">
-        <v>1</v>
-      </c>
-      <c r="C134" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D134" s="33">
-        <v>1</v>
-      </c>
-      <c r="E134" s="33">
-        <v>2</v>
-      </c>
-      <c r="F134" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="G134" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="H134" s="33">
-        <v>8</v>
-      </c>
-      <c r="I134" s="37"/>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="25">
-        <v>4</v>
-      </c>
-      <c r="B135" s="25">
-        <v>1</v>
-      </c>
-      <c r="C135" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D135" s="25">
-        <v>1</v>
-      </c>
-      <c r="E135" s="25">
-        <v>2</v>
-      </c>
-      <c r="F135" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="G135" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="H135" s="38">
-        <v>8</v>
-      </c>
-      <c r="I135" s="37"/>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="25">
-        <v>4</v>
-      </c>
-      <c r="B136" s="25">
-        <v>1</v>
-      </c>
-      <c r="C136" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D136" s="38"/>
-      <c r="E136" s="38"/>
-      <c r="F136" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="G136" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="H136" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="I136" s="37"/>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="25">
-        <v>4</v>
-      </c>
-      <c r="B137" s="25">
-        <v>1</v>
-      </c>
-      <c r="C137" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D137" s="38"/>
-      <c r="E137" s="38"/>
-      <c r="F137" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="G137" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="H137" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="I137" s="37"/>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="25">
-        <v>4</v>
-      </c>
-      <c r="B138" s="25">
-        <v>1</v>
-      </c>
-      <c r="C138" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D138" s="38"/>
-      <c r="E138" s="38"/>
-      <c r="F138" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="G138" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="H138" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="I138" s="37"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="25">
-        <v>4</v>
-      </c>
-      <c r="B139" s="25">
-        <v>1</v>
-      </c>
-      <c r="C139" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D139" s="38"/>
-      <c r="E139" s="38"/>
-      <c r="F139" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="G139" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="H139" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="I139" s="37"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="25">
-        <v>4</v>
-      </c>
-      <c r="B140" s="25">
-        <v>1</v>
-      </c>
-      <c r="C140" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D140" s="38"/>
-      <c r="E140" s="38"/>
-      <c r="F140" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="G140" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="H140" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="I140" s="37"/>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="25">
-        <v>4</v>
-      </c>
-      <c r="B141" s="25">
-        <v>1</v>
-      </c>
-      <c r="C141" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D141" s="38"/>
-      <c r="E141" s="38"/>
-      <c r="F141" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="G141" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="H141" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="I141" s="37"/>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="25">
-        <v>4</v>
-      </c>
-      <c r="B142" s="25">
-        <v>1</v>
-      </c>
-      <c r="C142" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D142" s="38"/>
-      <c r="E142" s="38"/>
-      <c r="F142" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="G142" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="H142" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="I142" s="37"/>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="25">
-        <v>4</v>
-      </c>
-      <c r="B143" s="25">
-        <v>1</v>
-      </c>
-      <c r="C143" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D143" s="38">
-        <v>2</v>
-      </c>
-      <c r="E143" s="38">
-        <v>3</v>
-      </c>
-      <c r="F143" s="38" t="s">
-        <v>348</v>
-      </c>
-      <c r="G143" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="H143" s="38">
-        <v>20</v>
-      </c>
-      <c r="I143" s="37"/>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="25">
-        <v>4</v>
-      </c>
-      <c r="B144" s="25">
-        <v>1</v>
-      </c>
-      <c r="C144" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D144" s="38">
-        <v>2</v>
-      </c>
-      <c r="E144" s="38">
-        <v>3</v>
-      </c>
-      <c r="F144" s="38" t="s">
-        <v>416</v>
-      </c>
-      <c r="G144" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="H144" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="I144" s="37"/>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="25">
-        <v>4</v>
-      </c>
-      <c r="B145" s="25">
-        <v>1</v>
-      </c>
-      <c r="C145" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D145" s="38">
-        <v>2</v>
-      </c>
-      <c r="E145" s="38">
-        <v>3</v>
-      </c>
-      <c r="F145" s="38" t="s">
-        <v>417</v>
-      </c>
-      <c r="G145" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="H145" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="I145" s="37"/>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="25">
-        <v>4</v>
-      </c>
-      <c r="B146" s="16">
-        <v>2</v>
-      </c>
-      <c r="C146" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D146" s="14">
-        <v>1</v>
-      </c>
-      <c r="E146" s="14">
-        <v>2</v>
-      </c>
-      <c r="F146" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="G146" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H146" s="16">
-        <v>10</v>
-      </c>
-      <c r="I146" s="37"/>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="25">
-        <v>4</v>
-      </c>
-      <c r="B147" s="16">
-        <v>2</v>
-      </c>
-      <c r="C147" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D147" s="14">
-        <v>1</v>
-      </c>
-      <c r="E147" s="14">
-        <v>2</v>
-      </c>
-      <c r="F147" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G147" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H147" s="16">
-        <v>10</v>
-      </c>
-      <c r="I147" s="37"/>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="25">
-        <v>4</v>
-      </c>
-      <c r="B148" s="16">
-        <v>2</v>
-      </c>
-      <c r="C148" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D148" s="14">
-        <v>1</v>
-      </c>
-      <c r="E148" s="14">
-        <v>2</v>
-      </c>
-      <c r="F148" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G148" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H148" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="I148" s="37"/>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="25">
-        <v>4</v>
-      </c>
-      <c r="B149" s="16">
-        <v>2</v>
-      </c>
-      <c r="C149" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D149" s="14">
-        <v>1</v>
-      </c>
-      <c r="E149" s="14">
-        <v>2</v>
-      </c>
-      <c r="F149" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="G149" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H149" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I149" s="37"/>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="25">
-        <v>4</v>
-      </c>
-      <c r="B150" s="16">
-        <v>2</v>
-      </c>
-      <c r="C150" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D150" s="14">
-        <v>1</v>
-      </c>
-      <c r="E150" s="14">
-        <v>2</v>
-      </c>
-      <c r="F150" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G150" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H150" s="16">
-        <v>8</v>
-      </c>
-      <c r="I150" s="37"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="25">
-        <v>4</v>
-      </c>
-      <c r="B151" s="38">
-        <v>2</v>
-      </c>
-      <c r="C151" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="D151" s="25">
-        <v>1</v>
-      </c>
-      <c r="E151" s="25">
-        <v>2</v>
-      </c>
-      <c r="F151" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="G151" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="H151" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="I151" s="37"/>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="25">
-        <v>4</v>
-      </c>
-      <c r="B152" s="38">
-        <v>2</v>
-      </c>
-      <c r="C152" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D152" s="38"/>
-      <c r="E152" s="38"/>
-      <c r="F152" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="G152" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="H152" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="I152" s="37"/>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="25">
-        <v>4</v>
-      </c>
-      <c r="B153" s="38">
-        <v>2</v>
-      </c>
-      <c r="C153" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D153" s="38"/>
-      <c r="E153" s="38"/>
-      <c r="F153" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="G153" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="H153" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="I153" s="37"/>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="25">
-        <v>4</v>
-      </c>
-      <c r="B154" s="38">
-        <v>2</v>
-      </c>
-      <c r="C154" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D154" s="38"/>
-      <c r="E154" s="38"/>
-      <c r="F154" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="G154" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H154" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="I154" s="37"/>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="25">
-        <v>4</v>
-      </c>
-      <c r="B155" s="38">
-        <v>2</v>
-      </c>
-      <c r="C155" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D155" s="38"/>
-      <c r="E155" s="38"/>
-      <c r="F155" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="G155" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H155" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="I155" s="37"/>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="25">
-        <v>4</v>
-      </c>
-      <c r="B156" s="38">
-        <v>2</v>
-      </c>
-      <c r="C156" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D156" s="38"/>
-      <c r="E156" s="38"/>
-      <c r="F156" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="G156" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="H156" s="38" t="s">
-        <v>349</v>
-      </c>
-      <c r="I156" s="37"/>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="25">
-        <v>4</v>
-      </c>
-      <c r="B157" s="38">
-        <v>2</v>
-      </c>
-      <c r="C157" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D157" s="38"/>
-      <c r="E157" s="38"/>
-      <c r="F157" s="38" t="s">
-        <v>381</v>
-      </c>
-      <c r="G157" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H157" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="I157" s="37"/>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="25">
-        <v>4</v>
-      </c>
-      <c r="B158" s="38">
-        <v>2</v>
-      </c>
-      <c r="C158" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D158" s="38"/>
-      <c r="E158" s="38"/>
-      <c r="F158" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="G158" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H158" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="I158" s="37"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C158" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una de las 5 categorías de la lista." sqref="C2:C129" xr:uid="{9B2CBAAB-1FE6-41F8-8B5C-1091AE36B169}">
       <formula1>"Entrada en calor,Potencia,Fuerza,Core,Cardio"</formula1>
     </dataValidation>
   </dataValidations>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E874AD4-E65F-4D04-A455-503B618C6663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DE5811-8F86-475C-AC64-16310F39CE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8268" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8439" uniqueCount="519">
   <si>
     <t>Semana</t>
   </si>
@@ -1586,6 +1586,18 @@
   <si>
     <t>Bug dead alternado con tobilleras</t>
   </si>
+  <si>
+    <t>Aperturas banco inclinado</t>
+  </si>
+  <si>
+    <t>10-8-6-4-2 (Aumentando la carga)</t>
+  </si>
+  <si>
+    <t>Aperturas inclinado con mancuernas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bug dead alternado </t>
+  </si>
 </sst>
 </file>
 
@@ -19517,7 +19529,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -21849,6 +21861,1154 @@
         <v>19</v>
       </c>
       <c r="H93" s="19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="30">
+        <v>3</v>
+      </c>
+      <c r="B94" s="25">
+        <v>1</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="25">
+        <v>1</v>
+      </c>
+      <c r="E94" s="25">
+        <v>2</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G94" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="30">
+        <v>3</v>
+      </c>
+      <c r="B95" s="25">
+        <v>1</v>
+      </c>
+      <c r="C95" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="25">
+        <v>1</v>
+      </c>
+      <c r="E95" s="25">
+        <v>2</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="30">
+        <v>3</v>
+      </c>
+      <c r="B96" s="25">
+        <v>1</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="25">
+        <v>1</v>
+      </c>
+      <c r="E96" s="25">
+        <v>2</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="G96" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="30">
+        <v>3</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1</v>
+      </c>
+      <c r="C97" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="25">
+        <v>1</v>
+      </c>
+      <c r="E97" s="25">
+        <v>2</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H97" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="30">
+        <v>3</v>
+      </c>
+      <c r="B98" s="25">
+        <v>1</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="25">
+        <v>1</v>
+      </c>
+      <c r="E98" s="25">
+        <v>2</v>
+      </c>
+      <c r="F98" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" s="25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="30">
+        <v>3</v>
+      </c>
+      <c r="B99" s="30">
+        <v>1</v>
+      </c>
+      <c r="C99" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="30">
+        <v>1</v>
+      </c>
+      <c r="E99" s="30">
+        <v>2</v>
+      </c>
+      <c r="F99" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H99" s="31">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="30">
+        <v>3</v>
+      </c>
+      <c r="B100" s="30">
+        <v>1</v>
+      </c>
+      <c r="C100" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D100" s="31"/>
+      <c r="E100" s="31"/>
+      <c r="F100" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G100" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" s="31" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="30">
+        <v>3</v>
+      </c>
+      <c r="B101" s="30">
+        <v>1</v>
+      </c>
+      <c r="C101" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D101" s="31"/>
+      <c r="E101" s="31"/>
+      <c r="F101" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="G101" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" s="31" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="30">
+        <v>3</v>
+      </c>
+      <c r="B102" s="30">
+        <v>1</v>
+      </c>
+      <c r="C102" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D102" s="31"/>
+      <c r="E102" s="31"/>
+      <c r="F102" s="32" t="s">
+        <v>517</v>
+      </c>
+      <c r="G102" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="H102" s="31" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="30">
+        <v>3</v>
+      </c>
+      <c r="B103" s="30">
+        <v>1</v>
+      </c>
+      <c r="C103" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D103" s="31"/>
+      <c r="E103" s="31"/>
+      <c r="F103" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="G103" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="30">
+        <v>3</v>
+      </c>
+      <c r="B104" s="30">
+        <v>1</v>
+      </c>
+      <c r="C104" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D104" s="31"/>
+      <c r="E104" s="31"/>
+      <c r="F104" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H104" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="30">
+        <v>3</v>
+      </c>
+      <c r="B105" s="30">
+        <v>1</v>
+      </c>
+      <c r="C105" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D105" s="31"/>
+      <c r="E105" s="31"/>
+      <c r="F105" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="G105" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="31" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="30">
+        <v>3</v>
+      </c>
+      <c r="B106" s="30">
+        <v>1</v>
+      </c>
+      <c r="C106" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="31">
+        <v>2</v>
+      </c>
+      <c r="E106" s="31">
+        <v>3</v>
+      </c>
+      <c r="F106" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="G106" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="30">
+        <v>3</v>
+      </c>
+      <c r="B107" s="30">
+        <v>1</v>
+      </c>
+      <c r="C107" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="31">
+        <v>2</v>
+      </c>
+      <c r="E107" s="31">
+        <v>3</v>
+      </c>
+      <c r="F107" s="31" t="s">
+        <v>518</v>
+      </c>
+      <c r="G107" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" s="31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="30">
+        <v>3</v>
+      </c>
+      <c r="B108" s="30">
+        <v>1</v>
+      </c>
+      <c r="C108" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="31">
+        <v>2</v>
+      </c>
+      <c r="E108" s="31">
+        <v>3</v>
+      </c>
+      <c r="F108" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G108" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" s="31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="30">
+        <v>3</v>
+      </c>
+      <c r="B109" s="26">
+        <v>2</v>
+      </c>
+      <c r="C109" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="27">
+        <v>1</v>
+      </c>
+      <c r="E109" s="27">
+        <v>2</v>
+      </c>
+      <c r="F109" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="G109" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H109" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="30">
+        <v>3</v>
+      </c>
+      <c r="B110" s="26">
+        <v>2</v>
+      </c>
+      <c r="C110" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="27">
+        <v>1</v>
+      </c>
+      <c r="E110" s="27">
+        <v>2</v>
+      </c>
+      <c r="F110" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="G110" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H110" s="26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="30">
+        <v>3</v>
+      </c>
+      <c r="B111" s="26">
+        <v>2</v>
+      </c>
+      <c r="C111" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="27">
+        <v>1</v>
+      </c>
+      <c r="E111" s="27">
+        <v>2</v>
+      </c>
+      <c r="F111" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" s="26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="30">
+        <v>3</v>
+      </c>
+      <c r="B112" s="26">
+        <v>2</v>
+      </c>
+      <c r="C112" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="27">
+        <v>1</v>
+      </c>
+      <c r="E112" s="27">
+        <v>2</v>
+      </c>
+      <c r="F112" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="G112" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="H112" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="30">
+        <v>3</v>
+      </c>
+      <c r="B113" s="26">
+        <v>2</v>
+      </c>
+      <c r="C113" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="27">
+        <v>1</v>
+      </c>
+      <c r="E113" s="27">
+        <v>2</v>
+      </c>
+      <c r="F113" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G113" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="H113" s="26">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="30">
+        <v>3</v>
+      </c>
+      <c r="B114" s="31">
+        <v>2</v>
+      </c>
+      <c r="C114" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="30">
+        <v>1</v>
+      </c>
+      <c r="E114" s="30">
+        <v>2</v>
+      </c>
+      <c r="F114" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G114" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="30">
+        <v>3</v>
+      </c>
+      <c r="B115" s="31">
+        <v>2</v>
+      </c>
+      <c r="C115" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D115" s="31"/>
+      <c r="E115" s="31"/>
+      <c r="F115" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G115" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H115" s="31" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="30">
+        <v>3</v>
+      </c>
+      <c r="B116" s="31">
+        <v>2</v>
+      </c>
+      <c r="C116" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D116" s="31"/>
+      <c r="E116" s="31"/>
+      <c r="F116" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="G116" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="31" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="30">
+        <v>3</v>
+      </c>
+      <c r="B117" s="31">
+        <v>2</v>
+      </c>
+      <c r="C117" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D117" s="31"/>
+      <c r="E117" s="31"/>
+      <c r="F117" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G117" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="30">
+        <v>3</v>
+      </c>
+      <c r="B118" s="31">
+        <v>2</v>
+      </c>
+      <c r="C118" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D118" s="31"/>
+      <c r="E118" s="31"/>
+      <c r="F118" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="G118" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H118" s="31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="30">
+        <v>3</v>
+      </c>
+      <c r="B119" s="31">
+        <v>2</v>
+      </c>
+      <c r="C119" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D119" s="31"/>
+      <c r="E119" s="31"/>
+      <c r="F119" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="G119" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H119" s="31" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="30">
+        <v>3</v>
+      </c>
+      <c r="B120" s="31">
+        <v>2</v>
+      </c>
+      <c r="C120" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D120" s="31"/>
+      <c r="E120" s="31"/>
+      <c r="F120" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G120" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H120" s="31" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="30">
+        <v>3</v>
+      </c>
+      <c r="B121" s="31">
+        <v>2</v>
+      </c>
+      <c r="C121" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D121" s="31">
+        <v>2</v>
+      </c>
+      <c r="E121" s="31">
+        <v>3</v>
+      </c>
+      <c r="F121" s="31" t="s">
+        <v>313</v>
+      </c>
+      <c r="G121" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" s="31" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="30">
+        <v>3</v>
+      </c>
+      <c r="B122" s="31">
+        <v>2</v>
+      </c>
+      <c r="C122" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D122" s="31">
+        <v>2</v>
+      </c>
+      <c r="E122" s="31">
+        <v>3</v>
+      </c>
+      <c r="F122" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="G122" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" s="31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="30">
+        <v>3</v>
+      </c>
+      <c r="B123" s="31">
+        <v>2</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D123" s="31">
+        <v>2</v>
+      </c>
+      <c r="E123" s="31">
+        <v>3</v>
+      </c>
+      <c r="F123" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G123" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="30">
+        <v>3</v>
+      </c>
+      <c r="B124" s="28">
+        <v>3</v>
+      </c>
+      <c r="C124" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="29">
+        <v>1</v>
+      </c>
+      <c r="E124" s="29">
+        <v>2</v>
+      </c>
+      <c r="F124" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G124" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H124" s="28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="30">
+        <v>3</v>
+      </c>
+      <c r="B125" s="28">
+        <v>3</v>
+      </c>
+      <c r="C125" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="29">
+        <v>1</v>
+      </c>
+      <c r="E125" s="29">
+        <v>2</v>
+      </c>
+      <c r="F125" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="G125" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="30">
+        <v>3</v>
+      </c>
+      <c r="B126" s="28">
+        <v>3</v>
+      </c>
+      <c r="C126" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="29">
+        <v>1</v>
+      </c>
+      <c r="E126" s="29">
+        <v>2</v>
+      </c>
+      <c r="F126" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="G126" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="30">
+        <v>3</v>
+      </c>
+      <c r="B127" s="28">
+        <v>3</v>
+      </c>
+      <c r="C127" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="29">
+        <v>1</v>
+      </c>
+      <c r="E127" s="29">
+        <v>2</v>
+      </c>
+      <c r="F127" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="G127" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H127" s="28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="30">
+        <v>3</v>
+      </c>
+      <c r="B128" s="28">
+        <v>3</v>
+      </c>
+      <c r="C128" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="29">
+        <v>1</v>
+      </c>
+      <c r="E128" s="29">
+        <v>2</v>
+      </c>
+      <c r="F128" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G128" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H128" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="30">
+        <v>3</v>
+      </c>
+      <c r="B129" s="31">
+        <v>3</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="30">
+        <v>1</v>
+      </c>
+      <c r="E129" s="30">
+        <v>2</v>
+      </c>
+      <c r="F129" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G129" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="30">
+        <v>3</v>
+      </c>
+      <c r="B130" s="31">
+        <v>3</v>
+      </c>
+      <c r="C130" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D130" s="31">
+        <v>2</v>
+      </c>
+      <c r="E130" s="31">
+        <v>4</v>
+      </c>
+      <c r="F130" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G130" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="30">
+        <v>3</v>
+      </c>
+      <c r="B131" s="31">
+        <v>3</v>
+      </c>
+      <c r="C131" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D131" s="31">
+        <v>2</v>
+      </c>
+      <c r="E131" s="31">
+        <v>4</v>
+      </c>
+      <c r="F131" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="G131" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="H131" s="31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="30">
+        <v>3</v>
+      </c>
+      <c r="B132" s="31">
+        <v>3</v>
+      </c>
+      <c r="C132" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D132" s="30">
+        <v>2</v>
+      </c>
+      <c r="E132" s="31">
+        <v>4</v>
+      </c>
+      <c r="F132" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="G132" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H132" s="31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="30">
+        <v>3</v>
+      </c>
+      <c r="B133" s="31">
+        <v>3</v>
+      </c>
+      <c r="C133" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D133" s="30">
+        <v>3</v>
+      </c>
+      <c r="E133" s="31">
+        <v>4</v>
+      </c>
+      <c r="F133" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="G133" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="30">
+        <v>3</v>
+      </c>
+      <c r="B134" s="31">
+        <v>3</v>
+      </c>
+      <c r="C134" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D134" s="30">
+        <v>3</v>
+      </c>
+      <c r="E134" s="31">
+        <v>4</v>
+      </c>
+      <c r="F134" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="G134" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H134" s="32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="30">
+        <v>3</v>
+      </c>
+      <c r="B135" s="31">
+        <v>3</v>
+      </c>
+      <c r="C135" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D135" s="30">
+        <v>3</v>
+      </c>
+      <c r="E135" s="31">
+        <v>4</v>
+      </c>
+      <c r="F135" s="31" t="s">
+        <v>298</v>
+      </c>
+      <c r="G135" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="30">
+        <v>3</v>
+      </c>
+      <c r="B136" s="31">
+        <v>3</v>
+      </c>
+      <c r="C136" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D136" s="30">
+        <v>4</v>
+      </c>
+      <c r="E136" s="31">
+        <v>4</v>
+      </c>
+      <c r="F136" s="31" t="s">
+        <v>310</v>
+      </c>
+      <c r="G136" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="32" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="30">
+        <v>3</v>
+      </c>
+      <c r="B137" s="31">
+        <v>3</v>
+      </c>
+      <c r="C137" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D137" s="30">
+        <v>4</v>
+      </c>
+      <c r="E137" s="31">
+        <v>4</v>
+      </c>
+      <c r="F137" s="31" t="s">
+        <v>408</v>
+      </c>
+      <c r="G137" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="30">
+        <v>3</v>
+      </c>
+      <c r="B138" s="31">
+        <v>3</v>
+      </c>
+      <c r="C138" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" s="30">
+        <v>4</v>
+      </c>
+      <c r="E138" s="31">
+        <v>4</v>
+      </c>
+      <c r="F138" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="G138" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="H138" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="30">
+        <v>3</v>
+      </c>
+      <c r="B139" s="31">
+        <v>3</v>
+      </c>
+      <c r="C139" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D139" s="30">
+        <v>4</v>
+      </c>
+      <c r="E139" s="31">
+        <v>4</v>
+      </c>
+      <c r="F139" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G139" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H139" s="32">
         <v>20</v>
       </c>
     </row>
@@ -57758,7 +58918,7 @@
       <c r="D182" s="52"/>
       <c r="E182" s="52"/>
       <c r="F182" s="52" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G182" s="52" t="s">
         <v>17</v>
@@ -57781,7 +58941,7 @@
       <c r="D183" s="52"/>
       <c r="E183" s="52"/>
       <c r="F183" s="52" t="s">
-        <v>344</v>
+        <v>495</v>
       </c>
       <c r="G183" s="52" t="s">
         <v>17</v>
@@ -57804,7 +58964,7 @@
       <c r="D184" s="52"/>
       <c r="E184" s="52"/>
       <c r="F184" s="52" t="s">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="G184" s="52" t="s">
         <v>17</v>
@@ -58496,13 +59656,13 @@
       <c r="D212" s="52"/>
       <c r="E212" s="52"/>
       <c r="F212" s="52" t="s">
-        <v>347</v>
+        <v>188</v>
       </c>
       <c r="G212" s="52" t="s">
         <v>17</v>
       </c>
       <c r="H212" s="52" t="s">
-        <v>70</v>
+        <v>493</v>
       </c>
       <c r="I212" s="53"/>
     </row>

--- a/pwa/rutinas.xlsx
+++ b/pwa/rutinas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5042FE63-8394-4856-B76D-7B510CC963F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B3BB58-EB36-4224-9940-729BE8C227AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PINES" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9889" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10007" uniqueCount="553">
   <si>
     <t>Semana</t>
   </si>
@@ -1695,6 +1695,12 @@
   <si>
     <t xml:space="preserve">Row serrucho  </t>
   </si>
+  <si>
+    <t>1x5 (70%) 2x3 (80%) 2x2 (90%RM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vuelos laterales   </t>
+  </si>
 </sst>
 </file>
 
@@ -45039,7 +45045,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -47969,7 +47975,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B113" s="25">
         <v>1</v>
@@ -47996,7 +48002,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B114" s="25">
         <v>1</v>
@@ -48023,7 +48029,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B115" s="25">
         <v>1</v>
@@ -48050,7 +48056,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B116" s="25">
         <v>1</v>
@@ -48077,7 +48083,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B117" s="25">
         <v>1</v>
@@ -48104,7 +48110,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B118" s="49">
         <v>1</v>
@@ -48131,7 +48137,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B119" s="49">
         <v>1</v>
@@ -48154,7 +48160,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B120" s="49">
         <v>1</v>
@@ -48177,7 +48183,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B121" s="49">
         <v>1</v>
@@ -48200,7 +48206,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B122" s="49">
         <v>1</v>
@@ -48223,7 +48229,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B123" s="49">
         <v>1</v>
@@ -48246,7 +48252,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B124" s="49">
         <v>1</v>
@@ -48269,7 +48275,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B125" s="26">
         <v>2</v>
@@ -48296,7 +48302,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B126" s="26">
         <v>2</v>
@@ -48323,7 +48329,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B127" s="26">
         <v>2</v>
@@ -48350,7 +48356,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B128" s="26">
         <v>2</v>
@@ -48377,7 +48383,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B129" s="26">
         <v>2</v>
@@ -48404,7 +48410,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B130" s="51">
         <v>2</v>
@@ -48431,7 +48437,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B131" s="51">
         <v>2</v>
@@ -48452,7 +48458,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B132" s="51">
         <v>2</v>
@@ -48473,7 +48479,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B133" s="51">
         <v>2</v>
@@ -48494,7 +48500,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B134" s="51">
         <v>2</v>
@@ -48515,7 +48521,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B135" s="51">
         <v>2</v>
@@ -48536,7 +48542,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B136" s="51">
         <v>2</v>
@@ -48557,7 +48563,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B137" s="28">
         <v>3</v>
@@ -48584,7 +48590,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B138" s="28">
         <v>3</v>
@@ -48611,7 +48617,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B139" s="28">
         <v>3</v>
@@ -48638,7 +48644,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B140" s="28">
         <v>3</v>
@@ -48665,7 +48671,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B141" s="28">
         <v>3</v>
@@ -48692,7 +48698,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B142" s="51">
         <v>3</v>
@@ -48719,7 +48725,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B143" s="51">
         <v>3</v>
@@ -48746,7 +48752,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B144" s="51">
         <v>3</v>
@@ -48773,7 +48779,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B145" s="51">
         <v>3</v>
@@ -48800,7 +48806,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B146" s="51">
         <v>3</v>
@@ -48827,7 +48833,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B147" s="51">
         <v>3</v>
@@ -48854,7 +48860,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B148" s="51">
         <v>3</v>
@@ -48881,7 +48887,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B149" s="51">
         <v>3</v>
@@ -48908,7 +48914,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B150" s="51">
         <v>3</v>
@@ -48935,7 +48941,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B151" s="51">
         <v>3</v>
@@ -48959,6 +48965,959 @@
         <v>10</v>
       </c>
       <c r="I151" s="50"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="54">
+        <v>4</v>
+      </c>
+      <c r="B152" s="39">
+        <v>1</v>
+      </c>
+      <c r="C152" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="40">
+        <v>1</v>
+      </c>
+      <c r="E152" s="40">
+        <v>2</v>
+      </c>
+      <c r="F152" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="G152" s="41"/>
+      <c r="H152" s="41">
+        <v>10</v>
+      </c>
+      <c r="I152" s="56"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="54">
+        <v>4</v>
+      </c>
+      <c r="B153" s="39">
+        <v>1</v>
+      </c>
+      <c r="C153" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="40">
+        <v>1</v>
+      </c>
+      <c r="E153" s="40">
+        <v>2</v>
+      </c>
+      <c r="F153" s="41" t="s">
+        <v>325</v>
+      </c>
+      <c r="G153" s="41"/>
+      <c r="H153" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="I153" s="56"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="54">
+        <v>4</v>
+      </c>
+      <c r="B154" s="39">
+        <v>1</v>
+      </c>
+      <c r="C154" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="40">
+        <v>1</v>
+      </c>
+      <c r="E154" s="40">
+        <v>2</v>
+      </c>
+      <c r="F154" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="G154" s="41"/>
+      <c r="H154" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="I154" s="56"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="54">
+        <v>4</v>
+      </c>
+      <c r="B155" s="39">
+        <v>1</v>
+      </c>
+      <c r="C155" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="40">
+        <v>1</v>
+      </c>
+      <c r="E155" s="40">
+        <v>2</v>
+      </c>
+      <c r="F155" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="G155" s="41"/>
+      <c r="H155" s="41">
+        <v>10</v>
+      </c>
+      <c r="I155" s="56"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="54">
+        <v>4</v>
+      </c>
+      <c r="B156" s="39">
+        <v>1</v>
+      </c>
+      <c r="C156" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="40">
+        <v>1</v>
+      </c>
+      <c r="E156" s="40">
+        <v>2</v>
+      </c>
+      <c r="F156" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G156" s="41"/>
+      <c r="H156" s="41">
+        <v>8</v>
+      </c>
+      <c r="I156" s="56"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="54">
+        <v>4</v>
+      </c>
+      <c r="B157" s="39">
+        <v>1</v>
+      </c>
+      <c r="C157" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="40">
+        <v>1</v>
+      </c>
+      <c r="E157" s="40">
+        <v>2</v>
+      </c>
+      <c r="F157" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="G157" s="41"/>
+      <c r="H157" s="41">
+        <v>10</v>
+      </c>
+      <c r="I157" s="56"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="54">
+        <v>4</v>
+      </c>
+      <c r="B158" s="54">
+        <v>1</v>
+      </c>
+      <c r="C158" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D158" s="55"/>
+      <c r="E158" s="55"/>
+      <c r="F158" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="G158" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" s="55" t="s">
+        <v>551</v>
+      </c>
+      <c r="I158" s="56"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="54">
+        <v>4</v>
+      </c>
+      <c r="B159" s="54">
+        <v>1</v>
+      </c>
+      <c r="C159" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D159" s="55"/>
+      <c r="E159" s="55"/>
+      <c r="F159" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="G159" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="I159" s="56"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="54">
+        <v>4</v>
+      </c>
+      <c r="B160" s="54">
+        <v>1</v>
+      </c>
+      <c r="C160" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D160" s="55"/>
+      <c r="E160" s="55"/>
+      <c r="F160" s="55" t="s">
+        <v>255</v>
+      </c>
+      <c r="G160" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H160" s="55" t="s">
+        <v>256</v>
+      </c>
+      <c r="I160" s="56"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="54">
+        <v>4</v>
+      </c>
+      <c r="B161" s="54">
+        <v>1</v>
+      </c>
+      <c r="C161" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D161" s="55"/>
+      <c r="E161" s="55"/>
+      <c r="F161" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="G161" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H161" s="55" t="s">
+        <v>551</v>
+      </c>
+      <c r="I161" s="56"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="54">
+        <v>4</v>
+      </c>
+      <c r="B162" s="54">
+        <v>1</v>
+      </c>
+      <c r="C162" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D162" s="55"/>
+      <c r="E162" s="55"/>
+      <c r="F162" s="55" t="s">
+        <v>230</v>
+      </c>
+      <c r="G162" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H162" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="I162" s="56"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="54">
+        <v>4</v>
+      </c>
+      <c r="B163" s="54">
+        <v>1</v>
+      </c>
+      <c r="C163" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D163" s="55"/>
+      <c r="E163" s="55"/>
+      <c r="F163" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="G163" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H163" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="I163" s="56"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="54">
+        <v>4</v>
+      </c>
+      <c r="B164" s="42">
+        <v>2</v>
+      </c>
+      <c r="C164" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="43">
+        <v>1</v>
+      </c>
+      <c r="E164" s="43">
+        <v>2</v>
+      </c>
+      <c r="F164" s="44" t="s">
+        <v>331</v>
+      </c>
+      <c r="G164" s="44"/>
+      <c r="H164" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="I164" s="56"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="54">
+        <v>4</v>
+      </c>
+      <c r="B165" s="42">
+        <v>2</v>
+      </c>
+      <c r="C165" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="43">
+        <v>1</v>
+      </c>
+      <c r="E165" s="43">
+        <v>2</v>
+      </c>
+      <c r="F165" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="44"/>
+      <c r="H165" s="44">
+        <v>10</v>
+      </c>
+      <c r="I165" s="56"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="54">
+        <v>4</v>
+      </c>
+      <c r="B166" s="42">
+        <v>2</v>
+      </c>
+      <c r="C166" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="43">
+        <v>1</v>
+      </c>
+      <c r="E166" s="43">
+        <v>2</v>
+      </c>
+      <c r="F166" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="G166" s="44"/>
+      <c r="H166" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="I166" s="56"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="54">
+        <v>4</v>
+      </c>
+      <c r="B167" s="42">
+        <v>2</v>
+      </c>
+      <c r="C167" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="43">
+        <v>1</v>
+      </c>
+      <c r="E167" s="43">
+        <v>2</v>
+      </c>
+      <c r="F167" s="44" t="s">
+        <v>332</v>
+      </c>
+      <c r="G167" s="44"/>
+      <c r="H167" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="I167" s="56"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="54">
+        <v>4</v>
+      </c>
+      <c r="B168" s="42">
+        <v>2</v>
+      </c>
+      <c r="C168" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="43">
+        <v>1</v>
+      </c>
+      <c r="E168" s="43">
+        <v>2</v>
+      </c>
+      <c r="F168" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="G168" s="44"/>
+      <c r="H168" s="44">
+        <v>10</v>
+      </c>
+      <c r="I168" s="56"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="54">
+        <v>4</v>
+      </c>
+      <c r="B169" s="42">
+        <v>2</v>
+      </c>
+      <c r="C169" s="43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="43">
+        <v>1</v>
+      </c>
+      <c r="E169" s="43">
+        <v>2</v>
+      </c>
+      <c r="F169" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="G169" s="44"/>
+      <c r="H169" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="I169" s="56"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="54">
+        <v>4</v>
+      </c>
+      <c r="B170" s="55">
+        <v>2</v>
+      </c>
+      <c r="C170" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D170" s="55"/>
+      <c r="E170" s="55"/>
+      <c r="F170" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="G170" s="55"/>
+      <c r="H170" s="55" t="s">
+        <v>551</v>
+      </c>
+      <c r="I170" s="56"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="54">
+        <v>4</v>
+      </c>
+      <c r="B171" s="55">
+        <v>2</v>
+      </c>
+      <c r="C171" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D171" s="55"/>
+      <c r="E171" s="55"/>
+      <c r="F171" s="55" t="s">
+        <v>252</v>
+      </c>
+      <c r="G171" s="55"/>
+      <c r="H171" s="55" t="s">
+        <v>263</v>
+      </c>
+      <c r="I171" s="56"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="54">
+        <v>4</v>
+      </c>
+      <c r="B172" s="55">
+        <v>2</v>
+      </c>
+      <c r="C172" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D172" s="55"/>
+      <c r="E172" s="55"/>
+      <c r="F172" s="55" t="s">
+        <v>229</v>
+      </c>
+      <c r="G172" s="55"/>
+      <c r="H172" s="55" t="s">
+        <v>263</v>
+      </c>
+      <c r="I172" s="56"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="54">
+        <v>4</v>
+      </c>
+      <c r="B173" s="55">
+        <v>2</v>
+      </c>
+      <c r="C173" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D173" s="55"/>
+      <c r="E173" s="55"/>
+      <c r="F173" s="55" t="s">
+        <v>195</v>
+      </c>
+      <c r="G173" s="55"/>
+      <c r="H173" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="I173" s="56"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="54">
+        <v>4</v>
+      </c>
+      <c r="B174" s="55">
+        <v>2</v>
+      </c>
+      <c r="C174" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D174" s="55"/>
+      <c r="E174" s="55"/>
+      <c r="F174" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="G174" s="55"/>
+      <c r="H174" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="I174" s="56"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="54">
+        <v>4</v>
+      </c>
+      <c r="B175" s="55">
+        <v>2</v>
+      </c>
+      <c r="C175" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D175" s="55"/>
+      <c r="E175" s="55"/>
+      <c r="F175" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="G175" s="55"/>
+      <c r="H175" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="I175" s="56"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="54">
+        <v>4</v>
+      </c>
+      <c r="B176" s="45">
+        <v>3</v>
+      </c>
+      <c r="C176" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="46">
+        <v>1</v>
+      </c>
+      <c r="E176" s="46">
+        <v>2</v>
+      </c>
+      <c r="F176" s="47" t="s">
+        <v>335</v>
+      </c>
+      <c r="G176" s="47"/>
+      <c r="H176" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="I176" s="56"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="54">
+        <v>4</v>
+      </c>
+      <c r="B177" s="45">
+        <v>3</v>
+      </c>
+      <c r="C177" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="46">
+        <v>1</v>
+      </c>
+      <c r="E177" s="46">
+        <v>2</v>
+      </c>
+      <c r="F177" s="47" t="s">
+        <v>337</v>
+      </c>
+      <c r="G177" s="47"/>
+      <c r="H177" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="I177" s="56"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="54">
+        <v>4</v>
+      </c>
+      <c r="B178" s="45">
+        <v>3</v>
+      </c>
+      <c r="C178" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" s="46">
+        <v>1</v>
+      </c>
+      <c r="E178" s="46">
+        <v>2</v>
+      </c>
+      <c r="F178" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178" s="47"/>
+      <c r="H178" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="I178" s="56"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="54">
+        <v>4</v>
+      </c>
+      <c r="B179" s="45">
+        <v>3</v>
+      </c>
+      <c r="C179" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179" s="46">
+        <v>1</v>
+      </c>
+      <c r="E179" s="46">
+        <v>2</v>
+      </c>
+      <c r="F179" s="47" t="s">
+        <v>338</v>
+      </c>
+      <c r="G179" s="47"/>
+      <c r="H179" s="47">
+        <v>5</v>
+      </c>
+      <c r="I179" s="56"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="54">
+        <v>4</v>
+      </c>
+      <c r="B180" s="45">
+        <v>3</v>
+      </c>
+      <c r="C180" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="46">
+        <v>1</v>
+      </c>
+      <c r="E180" s="46">
+        <v>2</v>
+      </c>
+      <c r="F180" s="47" t="s">
+        <v>339</v>
+      </c>
+      <c r="G180" s="47"/>
+      <c r="H180" s="47">
+        <v>10</v>
+      </c>
+      <c r="I180" s="56"/>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="54">
+        <v>4</v>
+      </c>
+      <c r="B181" s="45">
+        <v>3</v>
+      </c>
+      <c r="C181" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="46">
+        <v>1</v>
+      </c>
+      <c r="E181" s="46">
+        <v>2</v>
+      </c>
+      <c r="F181" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="G181" s="47"/>
+      <c r="H181" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I181" s="56"/>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="54">
+        <v>4</v>
+      </c>
+      <c r="B182" s="55">
+        <v>3</v>
+      </c>
+      <c r="C182" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D182" s="55"/>
+      <c r="E182" s="55"/>
+      <c r="F182" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="G182" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H182" s="55" t="s">
+        <v>551</v>
+      </c>
+      <c r="I182" s="56"/>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="54">
+        <v>4</v>
+      </c>
+      <c r="B183" s="55">
+        <v>3</v>
+      </c>
+      <c r="C183" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D183" s="55">
+        <v>2</v>
+      </c>
+      <c r="E183" s="55">
+        <v>4</v>
+      </c>
+      <c r="F183" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="G183" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H183" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I183" s="56"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="54">
+        <v>4</v>
+      </c>
+      <c r="B184" s="55">
+        <v>3</v>
+      </c>
+      <c r="C184" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D184" s="55">
+        <v>2</v>
+      </c>
+      <c r="E184" s="55">
+        <v>4</v>
+      </c>
+      <c r="F184" s="55" t="s">
+        <v>552</v>
+      </c>
+      <c r="G184" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H184" s="55">
+        <v>10</v>
+      </c>
+      <c r="I184" s="56"/>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="54">
+        <v>4</v>
+      </c>
+      <c r="B185" s="55">
+        <v>3</v>
+      </c>
+      <c r="C185" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D185" s="55">
+        <v>3</v>
+      </c>
+      <c r="E185" s="55">
+        <v>3</v>
+      </c>
+      <c r="F185" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="G185" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="H185" s="55">
+        <v>6</v>
+      </c>
+      <c r="I185" s="56"/>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="54">
+        <v>4</v>
+      </c>
+      <c r="B186" s="55">
+        <v>3</v>
+      </c>
+      <c r="C186" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D186" s="55">
+        <v>3</v>
+      </c>
+      <c r="E186" s="55">
+        <v>3</v>
+      </c>
+      <c r="F186" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="G186" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H186" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="I186" s="56"/>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="54">
+        <v>4</v>
+      </c>
+      <c r="B187" s="55">
+        <v>3</v>
+      </c>
+      <c r="C187" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D187" s="55">
+        <v>3</v>
+      </c>
+      <c r="E187" s="55">
+        <v>3</v>
+      </c>
+      <c r="F187" s="55" t="s">
+        <v>288</v>
+      </c>
+      <c r="G187" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H187" s="55">
+        <v>20</v>
+      </c>
+      <c r="I187" s="56"/>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="54">
+        <v>4</v>
+      </c>
+      <c r="B188" s="55">
+        <v>3</v>
+      </c>
+      <c r="C188" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D188" s="55">
+        <v>4</v>
+      </c>
+      <c r="E188" s="55">
+        <v>3</v>
+      </c>
+      <c r="F188" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="G188" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H188" s="55">
+        <v>8</v>
+      </c>
+      <c r="I188" s="56"/>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="54">
+        <v>4</v>
+      </c>
+      <c r="B189" s="55">
+        <v>3</v>
+      </c>
+      <c r="C189" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D189" s="55">
+        <v>4</v>
+      </c>
+      <c r="E189" s="55">
+        <v>3</v>
+      </c>
+      <c r="F189" s="55" t="s">
+        <v>210</v>
+      </c>
+      <c r="G189" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H189" s="55">
+        <v>8</v>
+      </c>
+      <c r="I189" s="56"/>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="54">
+        <v>4</v>
+      </c>
+      <c r="B190" s="55">
+        <v>3</v>
+      </c>
+      <c r="C190" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D190" s="55">
+        <v>4</v>
+      </c>
+      <c r="E190" s="55">
+        <v>3</v>
+      </c>
+      <c r="F190" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="G190" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H190" s="55">
+        <v>10</v>
+      </c>
+      <c r="I190" s="56"/>
     </row>
   </sheetData>
   <dataValidations count="1">
